--- a/data/value_bets_log.xlsx
+++ b/data/value_bets_log.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,13 +43,9 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -78,17 +74,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF0000"/>
+        <fgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
     <fill>
@@ -115,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -141,10 +132,7 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -512,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -606,22 +594,22 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>04:34</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>✅ Emiliana Arango</t>
+          <t>✅ Caty McNally</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Linda Noskova</t>
+          <t>Marta Kostyuk</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -635,16 +623,16 @@
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>4.18</v>
+        <v>4.01</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>23.9</v>
+        <v>24.9</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>76.90000000000001</v>
+        <v>37</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -662,49 +650,49 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>04:34</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>✅ Sergey Fomin</t>
+          <t>✅ Hiroki Moriya</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Andrej Nedic</t>
+          <t>Marat Sharipov</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Shymkent, Kazakhstan Men Singles</t>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>CLAY</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="G3" s="8" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>1.91</v>
+        <v>2.72</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>52.2</v>
+        <v>36.8</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>69.8</v>
+        <v>34.3</v>
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>TA-clay</t>
+          <t>TA-hard</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
@@ -718,27 +706,27 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>04:34</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>✅ Elena-Gabriela Ruse</t>
+          <t>✅ Laslo Djere</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Elena Rybakina</t>
+          <t>Justin Engel</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>WTA - WTA Madrid, Spain Women Singles</t>
+          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -747,16 +735,16 @@
         </is>
       </c>
       <c r="G4" s="4" t="n">
-        <v>11</v>
+        <v>1.44</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>6.83</v>
+        <v>1.12</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>14.6</v>
+        <v>89.2</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>61</v>
+        <v>28.5</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
@@ -774,27 +762,27 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>04:34</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>✅ Stefanos Sakellaridis</t>
+          <t>✅ Coco Gauff</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Jacopo Vasami</t>
+          <t>Linda Noskova</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Rome, Italy Men Singles</t>
+          <t>WTA - WTA Madrid, Spain Women Singles</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -803,16 +791,16 @@
         </is>
       </c>
       <c r="G5" s="8" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>44.3</v>
+        <v>81.2</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>27.5</v>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
@@ -830,27 +818,27 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>04:34</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>✅ Clement Tabur</t>
+          <t>✅ Yusuke Takahashi</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Kilian Feldbausch</t>
+          <t>Yuta Shimizu</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Savannah, USA Men Singles</t>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -859,16 +847,16 @@
         </is>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.75</v>
+        <v>3.75</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>1.22</v>
+        <v>3.07</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>43.3</v>
+        <v>32.6</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>22.3</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
@@ -886,22 +874,22 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>04:34</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>✅ Marin Cilic</t>
+          <t>✅ Daniil Medvedev</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Joao Fonseca</t>
+          <t>Nicolai Budkov Kjaer</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -915,16 +903,16 @@
         </is>
       </c>
       <c r="G7" s="8" t="n">
-        <v>4.33</v>
+        <v>1.33</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>3.11</v>
+        <v>1.14</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>32.1</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>39.1</v>
+        <v>16.9</v>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
@@ -942,49 +930,49 @@
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>04:34</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>✅ Nishesh Basavareddy</t>
+          <t>✅ Ann Li</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Andres Andrade</t>
+          <t>Leylah Fernandez</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Savannah, USA Men Singles</t>
+          <t>WTA - WTA Madrid, Spain Women Singles</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>CLAY</t>
         </is>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.7</v>
+        <v>2.37</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>1.27</v>
+        <v>2.03</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>78.8</v>
+        <v>49.3</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>33.9</v>
+        <v>16.8</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>TA-hard</t>
+          <t>TA-clay</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -998,27 +986,27 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>04:34</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>✅ Sofia Kenin</t>
+          <t>✅ Marco Cecchinato</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Qinwen Zheng</t>
+          <t>Daniel Michalski</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>WTA - WTA Madrid, Spain Women Singles</t>
+          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -1027,16 +1015,16 @@
         </is>
       </c>
       <c r="G9" s="8" t="n">
-        <v>4.33</v>
+        <v>1.57</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>3.31</v>
+        <v>1.35</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>30.2</v>
+        <v>74.3</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>30.9</v>
+        <v>16.6</v>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
@@ -1054,27 +1042,27 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>04:34</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>✅ Yulia Putintseva</t>
+          <t>✅ Karen Khachanov</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Marta Kostyuk</t>
+          <t>Jakub Mensik</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>WTA - WTA Madrid, Spain Women Singles</t>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1083,16 +1071,16 @@
         </is>
       </c>
       <c r="G10" s="4" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>3.07</v>
+        <v>2</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>32.5</v>
+        <v>49.9</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>30.1</v>
+        <v>14.7</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
@@ -1110,49 +1098,49 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>04:34</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>✅ Cameron Norrie</t>
+          <t>✅ Hayato Matsuoka</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Tomas Machac</t>
+          <t>Omar Jasika</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>ATP - ATP Madrid, Spain Men Singles</t>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>CLAY</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="G11" s="8" t="n">
-        <v>2.12</v>
+        <v>1.66</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>60.1</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>27.4</v>
+        <v>14.7</v>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>TA-clay</t>
+          <t>TA-hard</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -1166,27 +1154,27 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>04:34</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>✅ Andrea Vavassori</t>
+          <t>✅ Tom Gentzsch</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Pol Martin Tiffon</t>
+          <t>George Loffhagen</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Rome, Italy Men Singles</t>
+          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1195,16 +1183,16 @@
         </is>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>24.6</v>
+        <v>11.3</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
@@ -1222,49 +1210,49 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>04:34</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>✅ Linda Klimovicova</t>
+          <t>✅ Karolina Pliskova</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Yue Yuan</t>
+          <t>Solana Sierra</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>WTA 125K - WTA 125K Oeiras 4, Portugal Women Singles</t>
+          <t>WTA - WTA Madrid, Spain Women Singles</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>CLAY</t>
         </is>
       </c>
       <c r="G13" s="8" t="n">
-        <v>2.75</v>
+        <v>1.58</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>2.24</v>
+        <v>1.44</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>44.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>22.9</v>
+        <v>10</v>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>TA-hard</t>
+          <t>TA-clay</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -1278,49 +1266,49 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>04:34</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>✅ Yuta Shimizu</t>
+          <t>✅ Flavio Cobolli</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>August Holmgren</t>
+          <t>Adolfo Daniel Vallejo</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Gwangju, Korea Republic Men Singles</t>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>CLAY</t>
         </is>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.75</v>
+        <v>1.53</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="J14" s="10" t="n">
-        <v>19.5</v>
+        <v>71.7</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>TA-hard</t>
+          <t>TA-clay</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1334,27 +1322,27 @@
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>04:34</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>✅ Leolia Jeanjean</t>
+          <t>✅ Luciano Darderi</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Coco Gauff</t>
+          <t>Francisco Cerundolo</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>WTA - WTA Madrid, Spain Women Singles</t>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1363,16 +1351,16 @@
         </is>
       </c>
       <c r="G15" s="8" t="n">
-        <v>17</v>
+        <v>2.77</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>14.45</v>
+        <v>2.56</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J15" s="10" t="n">
-        <v>17.6</v>
+        <v>39</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
@@ -1390,22 +1378,22 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>04:34</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>✅ Lorenzo Musetti</t>
+          <t>✅ Alexander Zverev</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Hubert Hurkacz</t>
+          <t>Terence Atmane</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1419,16 +1407,16 @@
         </is>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.54</v>
+        <v>1.17</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="J16" s="10" t="n">
-        <v>17.3</v>
+        <v>90.09999999999999</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>5.4</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
@@ -1442,790 +1430,6 @@
       </c>
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>03:15</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>✅ Tommy Paul</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Thiago Agustin Tirante</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>ATP - ATP Madrid, Spain Men Singles</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I17" s="7" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="J17" s="10" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="K17" s="7" t="inlineStr">
-        <is>
-          <t>TA-clay</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M17" s="7" t="inlineStr"/>
-      <c r="N17" s="7" t="inlineStr"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>03:15</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>✅ Katie Boulter</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Jessica Pegula</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>WTA - WTA Madrid, Spain Women Singles</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="J18" s="10" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>TA-clay</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>03:15</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>✅ Gabriel Diallo</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Elmer Moller</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>ATP - ATP Madrid, Spain Men Singles</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="I19" s="7" t="n">
-        <v>70.7</v>
-      </c>
-      <c r="J19" s="10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>TA-clay</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M19" s="7" t="inlineStr"/>
-      <c r="N19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>03:15</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>✅ Fiona Ferro</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Elena Pridankina</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>WTA 125K - WTA 125K Oeiras 4, Portugal Women Singles</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="J20" s="10" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>TA-hard</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>03:15</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>✅ Cristina Bucsa</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Zeynep Sonmez</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>WTA - WTA Madrid, Spain Women Singles</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="I21" s="7" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="J21" s="10" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>TA-clay</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M21" s="7" t="inlineStr"/>
-      <c r="N21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>03:15</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>✅ Arthur Rinderknech</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Dusan Lajovic</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>ATP - ATP Madrid, Spain Men Singles</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>69.3</v>
-      </c>
-      <c r="J22" s="10" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>TA-clay</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
-      <c r="N22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>03:15</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>✅ Sorana Cirstea</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Tyra Caterina Grant</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>WTA - WTA Madrid, Spain Women Singles</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="I23" s="7" t="n">
-        <v>87.7</v>
-      </c>
-      <c r="J23" s="10" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="K23" s="7" t="inlineStr">
-        <is>
-          <t>TA-clay</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M23" s="7" t="inlineStr"/>
-      <c r="N23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>03:15</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>✅ Jelena Ostapenko</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Simona Waltert</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>WTA - WTA Madrid, Spain Women Singles</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="J24" s="10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>TA-clay</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
-      <c r="N24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>03:15</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>✅ Ben Shelton</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>Dino Prizmic</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>ATP - ATP Madrid, Spain Men Singles</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="I25" s="7" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="J25" s="10" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="K25" s="7" t="inlineStr">
-        <is>
-          <t>TA-clay</t>
-        </is>
-      </c>
-      <c r="L25" s="7" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M25" s="7" t="inlineStr"/>
-      <c r="N25" s="7" t="inlineStr"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>03:15</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>✅ Elise Mertens</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Alexandra Eala</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>WTA - WTA Madrid, Spain Women Singles</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="J26" s="2" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>TA-clay</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>03:15</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>✅ Tomas Martin Etcheverry</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>Sebastian Ofner</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>ATP - ATP Madrid, Spain Men Singles</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I27" s="7" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J27" s="7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="K27" s="7" t="inlineStr">
-        <is>
-          <t>TA-clay</t>
-        </is>
-      </c>
-      <c r="L27" s="7" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M27" s="7" t="inlineStr"/>
-      <c r="N27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>03:15</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>✅ Alex Michelsen</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Jan-Lennard Struff</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>ATP - ATP Madrid, Spain Men Singles</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="J28" s="2" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>TA-clay</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>03:15</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>✅ Yu Hsiou Hsu</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Tristan Schoolkate</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Gwangju, Korea Republic Men Singles</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="I29" s="7" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="J29" s="7" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="K29" s="7" t="inlineStr">
-        <is>
-          <t>TA-hard</t>
-        </is>
-      </c>
-      <c r="L29" s="7" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M29" s="7" t="inlineStr"/>
-      <c r="N29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03:15</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>✅ Lucia Bronzetti</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Polina Kudermetova</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>WTA 125K - WTA 125K Oeiras 4, Portugal Women Singles</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>TA-hard</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/value_bets_log.xlsx
+++ b/data/value_bets_log.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,8 +44,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -87,6 +91,11 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -106,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -133,6 +142,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -500,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1431,6 +1443,2022 @@
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr"/>
     </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>✅ Cameron Norrie</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Jannik Sinner</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>9.24</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J17" s="10" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>✅ Marko ToPo</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Martin Krumich</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr"/>
+      <c r="N18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>✅ Bernard Tomic</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Marat Sharipov</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="J19" s="10" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>TA-hard</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>✅ Hayato Matsuoka</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Keegan Smith</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>TA-hard</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr"/>
+      <c r="N20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>✅ Pierre-Hugues Herbert</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Pol Martin Tiffon</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>✅ Chun Hsin Tseng</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Lukas Neumayer</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M22" s="7" t="inlineStr"/>
+      <c r="N22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>✅ Viktor Durasovic</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Buvaysar Gadamauri</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Shymkent II, Kazakhstan Men Singles</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>✅ Rio Noguchi</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Yu Hsiou Hsu</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>TA-hard</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M24" s="7" t="inlineStr"/>
+      <c r="N24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>✅ Stefanos Tsitsipas</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Casper Ruud</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>✅ Ioannis Xilas</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Michael Geerts</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="J26" s="6" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L26" s="7" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M26" s="7" t="inlineStr"/>
+      <c r="N26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>✅ Thomas Faurel</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Inaki Montes-de la Torre</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>✅ Vit Kopriva</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Rafael Jodar</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="J28" s="6" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M28" s="7" t="inlineStr"/>
+      <c r="N28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>✅ Jaime Faria</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Andrea Guerrieri</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>✅ Sho Shimabukuro</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Yuta Shimizu</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>TA-hard</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M30" s="7" t="inlineStr"/>
+      <c r="N30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>✅ Frederico Ferreira Silva</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Carlos Sanchez Jover</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>✅ Luka Pavlovic</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Vitaliy Sachko</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M32" s="7" t="inlineStr"/>
+      <c r="N32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>✅ Dalibor Svrcina</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Felix Gill</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>✅ Mirra Andreeva</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Leylah Fernandez</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>WTA - WTA Madrid, Spain Women Singles</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="K34" s="7" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M34" s="7" t="inlineStr"/>
+      <c r="N34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>✅ Tom Paris</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Sascha Gueymard Wayenburg</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>✅ Matteo Berrettini</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>Patrick Kypson</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="K36" s="7" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L36" s="7" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M36" s="7" t="inlineStr"/>
+      <c r="N36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>✅ Alexander Zverev</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Jakub Mensik</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>✅ Lorenzo Musetti</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>Jiri Lehecka</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L38" s="7" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M38" s="7" t="inlineStr"/>
+      <c r="N38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>✅ Zdenek Kolar</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Filip Cristian Jianu</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>✅ Daniil Medvedev</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Flavio Cobolli</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M40" s="7" t="inlineStr"/>
+      <c r="N40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>✅ Nikoloz Basilashvili</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Sandro Kopp</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>✅ Stefanos Sakellaridis</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Enrico Dalla Valle</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I42" s="7" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M42" s="7" t="inlineStr"/>
+      <c r="N42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>✅ Adam Walton</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Jie Cui</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>TA-hard</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>✅ Toby Samuel</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Raul Brancaccio</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="J44" s="7" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K44" s="7" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M44" s="7" t="inlineStr"/>
+      <c r="N44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>✅ Mikhail Kukushkin</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Coleman Wong</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>TA-hard</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>✅ Kimmer Coppejans</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Matteo Martineau</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="J46" s="7" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M46" s="7" t="inlineStr"/>
+      <c r="N46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>✅ Tomas Martin Etcheverry</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Arthur Fils</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>✅ Fajing Sun</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Tristan Schoolkate</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="J48" s="7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>TA-hard</t>
+        </is>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M48" s="7" t="inlineStr"/>
+      <c r="N48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>04:32</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>✅ Norbert Gombos</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Thiago Seyboth Wild</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>✅ Ioannis Xilas</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Michael Geerts</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="J50" s="6" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>✅ Alexander Zverev</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Jakub Mensik</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I51" s="7" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="K51" s="7" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="inlineStr"/>
+      <c r="N51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>✅ Daniil Medvedev</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Flavio Cobolli</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/value_bets_log.xlsx
+++ b/data/value_bets_log.xlsx
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N52"/>
+  <dimension ref="A1:N62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3459,6 +3459,566 @@
       <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr"/>
     </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>✅ Ioannis Xilas</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Michael Geerts</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="J53" s="10" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>✅ Alexander Zverev</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Jakub Mensik</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G54" s="8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="K54" s="7" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M54" s="7" t="inlineStr"/>
+      <c r="N54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>✅ Daniil Medvedev</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Flavio Cobolli</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>✅ Zachary Svajda</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>Hubert Hurkacz</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G56" s="8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="J56" s="7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K56" s="7" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M56" s="7" t="inlineStr"/>
+      <c r="N56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>✅ Cristian Garin</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Moez Echargui</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>✅ Michael Mmoh</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>Andrew Fenty</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="J58" s="7" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="K58" s="7" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M58" s="7" t="inlineStr"/>
+      <c r="N58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>✅ Aryna Sabalenka</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Hailey Baptiste</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>WTA - WTA Madrid, Spain Women Singles</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>93.3</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>✅ Ioannis Xilas</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Michael Geerts</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="J60" s="6" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>✅ Alexander Zverev</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Jakub Mensik</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I61" s="7" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="J61" s="9" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M61" s="7" t="inlineStr"/>
+      <c r="N61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>✅ Daniil Medvedev</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Flavio Cobolli</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/value_bets_log.xlsx
+++ b/data/value_bets_log.xlsx
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:N65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4019,6 +4019,174 @@
       <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr"/>
     </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>✅ Ioannis Xilas</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Michael Geerts</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>✅ Alexander Zverev</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Jakub Mensik</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G64" s="8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I64" s="7" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M64" s="7" t="inlineStr"/>
+      <c r="N64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>✅ Daniil Medvedev</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Flavio Cobolli</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>TA-clay</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/value_bets_log.xlsx
+++ b/data/value_bets_log.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,8 +30,22 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <i val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +72,46 @@
         <fgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -77,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +143,36 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -565,6 +649,921 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>✅ Hamish Stewart</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Blaise Bicknell</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H2" s="8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I2" s="5" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="J2" s="9" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M2" s="7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N2" s="10" t="inlineStr"/>
+      <c r="O2" s="11" t="inlineStr"/>
+      <c r="P2" s="5" t="inlineStr"/>
+      <c r="Q2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>✅ Marcelo Tomas Barrios Vera</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>Lukas Neumayer</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I3" s="12" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M3" s="13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N3" s="10" t="inlineStr"/>
+      <c r="O3" s="11" t="inlineStr"/>
+      <c r="P3" s="12" t="inlineStr"/>
+      <c r="Q3" s="12" t="inlineStr"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>✅ David Goffin</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Thomas Faurel</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="N4" s="10" t="inlineStr"/>
+      <c r="O4" s="11" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>✅ Adrian Mannarino</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Jesper De Jong</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="I5" s="12" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M5" s="13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N5" s="10" t="inlineStr"/>
+      <c r="O5" s="11" t="inlineStr"/>
+      <c r="P5" s="12" t="inlineStr"/>
+      <c r="Q5" s="12" t="inlineStr"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>✅ David Jorda Sanchis</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Sandro Kopp</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="N6" s="10" t="inlineStr"/>
+      <c r="O6" s="11" t="inlineStr"/>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>✅ Rudolf Molleker</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Henri Squire</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I7" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="K7" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="N7" s="10" t="inlineStr"/>
+      <c r="O7" s="11" t="inlineStr"/>
+      <c r="P7" s="12" t="inlineStr"/>
+      <c r="Q7" s="12" t="inlineStr"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>✅ Jonas Forejtek</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Zdenek Kolar</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" s="10" t="inlineStr"/>
+      <c r="O8" s="11" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>✅ Arthur Fils</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Jiri Lehecka</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="K9" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L9" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="N9" s="10" t="inlineStr"/>
+      <c r="O9" s="11" t="inlineStr"/>
+      <c r="P9" s="12" t="inlineStr"/>
+      <c r="Q9" s="12" t="inlineStr"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>✅ Jaime Faria</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Martin Krumich</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N10" s="10" t="inlineStr"/>
+      <c r="O10" s="11" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>✅ Damir Dzumhur</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Emilio Nava</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="K11" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N11" s="10" t="inlineStr"/>
+      <c r="O11" s="11" t="inlineStr"/>
+      <c r="P11" s="12" t="inlineStr"/>
+      <c r="Q11" s="12" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>✅ Mert Alkaya</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Paul Jubb</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N12" s="10" t="inlineStr"/>
+      <c r="O12" s="11" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>✅ Lorenzo Sonego</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Mattia Bellucci</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I13" s="12" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="K13" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L13" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="N13" s="10" t="inlineStr"/>
+      <c r="O13" s="11" t="inlineStr"/>
+      <c r="P13" s="12" t="inlineStr"/>
+      <c r="Q13" s="12" t="inlineStr"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>✅ Vitaliy Sachko</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Nikolas Sanchez Izquierdo</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="N14" s="10" t="inlineStr"/>
+      <c r="O14" s="11" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>✅ Mirra Andreeva</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Hailey Baptiste</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Madrid, Spain Women Singles</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="K15" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="L15" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N15" s="10" t="inlineStr"/>
+      <c r="O15" s="11" t="inlineStr"/>
+      <c r="P15" s="12" t="inlineStr"/>
+      <c r="Q15" s="12" t="inlineStr"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>✅ Adam Walton</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Jie Cui</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="N16" s="10" t="inlineStr"/>
+      <c r="O16" s="11" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/value_bets_log.xlsx
+++ b/data/value_bets_log.xlsx
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1564,6 +1564,1714 @@
       <c r="P16" s="5" t="inlineStr"/>
       <c r="Q16" s="5" t="inlineStr"/>
     </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>✅ David Goffin</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Thomas Faurel</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="N17" s="10" t="inlineStr"/>
+      <c r="O17" s="11" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>✅ Adrian Mannarino</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Jesper De Jong</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L18" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N18" s="10" t="inlineStr"/>
+      <c r="O18" s="11" t="inlineStr"/>
+      <c r="P18" s="12" t="inlineStr"/>
+      <c r="Q18" s="12" t="inlineStr"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>✅ David Jorda Sanchis</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Sandro Kopp</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="N19" s="10" t="inlineStr"/>
+      <c r="O19" s="11" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>✅ Rudolf Molleker</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Henri Squire</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="K20" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L20" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="N20" s="10" t="inlineStr"/>
+      <c r="O20" s="11" t="inlineStr"/>
+      <c r="P20" s="12" t="inlineStr"/>
+      <c r="Q20" s="12" t="inlineStr"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>✅ Jonas Forejtek</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Zdenek Kolar</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" s="10" t="inlineStr"/>
+      <c r="O21" s="11" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>✅ Arthur Fils</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Jiri Lehecka</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="J22" s="14" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L22" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="N22" s="10" t="inlineStr"/>
+      <c r="O22" s="11" t="inlineStr"/>
+      <c r="P22" s="12" t="inlineStr"/>
+      <c r="Q22" s="12" t="inlineStr"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>✅ Jaime Faria</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Martin Krumich</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="J23" s="14" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N23" s="10" t="inlineStr"/>
+      <c r="O23" s="11" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>✅ Damir Dzumhur</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Emilio Nava</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="J24" s="14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="K24" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L24" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N24" s="10" t="inlineStr"/>
+      <c r="O24" s="11" t="inlineStr"/>
+      <c r="P24" s="12" t="inlineStr"/>
+      <c r="Q24" s="12" t="inlineStr"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>✅ Mert Alkaya</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Paul Jubb</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="J25" s="14" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N25" s="10" t="inlineStr"/>
+      <c r="O25" s="11" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>✅ Lorenzo Sonego</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>Mattia Bellucci</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="J26" s="14" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="K26" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L26" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="N26" s="10" t="inlineStr"/>
+      <c r="O26" s="11" t="inlineStr"/>
+      <c r="P26" s="12" t="inlineStr"/>
+      <c r="Q26" s="12" t="inlineStr"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>✅ Vitaliy Sachko</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Nikolas Sanchez Izquierdo</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="N27" s="10" t="inlineStr"/>
+      <c r="O27" s="11" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>✅ Mirra Andreeva</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>Hailey Baptiste</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Madrid, Spain Women Singles</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="J28" s="12" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="K28" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="L28" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N28" s="10" t="inlineStr"/>
+      <c r="O28" s="11" t="inlineStr"/>
+      <c r="P28" s="12" t="inlineStr"/>
+      <c r="Q28" s="12" t="inlineStr"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>✅ Adam Walton</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Jie Cui</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="N29" s="10" t="inlineStr"/>
+      <c r="O29" s="11" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>✅ Hamish Stewart</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Blaise Bicknell</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="J30" s="12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K30" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L30" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M30" s="13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="N30" s="10" t="inlineStr"/>
+      <c r="O30" s="11" t="inlineStr"/>
+      <c r="P30" s="12" t="inlineStr"/>
+      <c r="Q30" s="12" t="inlineStr"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>✅ David Goffin</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Thomas Faurel</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M31" s="7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="N31" s="10" t="inlineStr"/>
+      <c r="O31" s="11" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>✅ Adrian Mannarino</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>Jesper De Jong</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="K32" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L32" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M32" s="13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N32" s="10" t="inlineStr"/>
+      <c r="O32" s="11" t="inlineStr"/>
+      <c r="P32" s="12" t="inlineStr"/>
+      <c r="Q32" s="12" t="inlineStr"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>✅ David Jorda Sanchis</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Sandro Kopp</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M33" s="7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="N33" s="10" t="inlineStr"/>
+      <c r="O33" s="11" t="inlineStr"/>
+      <c r="P33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>✅ Rudolf Molleker</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>Henri Squire</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="K34" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L34" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="N34" s="10" t="inlineStr"/>
+      <c r="O34" s="11" t="inlineStr"/>
+      <c r="P34" s="12" t="inlineStr"/>
+      <c r="Q34" s="12" t="inlineStr"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>✅ Jonas Forejtek</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Zdenek Kolar</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="J35" s="14" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M35" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N35" s="10" t="inlineStr"/>
+      <c r="O35" s="11" t="inlineStr"/>
+      <c r="P35" s="5" t="inlineStr"/>
+      <c r="Q35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>✅ Arthur Fils</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>Jiri Lehecka</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="J36" s="14" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="K36" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L36" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M36" s="13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="N36" s="10" t="inlineStr"/>
+      <c r="O36" s="11" t="inlineStr"/>
+      <c r="P36" s="12" t="inlineStr"/>
+      <c r="Q36" s="12" t="inlineStr"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>✅ Jaime Faria</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Martin Krumich</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="J37" s="14" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M37" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N37" s="10" t="inlineStr"/>
+      <c r="O37" s="11" t="inlineStr"/>
+      <c r="P37" s="5" t="inlineStr"/>
+      <c r="Q37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>✅ Damir Dzumhur</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>Emilio Nava</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I38" s="12" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="J38" s="14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="K38" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L38" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M38" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N38" s="10" t="inlineStr"/>
+      <c r="O38" s="11" t="inlineStr"/>
+      <c r="P38" s="12" t="inlineStr"/>
+      <c r="Q38" s="12" t="inlineStr"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>✅ Mert Alkaya</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Paul Jubb</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="J39" s="14" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M39" s="7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N39" s="10" t="inlineStr"/>
+      <c r="O39" s="11" t="inlineStr"/>
+      <c r="P39" s="5" t="inlineStr"/>
+      <c r="Q39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>✅ Lorenzo Sonego</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>Mattia Bellucci</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I40" s="12" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="J40" s="14" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="K40" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L40" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M40" s="13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="N40" s="10" t="inlineStr"/>
+      <c r="O40" s="11" t="inlineStr"/>
+      <c r="P40" s="12" t="inlineStr"/>
+      <c r="Q40" s="12" t="inlineStr"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>✅ Vitaliy Sachko</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Nikolas Sanchez Izquierdo</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M41" s="7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="N41" s="10" t="inlineStr"/>
+      <c r="O41" s="11" t="inlineStr"/>
+      <c r="P41" s="5" t="inlineStr"/>
+      <c r="Q41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>✅ Mirra Andreeva</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>Hailey Baptiste</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Madrid, Spain Women Singles</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G42" s="13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I42" s="12" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="J42" s="12" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="K42" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="L42" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M42" s="13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N42" s="10" t="inlineStr"/>
+      <c r="O42" s="11" t="inlineStr"/>
+      <c r="P42" s="12" t="inlineStr"/>
+      <c r="Q42" s="12" t="inlineStr"/>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>✅ Adam Walton</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Jie Cui</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M43" s="7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="N43" s="10" t="inlineStr"/>
+      <c r="O43" s="11" t="inlineStr"/>
+      <c r="P43" s="5" t="inlineStr"/>
+      <c r="Q43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>✅ Hamish Stewart</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>Blaise Bicknell</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
+        </is>
+      </c>
+      <c r="F44" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G44" s="13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I44" s="12" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="J44" s="12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K44" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L44" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M44" s="13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="N44" s="10" t="inlineStr"/>
+      <c r="O44" s="11" t="inlineStr"/>
+      <c r="P44" s="12" t="inlineStr"/>
+      <c r="Q44" s="12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/value_bets_log.xlsx
+++ b/data/value_bets_log.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Value Bets Log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Handicap Bets" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45,7 +46,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -112,6 +113,11 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E4E79"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -131,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -173,6 +179,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3275,4 +3284,106 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>Ora</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="inlineStr">
+        <is>
+          <t>Punta su (handicap)</t>
+        </is>
+      </c>
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>Avversario</t>
+        </is>
+      </c>
+      <c r="E1" s="15" t="inlineStr">
+        <is>
+          <t>Handicap</t>
+        </is>
+      </c>
+      <c r="F1" s="15" t="inlineStr">
+        <is>
+          <t>Quota</t>
+        </is>
+      </c>
+      <c r="G1" s="15" t="inlineStr">
+        <is>
+          <t>Prob %</t>
+        </is>
+      </c>
+      <c r="H1" s="15" t="inlineStr">
+        <is>
+          <t>EV %</t>
+        </is>
+      </c>
+      <c r="I1" s="15" t="inlineStr">
+        <is>
+          <t>Torneo</t>
+        </is>
+      </c>
+      <c r="J1" s="15" t="inlineStr">
+        <is>
+          <t>Superficie</t>
+        </is>
+      </c>
+      <c r="K1" s="15" t="inlineStr">
+        <is>
+          <t>Elo Diff</t>
+        </is>
+      </c>
+      <c r="L1" s="15" t="inlineStr">
+        <is>
+          <t>Margine Atteso</t>
+        </is>
+      </c>
+      <c r="M1" s="15" t="inlineStr">
+        <is>
+          <t>Elo Usato</t>
+        </is>
+      </c>
+      <c r="N1" s="15" t="inlineStr">
+        <is>
+          <t>Fonte</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/value_bets_log.xlsx
+++ b/data/value_bets_log.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -118,6 +122,16 @@
         <fgColor rgb="001E4E79"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEEFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FF0000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -137,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -182,6 +196,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -549,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q44"/>
+  <dimension ref="A1:Q63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -838,8 +861,14 @@
       </c>
       <c r="N4" s="10" t="inlineStr"/>
       <c r="O4" s="11" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
@@ -1021,8 +1050,14 @@
       </c>
       <c r="N7" s="10" t="inlineStr"/>
       <c r="O7" s="11" t="inlineStr"/>
-      <c r="P7" s="12" t="inlineStr"/>
-      <c r="Q7" s="12" t="inlineStr"/>
+      <c r="P7" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q7" s="12" t="n">
+        <v>1.52</v>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -1143,8 +1178,14 @@
       </c>
       <c r="N9" s="10" t="inlineStr"/>
       <c r="O9" s="11" t="inlineStr"/>
-      <c r="P9" s="12" t="inlineStr"/>
-      <c r="Q9" s="12" t="inlineStr"/>
+      <c r="P9" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q9" s="12" t="n">
+        <v>0.57</v>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -1265,8 +1306,14 @@
       </c>
       <c r="N11" s="10" t="inlineStr"/>
       <c r="O11" s="11" t="inlineStr"/>
-      <c r="P11" s="12" t="inlineStr"/>
-      <c r="Q11" s="12" t="inlineStr"/>
+      <c r="P11" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q11" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -1326,8 +1373,14 @@
       </c>
       <c r="N12" s="10" t="inlineStr"/>
       <c r="O12" s="11" t="inlineStr"/>
-      <c r="P12" s="5" t="inlineStr"/>
-      <c r="Q12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>1.1</v>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
@@ -1387,8 +1440,14 @@
       </c>
       <c r="N13" s="10" t="inlineStr"/>
       <c r="O13" s="11" t="inlineStr"/>
-      <c r="P13" s="12" t="inlineStr"/>
-      <c r="Q13" s="12" t="inlineStr"/>
+      <c r="P13" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q13" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
@@ -1570,8 +1629,14 @@
       </c>
       <c r="N16" s="10" t="inlineStr"/>
       <c r="O16" s="11" t="inlineStr"/>
-      <c r="P16" s="5" t="inlineStr"/>
-      <c r="Q16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q16" s="5" t="n">
+        <v>0.27</v>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="5" t="inlineStr">
@@ -3280,6 +3345,1165 @@
       <c r="O44" s="11" t="inlineStr"/>
       <c r="P44" s="12" t="inlineStr"/>
       <c r="Q44" s="12" t="inlineStr"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>✅ Alexander Binda</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Manas Dhamne</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Shymkent II, Kazakhstan Men Singles</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="J45" s="18" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M45" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N45" s="10" t="inlineStr"/>
+      <c r="O45" s="11" t="inlineStr"/>
+      <c r="P45" s="5" t="inlineStr"/>
+      <c r="Q45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>✅ Kimmer Coppejans</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>Pol Martin Tiffon</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" s="8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I46" s="12" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="K46" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="L46" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M46" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N46" s="10" t="inlineStr"/>
+      <c r="O46" s="11" t="inlineStr"/>
+      <c r="P46" s="12" t="inlineStr"/>
+      <c r="Q46" s="12" t="inlineStr"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>✅ Rinky Hijikata</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Zizou Bergs</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="I47" s="5" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M47" s="7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N47" s="10" t="inlineStr"/>
+      <c r="O47" s="11" t="inlineStr"/>
+      <c r="P47" s="5" t="inlineStr"/>
+      <c r="Q47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>✅ Laslo Djere</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>Lukas Neumayer</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
+        </is>
+      </c>
+      <c r="F48" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G48" s="13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H48" s="8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I48" s="12" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="K48" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="L48" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M48" s="13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="N48" s="10" t="inlineStr"/>
+      <c r="O48" s="11" t="inlineStr"/>
+      <c r="P48" s="12" t="inlineStr"/>
+      <c r="Q48" s="12" t="inlineStr"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>✅ Alex Bolt</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Keegan Smith</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M49" s="7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="N49" s="10" t="inlineStr"/>
+      <c r="O49" s="11" t="inlineStr"/>
+      <c r="P49" s="5" t="inlineStr"/>
+      <c r="Q49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>✅ Marcos Giron</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>Roman Andres Burruchaga</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F50" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G50" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H50" s="8" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I50" s="12" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="K50" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L50" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M50" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N50" s="10" t="inlineStr"/>
+      <c r="O50" s="11" t="inlineStr"/>
+      <c r="P50" s="12" t="inlineStr"/>
+      <c r="Q50" s="12" t="inlineStr"/>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>✅ Matteo Arnaldi</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Nuno Borges</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M51" s="7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N51" s="10" t="inlineStr"/>
+      <c r="O51" s="11" t="inlineStr"/>
+      <c r="P51" s="5" t="inlineStr"/>
+      <c r="Q51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>✅ Mert Alkaya</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>Gauthier Onclin</t>
+        </is>
+      </c>
+      <c r="E52" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G52" s="13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H52" s="8" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I52" s="12" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="J52" s="14" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="K52" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="L52" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M52" s="13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N52" s="10" t="inlineStr"/>
+      <c r="O52" s="11" t="inlineStr"/>
+      <c r="P52" s="12" t="inlineStr"/>
+      <c r="Q52" s="12" t="inlineStr"/>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>✅ Hamish Stewart</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>Eliakim Coulibaly</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H53" s="8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="J53" s="14" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M53" s="7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="N53" s="10" t="inlineStr"/>
+      <c r="O53" s="11" t="inlineStr"/>
+      <c r="P53" s="5" t="inlineStr"/>
+      <c r="Q53" s="5" t="inlineStr"/>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>✅ Mili Poljicak</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>Buvaysar Gadamauri</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Shymkent II, Kazakhstan Men Singles</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G54" s="13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H54" s="8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I54" s="12" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="J54" s="14" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="K54" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L54" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M54" s="13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="N54" s="10" t="inlineStr"/>
+      <c r="O54" s="11" t="inlineStr"/>
+      <c r="P54" s="12" t="inlineStr"/>
+      <c r="Q54" s="12" t="inlineStr"/>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>✅ Antoine Ghibaudo</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>Andrej Nedic</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Shymkent II, Kazakhstan Men Singles</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H55" s="8" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="I55" s="5" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="J55" s="14" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M55" s="7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N55" s="10" t="inlineStr"/>
+      <c r="O55" s="11" t="inlineStr"/>
+      <c r="P55" s="5" t="inlineStr"/>
+      <c r="Q55" s="5" t="inlineStr"/>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>✅ Arthur Fils</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>Jannik Sinner</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G56" s="13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H56" s="8" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="I56" s="12" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="J56" s="14" t="n">
+        <v>14</v>
+      </c>
+      <c r="K56" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="L56" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M56" s="13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N56" s="10" t="inlineStr"/>
+      <c r="O56" s="11" t="inlineStr"/>
+      <c r="P56" s="12" t="inlineStr"/>
+      <c r="Q56" s="12" t="inlineStr"/>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>✅ Yibing Wu</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Ethan Quinn</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H57" s="8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="J57" s="14" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M57" s="7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N57" s="10" t="inlineStr"/>
+      <c r="O57" s="11" t="inlineStr"/>
+      <c r="P57" s="5" t="inlineStr"/>
+      <c r="Q57" s="5" t="inlineStr"/>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>✅ Fajing Sun</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>Mark Lajal</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G58" s="13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H58" s="8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="I58" s="12" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="J58" s="14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="K58" s="12" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L58" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M58" s="13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N58" s="10" t="inlineStr"/>
+      <c r="O58" s="11" t="inlineStr"/>
+      <c r="P58" s="12" t="inlineStr"/>
+      <c r="Q58" s="12" t="inlineStr"/>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>✅ Jesper De Jong</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Gianluca Cadenasso</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H59" s="8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M59" s="7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="N59" s="10" t="inlineStr"/>
+      <c r="O59" s="11" t="inlineStr"/>
+      <c r="P59" s="5" t="inlineStr"/>
+      <c r="Q59" s="5" t="inlineStr"/>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>✅ Jaime Faria</t>
+        </is>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>Miguel Damas</t>
+        </is>
+      </c>
+      <c r="E60" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
+        </is>
+      </c>
+      <c r="F60" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G60" s="13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H60" s="8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I60" s="12" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="J60" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K60" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L60" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M60" s="13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="N60" s="10" t="inlineStr"/>
+      <c r="O60" s="11" t="inlineStr"/>
+      <c r="P60" s="12" t="inlineStr"/>
+      <c r="Q60" s="12" t="inlineStr"/>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>✅ Roman Safiullin</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>David Jorda Sanchis</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H61" s="8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="J61" s="5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M61" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N61" s="10" t="inlineStr"/>
+      <c r="O61" s="11" t="inlineStr"/>
+      <c r="P61" s="5" t="inlineStr"/>
+      <c r="Q61" s="5" t="inlineStr"/>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>✅ Alexander Zverev</t>
+        </is>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>Alexander Blockx</t>
+        </is>
+      </c>
+      <c r="E62" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="F62" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G62" s="13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="H62" s="8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I62" s="12" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="J62" s="12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K62" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L62" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="N62" s="10" t="inlineStr"/>
+      <c r="O62" s="11" t="inlineStr"/>
+      <c r="P62" s="12" t="inlineStr"/>
+      <c r="Q62" s="12" t="inlineStr"/>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>02:36</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>✅ Ignacio Buse</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Alejandro Tabilo</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H63" s="8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M63" s="7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N63" s="10" t="inlineStr"/>
+      <c r="O63" s="11" t="inlineStr"/>
+      <c r="P63" s="5" t="inlineStr"/>
+      <c r="Q63" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3292,7 +4516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3383,6 +4607,1566 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>✅ Kimmer Coppejans  +1.5</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="inlineStr">
+        <is>
+          <t>Pol Martin Tiffon</t>
+        </is>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G2" s="16" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="H2" s="18" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="I2" s="16" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
+        </is>
+      </c>
+      <c r="J2" s="16" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K2" s="16" t="n">
+        <v>134</v>
+      </c>
+      <c r="L2" s="16" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="M2" s="16" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="N2" s="16" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>✅ Kimmer Coppejans  +0.5</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>Pol Martin Tiffon</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F3" s="13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="H3" s="18" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
+        </is>
+      </c>
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K3" s="12" t="n">
+        <v>134</v>
+      </c>
+      <c r="L3" s="12" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="M3" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>✅ Fajing Sun  +2.5</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>Mark Lajal</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="I4" s="16" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
+        </is>
+      </c>
+      <c r="J4" s="16" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="K4" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="L4" s="16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M4" s="16" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="N4" s="16" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>✅ Mert Alkaya  +3.5</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Gauthier Onclin</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="L5" s="12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M5" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>✅ Matteo Arnaldi  +1.5</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>Nuno Borges</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K6" s="16" t="n">
+        <v>54</v>
+      </c>
+      <c r="L6" s="16" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M6" s="16" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="N6" s="16" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>✅ Rinky Hijikata  +3.5</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Zizou Bergs</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K7" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="L7" s="12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M7" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="N7" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>✅ Alex Bolt  -2.5</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Keegan Smith</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="K8" s="16" t="n">
+        <v>290</v>
+      </c>
+      <c r="L8" s="16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M8" s="16" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="N8" s="16" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>✅ Laslo Djere  -1.5</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Lukas Neumayer</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K9" s="12" t="n">
+        <v>184</v>
+      </c>
+      <c r="L9" s="12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M9" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="N9" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>✅ Alexis Galarneau  +2.5</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>Adam Walton</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="K10" s="16" t="n">
+        <v>64</v>
+      </c>
+      <c r="L10" s="16" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="M10" s="16" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="N10" s="16" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>✅ Raul Brancaccio  +2.5</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Marco Cecchinato</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K11" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="L11" s="12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="M11" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="N11" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>✅ Nerman Fatic  -0.5</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>Zdenek Kolar</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+        </is>
+      </c>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K12" s="16" t="n">
+        <v>104</v>
+      </c>
+      <c r="L12" s="16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M12" s="16" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>✅ Matteo Arnaldi  +0.5</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Nuno Borges</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="J13" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K13" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="L13" s="12" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M13" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="N13" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>✅ Matteo Berrettini  +0.5</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>Hubert Hurkacz</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K14" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="L14" s="16" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="M14" s="16" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="N14" s="16" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>02:37</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>✅ Kimmer Coppejans  +1.5</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>Pol Martin Tiffon</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
+        </is>
+      </c>
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K15" s="16" t="n">
+        <v>134</v>
+      </c>
+      <c r="L15" s="16" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="M15" s="16" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="N15" s="16" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>02:37</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>✅ Kimmer Coppejans  +0.5</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Pol Martin Tiffon</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="H16" s="18" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
+        </is>
+      </c>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>134</v>
+      </c>
+      <c r="L16" s="12" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="M16" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="N16" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>02:37</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>✅ Fajing Sun  +2.5</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>Mark Lajal</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
+        </is>
+      </c>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="K17" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="L17" s="16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M17" s="16" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="N17" s="16" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>02:37</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>✅ Mert Alkaya  +3.5</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Gauthier Onclin</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
+        </is>
+      </c>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K18" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="L18" s="12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M18" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="N18" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>02:37</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>✅ Matteo Arnaldi  +1.5</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>Nuno Borges</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G19" s="16" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K19" s="16" t="n">
+        <v>54</v>
+      </c>
+      <c r="L19" s="16" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M19" s="16" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="N19" s="16" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>02:37</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>✅ Rinky Hijikata  +3.5</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Zizou Bergs</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
+        </is>
+      </c>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K20" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="L20" s="12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M20" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="N20" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>02:37</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>✅ Alex Bolt  -2.5</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>Keegan Smith</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
+        </is>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="K21" s="16" t="n">
+        <v>290</v>
+      </c>
+      <c r="L21" s="16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M21" s="16" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="N21" s="16" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>02:37</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>✅ Laslo Djere  -1.5</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>Lukas Neumayer</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
+        </is>
+      </c>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K22" s="12" t="n">
+        <v>184</v>
+      </c>
+      <c r="L22" s="12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M22" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="N22" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>02:37</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>✅ Alexis Galarneau  +2.5</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>Adam Walton</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G23" s="16" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
+        </is>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="K23" s="16" t="n">
+        <v>64</v>
+      </c>
+      <c r="L23" s="16" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="M23" s="16" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="N23" s="16" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>02:37</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>✅ Raul Brancaccio  +2.5</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Marco Cecchinato</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+        </is>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K24" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="L24" s="12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="M24" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="N24" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>02:37</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>✅ Nerman Fatic  -0.5</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>Zdenek Kolar</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="F25" s="17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G25" s="16" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+        </is>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K25" s="16" t="n">
+        <v>104</v>
+      </c>
+      <c r="L25" s="16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M25" s="16" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="N25" s="16" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>02:37</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>✅ Matteo Arnaldi  +0.5</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>Nuno Borges</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="J26" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K26" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="L26" s="12" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M26" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="N26" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>02:37</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>✅ Matteo Berrettini  +0.5</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>Hubert Hurkacz</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F27" s="17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G27" s="16" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K27" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="L27" s="16" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="M27" s="16" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="N27" s="16" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/value_bets_log.xlsx
+++ b/data/value_bets_log.xlsx
@@ -44,10 +44,10 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="17">
@@ -94,7 +94,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
+        <fgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
     <fill>
@@ -114,6 +114,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
@@ -125,11 +130,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEEFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -192,19 +192,19 @@
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -684,27 +684,27 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>✅ Hamish Stewart</t>
+          <t>✅ Alexander Binda</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Blaise Bicknell</t>
+          <t>Manas Dhamne</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
+          <t>Challenger - ATP Challenger Shymkent II, Kazakhstan Men Singles</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -713,20 +713,20 @@
         </is>
       </c>
       <c r="G2" s="7" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>63.4</v>
+        <v>50.5</v>
       </c>
       <c r="J2" s="9" t="n">
-        <v>36.3</v>
+        <v>51.5</v>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>TA-clay+forma</t>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
         </is>
       </c>
       <c r="L2" s="5" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="M2" s="7" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="N2" s="10" t="inlineStr"/>
       <c r="O2" s="11" t="inlineStr"/>
@@ -745,27 +745,27 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>✅ Marcelo Tomas Barrios Vera</t>
+          <t>✅ Kimmer Coppejans</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Lukas Neumayer</t>
+          <t>Pol Martin Tiffon</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
+          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -774,20 +774,20 @@
         </is>
       </c>
       <c r="G3" s="13" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="I3" s="12" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="J3" s="9" t="n">
-        <v>36.1</v>
+        <v>68.3</v>
+      </c>
+      <c r="J3" s="14" t="n">
+        <v>36.7</v>
       </c>
       <c r="K3" s="12" t="inlineStr">
         <is>
-          <t>TA-clay+forma</t>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="M3" s="13" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="N3" s="10" t="inlineStr"/>
       <c r="O3" s="11" t="inlineStr"/>
@@ -806,22 +806,22 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>✅ David Goffin</t>
+          <t>✅ Rinky Hijikata</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Thomas Faurel</t>
+          <t>Zizou Bergs</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -835,20 +835,20 @@
         </is>
       </c>
       <c r="G4" s="7" t="n">
-        <v>1.61</v>
+        <v>3.4</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>1.29</v>
+        <v>2.59</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="J4" s="9" t="n">
-        <v>24.8</v>
+        <v>38.6</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>31.3</v>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
@@ -857,43 +857,37 @@
         </is>
       </c>
       <c r="M4" s="7" t="n">
-        <v>1.61</v>
+        <v>3.4</v>
       </c>
       <c r="N4" s="10" t="inlineStr"/>
       <c r="O4" s="11" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="Q4" s="5" t="n">
-        <v>-1</v>
-      </c>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>✅ Adrian Mannarino</t>
+          <t>✅ Laslo Djere</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Jesper De Jong</t>
+          <t>Lukas Neumayer</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -902,20 +896,20 @@
         </is>
       </c>
       <c r="G5" s="13" t="n">
-        <v>4.8</v>
+        <v>1.75</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>3.86</v>
+        <v>1.35</v>
       </c>
       <c r="I5" s="12" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>24.3</v>
+        <v>74.3</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>30</v>
       </c>
       <c r="K5" s="12" t="inlineStr">
         <is>
-          <t>TA-clay+forma</t>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
         </is>
       </c>
       <c r="L5" s="12" t="inlineStr">
@@ -924,7 +918,7 @@
         </is>
       </c>
       <c r="M5" s="13" t="n">
-        <v>4.8</v>
+        <v>1.75</v>
       </c>
       <c r="N5" s="10" t="inlineStr"/>
       <c r="O5" s="11" t="inlineStr"/>
@@ -934,49 +928,49 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>✅ David Jorda Sanchis</t>
+          <t>✅ Alex Bolt</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Sandro Kopp</t>
+          <t>Keegan Smith</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>CLAY</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="G6" s="7" t="n">
-        <v>2.25</v>
+        <v>1.47</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>1.84</v>
+        <v>1.19</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>22.5</v>
+        <v>84.2</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>23.7</v>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+          <t>TA-hard+forma+fat(-0.3/-0.3)</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
@@ -985,7 +979,7 @@
         </is>
       </c>
       <c r="M6" s="7" t="n">
-        <v>2.25</v>
+        <v>1.47</v>
       </c>
       <c r="N6" s="10" t="inlineStr"/>
       <c r="O6" s="11" t="inlineStr"/>
@@ -995,27 +989,27 @@
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>✅ Rudolf Molleker</t>
+          <t>✅ Marcos Giron</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Henri Squire</t>
+          <t>Roman Andres Burruchaga</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -1024,20 +1018,20 @@
         </is>
       </c>
       <c r="G7" s="13" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="I7" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="J7" s="9" t="n">
-        <v>20.9</v>
+        <v>49.2</v>
+      </c>
+      <c r="J7" s="14" t="n">
+        <v>23.1</v>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+          <t>TA-clay+forma</t>
         </is>
       </c>
       <c r="L7" s="12" t="inlineStr">
@@ -1046,43 +1040,37 @@
         </is>
       </c>
       <c r="M7" s="13" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="N7" s="10" t="inlineStr"/>
       <c r="O7" s="11" t="inlineStr"/>
-      <c r="P7" s="12" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="Q7" s="12" t="n">
-        <v>1.52</v>
-      </c>
+      <c r="P7" s="12" t="inlineStr"/>
+      <c r="Q7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>✅ Jonas Forejtek</t>
+          <t>✅ Matteo Arnaldi</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Zdenek Kolar</t>
+          <t>Nuno Borges</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -1091,20 +1079,20 @@
         </is>
       </c>
       <c r="G8" s="7" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>58.7</v>
+        <v>57.7</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>17.4</v>
+        <v>21.2</v>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
@@ -1113,7 +1101,7 @@
         </is>
       </c>
       <c r="M8" s="7" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="N8" s="10" t="inlineStr"/>
       <c r="O8" s="11" t="inlineStr"/>
@@ -1123,27 +1111,27 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>✅ Arthur Fils</t>
+          <t>✅ Mert Alkaya</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Jiri Lehecka</t>
+          <t>Gauthier Onclin</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>ATP - ATP Madrid, Spain Men Singles</t>
+          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -1152,20 +1140,20 @@
         </is>
       </c>
       <c r="G9" s="13" t="n">
-        <v>1.57</v>
+        <v>3.25</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>1.36</v>
+        <v>2.72</v>
       </c>
       <c r="I9" s="12" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="J9" s="14" t="n">
-        <v>15.8</v>
+        <v>36.7</v>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>19.3</v>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>TA-clay+forma</t>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
         </is>
       </c>
       <c r="L9" s="12" t="inlineStr">
@@ -1174,43 +1162,37 @@
         </is>
       </c>
       <c r="M9" s="13" t="n">
-        <v>1.57</v>
+        <v>3.25</v>
       </c>
       <c r="N9" s="10" t="inlineStr"/>
       <c r="O9" s="11" t="inlineStr"/>
-      <c r="P9" s="12" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="Q9" s="12" t="n">
-        <v>0.57</v>
-      </c>
+      <c r="P9" s="12" t="inlineStr"/>
+      <c r="Q9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>✅ Jaime Faria</t>
+          <t>✅ Hamish Stewart</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Martin Krumich</t>
+          <t>Eliakim Coulibaly</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
+          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1219,20 +1201,20 @@
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>1.5</v>
+        <v>2.35</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>1.31</v>
+        <v>1.97</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>14.2</v>
+        <v>50.7</v>
+      </c>
+      <c r="J10" s="15" t="n">
+        <v>19.1</v>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+          <t>TA-clay+forma</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
@@ -1241,7 +1223,7 @@
         </is>
       </c>
       <c r="M10" s="7" t="n">
-        <v>1.5</v>
+        <v>2.35</v>
       </c>
       <c r="N10" s="10" t="inlineStr"/>
       <c r="O10" s="11" t="inlineStr"/>
@@ -1251,27 +1233,27 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>✅ Damir Dzumhur</t>
+          <t>✅ Mili Poljicak</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Emilio Nava</t>
+          <t>Buvaysar Gadamauri</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+          <t>Challenger - ATP Challenger Shymkent II, Kazakhstan Men Singles</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -1280,16 +1262,16 @@
         </is>
       </c>
       <c r="G11" s="13" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>2.21</v>
+        <v>1.32</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="J11" s="14" t="n">
-        <v>13.3</v>
+        <v>75.7</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>18.8</v>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
@@ -1302,43 +1284,37 @@
         </is>
       </c>
       <c r="M11" s="13" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="N11" s="10" t="inlineStr"/>
       <c r="O11" s="11" t="inlineStr"/>
-      <c r="P11" s="12" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="Q11" s="12" t="n">
-        <v>-1</v>
-      </c>
+      <c r="P11" s="12" t="inlineStr"/>
+      <c r="Q11" s="12" t="inlineStr"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>✅ Mert Alkaya</t>
+          <t>✅ Antoine Ghibaudo</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Paul Jubb</t>
+          <t>Andrej Nedic</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
+          <t>Challenger - ATP Challenger Shymkent II, Kazakhstan Men Singles</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1347,16 +1323,16 @@
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>1.87</v>
+        <v>2.39</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="J12" s="14" t="n">
-        <v>12.6</v>
+        <v>41.8</v>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>14.9</v>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
@@ -1369,43 +1345,37 @@
         </is>
       </c>
       <c r="M12" s="7" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="N12" s="10" t="inlineStr"/>
       <c r="O12" s="11" t="inlineStr"/>
-      <c r="P12" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="Q12" s="5" t="n">
-        <v>1.1</v>
-      </c>
+      <c r="P12" s="5" t="inlineStr"/>
+      <c r="Q12" s="5" t="inlineStr"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>✅ Lorenzo Sonego</t>
+          <t>✅ Arthur Fils</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Mattia Bellucci</t>
+          <t>Jannik Sinner</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -1414,20 +1384,20 @@
         </is>
       </c>
       <c r="G13" s="13" t="n">
-        <v>1.67</v>
+        <v>5.5</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>1.5</v>
+        <v>4.82</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="J13" s="14" t="n">
-        <v>11.1</v>
+        <v>20.7</v>
+      </c>
+      <c r="J13" s="15" t="n">
+        <v>14</v>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>TA-clay+forma</t>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
@@ -1436,43 +1406,37 @@
         </is>
       </c>
       <c r="M13" s="13" t="n">
-        <v>1.67</v>
+        <v>5.5</v>
       </c>
       <c r="N13" s="10" t="inlineStr"/>
       <c r="O13" s="11" t="inlineStr"/>
-      <c r="P13" s="12" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="Q13" s="12" t="n">
-        <v>-1</v>
-      </c>
+      <c r="P13" s="12" t="inlineStr"/>
+      <c r="Q13" s="12" t="inlineStr"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>✅ Vitaliy Sachko</t>
+          <t>✅ Yibing Wu</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Nikolas Sanchez Izquierdo</t>
+          <t>Ethan Quinn</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1481,16 +1445,16 @@
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="J14" s="5" t="n">
-        <v>9.699999999999999</v>
+        <v>62.4</v>
+      </c>
+      <c r="J14" s="15" t="n">
+        <v>12.4</v>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
@@ -1503,7 +1467,7 @@
         </is>
       </c>
       <c r="M14" s="7" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="N14" s="10" t="inlineStr"/>
       <c r="O14" s="11" t="inlineStr"/>
@@ -1513,49 +1477,49 @@
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>✅ Mirra Andreeva</t>
+          <t>✅ Fajing Sun</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Hailey Baptiste</t>
+          <t>Mark Lajal</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>WTA - WTA Madrid, Spain Women Singles</t>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>CLAY</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="G15" s="13" t="n">
-        <v>1.3</v>
+        <v>2.62</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>1.19</v>
+        <v>2.34</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>8.9</v>
+        <v>42.8</v>
+      </c>
+      <c r="J15" s="15" t="n">
+        <v>12.2</v>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+          <t>TA-hard+forma+fat(0.0/-0.3)</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
@@ -1564,7 +1528,7 @@
         </is>
       </c>
       <c r="M15" s="13" t="n">
-        <v>1.3</v>
+        <v>2.62</v>
       </c>
       <c r="N15" s="10" t="inlineStr"/>
       <c r="O15" s="11" t="inlineStr"/>
@@ -1574,49 +1538,49 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>✅ Adam Walton</t>
+          <t>✅ Jesper De Jong</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Jie Cui</t>
+          <t>Gianluca Cadenasso</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>CLAY</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>85.59999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>8.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>TA-hard+forma</t>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
@@ -1625,287 +1589,281 @@
         </is>
       </c>
       <c r="M16" s="7" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="N16" s="10" t="inlineStr"/>
       <c r="O16" s="11" t="inlineStr"/>
-      <c r="P16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="Q16" s="5" t="n">
-        <v>0.27</v>
-      </c>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>14:13</t>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>✅ David Goffin</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Thomas Faurel</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>1.61</v>
+          <t>✅ Jaime Faria</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>Miguel Damas</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>1.33</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="J17" s="9" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>TA-clay+forma+fat(-0.3/0.0)</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M17" s="7" t="n">
-        <v>1.61</v>
+        <v>1.24</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>1.33</v>
       </c>
       <c r="N17" s="10" t="inlineStr"/>
       <c r="O17" s="11" t="inlineStr"/>
-      <c r="P17" s="5" t="inlineStr"/>
-      <c r="Q17" s="5" t="inlineStr"/>
+      <c r="P17" s="12" t="inlineStr"/>
+      <c r="Q17" s="12" t="inlineStr"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>14:13</t>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>✅ Adrian Mannarino</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Jesper De Jong</t>
-        </is>
-      </c>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G18" s="13" t="n">
-        <v>4.8</v>
+          <t>✅ Roman Safiullin</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>David Jorda Sanchis</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>1.2</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="I18" s="12" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="J18" s="9" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="K18" s="12" t="inlineStr">
+        <v>1.12</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>TA-clay+forma</t>
         </is>
       </c>
-      <c r="L18" s="12" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M18" s="13" t="n">
-        <v>4.8</v>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>1.2</v>
       </c>
       <c r="N18" s="10" t="inlineStr"/>
       <c r="O18" s="11" t="inlineStr"/>
-      <c r="P18" s="12" t="inlineStr"/>
-      <c r="Q18" s="12" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr"/>
+      <c r="Q18" s="5" t="inlineStr"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>14:13</t>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>✅ David Jorda Sanchis</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Sandro Kopp</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>2.25</v>
+          <t>✅ Alexander Zverev</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Alexander Blockx</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>1.28</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="J19" s="9" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>TA-clay+forma+fat(0.0/-0.3)</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M19" s="7" t="n">
-        <v>2.25</v>
+        <v>1.22</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K19" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L19" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>1.28</v>
       </c>
       <c r="N19" s="10" t="inlineStr"/>
       <c r="O19" s="11" t="inlineStr"/>
-      <c r="P19" s="5" t="inlineStr"/>
-      <c r="Q19" s="5" t="inlineStr"/>
+      <c r="P19" s="12" t="inlineStr"/>
+      <c r="Q19" s="12" t="inlineStr"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>14:13</t>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>✅ Rudolf Molleker</t>
-        </is>
-      </c>
-      <c r="D20" s="12" t="inlineStr">
-        <is>
-          <t>Henri Squire</t>
-        </is>
-      </c>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
-        </is>
-      </c>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G20" s="13" t="n">
-        <v>2.52</v>
+          <t>✅ Ignacio Buse</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Alejandro Tabilo</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>2.15</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="I20" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="J20" s="9" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="K20" s="12" t="inlineStr">
+        <v>2.05</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>TA-clay+forma+fat(-0.3/0.0)</t>
         </is>
       </c>
-      <c r="L20" s="12" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M20" s="13" t="n">
-        <v>2.52</v>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>2.15</v>
       </c>
       <c r="N20" s="10" t="inlineStr"/>
       <c r="O20" s="11" t="inlineStr"/>
-      <c r="P20" s="12" t="inlineStr"/>
-      <c r="Q20" s="12" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr"/>
+      <c r="Q20" s="5" t="inlineStr"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>03:02</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>✅ Jonas Forejtek</t>
+          <t>✅ Alexander Binda</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Zdenek Kolar</t>
+          <t>Manas Dhamne</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+          <t>Challenger - ATP Challenger Shymkent II, Kazakhstan Men Singles</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -1914,20 +1872,20 @@
         </is>
       </c>
       <c r="G21" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="J21" s="14" t="n">
-        <v>17.4</v>
+        <v>50.5</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>51.5</v>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
@@ -1936,7 +1894,7 @@
         </is>
       </c>
       <c r="M21" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N21" s="10" t="inlineStr"/>
       <c r="O21" s="11" t="inlineStr"/>
@@ -1946,27 +1904,27 @@
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>03:02</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>✅ Arthur Fils</t>
+          <t>✅ Kimmer Coppejans</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Jiri Lehecka</t>
+          <t>Pol Martin Tiffon</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>ATP - ATP Madrid, Spain Men Singles</t>
+          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
@@ -1975,20 +1933,20 @@
         </is>
       </c>
       <c r="G22" s="13" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>73.8</v>
+        <v>68.3</v>
       </c>
       <c r="J22" s="14" t="n">
-        <v>15.8</v>
+        <v>36.7</v>
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>TA-clay+forma</t>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
         </is>
       </c>
       <c r="L22" s="12" t="inlineStr">
@@ -1997,7 +1955,7 @@
         </is>
       </c>
       <c r="M22" s="13" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="N22" s="10" t="inlineStr"/>
       <c r="O22" s="11" t="inlineStr"/>
@@ -2007,27 +1965,27 @@
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>03:02</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>✅ Jaime Faria</t>
+          <t>✅ Rinky Hijikata</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Martin Krumich</t>
+          <t>Zizou Bergs</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
+          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -2036,20 +1994,20 @@
         </is>
       </c>
       <c r="G23" s="7" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>1.31</v>
+        <v>2.59</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>76.09999999999999</v>
+        <v>38.6</v>
       </c>
       <c r="J23" s="14" t="n">
-        <v>14.2</v>
+        <v>31.3</v>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -2058,7 +2016,7 @@
         </is>
       </c>
       <c r="M23" s="7" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="N23" s="10" t="inlineStr"/>
       <c r="O23" s="11" t="inlineStr"/>
@@ -2068,27 +2026,27 @@
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>03:02</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>✅ Damir Dzumhur</t>
+          <t>✅ Laslo Djere</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Emilio Nava</t>
+          <t>Lukas Neumayer</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -2097,20 +2055,20 @@
         </is>
       </c>
       <c r="G24" s="13" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>2.21</v>
+        <v>1.35</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>45.3</v>
+        <v>74.3</v>
       </c>
       <c r="J24" s="14" t="n">
-        <v>13.3</v>
+        <v>30</v>
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>TA-clay+forma</t>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
         </is>
       </c>
       <c r="L24" s="12" t="inlineStr">
@@ -2119,7 +2077,7 @@
         </is>
       </c>
       <c r="M24" s="13" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="N24" s="10" t="inlineStr"/>
       <c r="O24" s="11" t="inlineStr"/>
@@ -2129,49 +2087,49 @@
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>03:02</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>✅ Mert Alkaya</t>
+          <t>✅ Alex Bolt</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Paul Jubb</t>
+          <t>Keegan Smith</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>CLAY</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="G25" s="7" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>1.87</v>
+        <v>1.19</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>53.6</v>
+        <v>84.2</v>
       </c>
       <c r="J25" s="14" t="n">
-        <v>12.6</v>
+        <v>23.7</v>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+          <t>TA-hard+forma+fat(-0.3/-0.3)</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -2180,7 +2138,7 @@
         </is>
       </c>
       <c r="M25" s="7" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="N25" s="10" t="inlineStr"/>
       <c r="O25" s="11" t="inlineStr"/>
@@ -2190,22 +2148,22 @@
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>03:02</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>✅ Lorenzo Sonego</t>
+          <t>✅ Matteo Arnaldi</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Mattia Bellucci</t>
+          <t>Nuno Borges</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
@@ -2219,20 +2177,20 @@
         </is>
       </c>
       <c r="G26" s="13" t="n">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>66.5</v>
+        <v>57.7</v>
       </c>
       <c r="J26" s="14" t="n">
-        <v>10.4</v>
+        <v>21.2</v>
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>TA-clay+forma</t>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
         </is>
       </c>
       <c r="L26" s="12" t="inlineStr">
@@ -2241,7 +2199,7 @@
         </is>
       </c>
       <c r="M26" s="13" t="n">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="N26" s="10" t="inlineStr"/>
       <c r="O26" s="11" t="inlineStr"/>
@@ -2251,27 +2209,27 @@
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>03:02</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>✅ Vitaliy Sachko</t>
+          <t>✅ Hamish Stewart</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Nikolas Sanchez Izquierdo</t>
+          <t>Eliakim Coulibaly</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -2280,16 +2238,16 @@
         </is>
       </c>
       <c r="G27" s="7" t="n">
-        <v>1.62</v>
+        <v>2.37</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>1.48</v>
+        <v>1.97</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="J27" s="5" t="n">
-        <v>9.699999999999999</v>
+        <v>50.7</v>
+      </c>
+      <c r="J27" s="14" t="n">
+        <v>20.1</v>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
@@ -2302,7 +2260,7 @@
         </is>
       </c>
       <c r="M27" s="7" t="n">
-        <v>1.62</v>
+        <v>2.37</v>
       </c>
       <c r="N27" s="10" t="inlineStr"/>
       <c r="O27" s="11" t="inlineStr"/>
@@ -2312,27 +2270,27 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>03:02</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>✅ Mirra Andreeva</t>
+          <t>✅ Mert Alkaya</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Hailey Baptiste</t>
+          <t>Gauthier Onclin</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>WTA - WTA Madrid, Spain Women Singles</t>
+          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -2341,16 +2299,16 @@
         </is>
       </c>
       <c r="G28" s="13" t="n">
-        <v>1.3</v>
+        <v>3.25</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>1.19</v>
+        <v>2.72</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="J28" s="12" t="n">
-        <v>8.9</v>
+        <v>36.7</v>
+      </c>
+      <c r="J28" s="15" t="n">
+        <v>19.3</v>
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
@@ -2363,7 +2321,7 @@
         </is>
       </c>
       <c r="M28" s="13" t="n">
-        <v>1.3</v>
+        <v>3.25</v>
       </c>
       <c r="N28" s="10" t="inlineStr"/>
       <c r="O28" s="11" t="inlineStr"/>
@@ -2373,49 +2331,49 @@
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>03:02</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>✅ Adam Walton</t>
+          <t>✅ Marcos Giron</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Jie Cui</t>
+          <t>Roman Andres Burruchaga</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>CLAY</t>
         </is>
       </c>
       <c r="G29" s="7" t="n">
-        <v>1.27</v>
+        <v>2.42</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>1.17</v>
+        <v>2.03</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="J29" s="5" t="n">
-        <v>8.699999999999999</v>
+        <v>49.2</v>
+      </c>
+      <c r="J29" s="15" t="n">
+        <v>19.1</v>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>TA-hard+forma</t>
+          <t>TA-clay+forma</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -2424,7 +2382,7 @@
         </is>
       </c>
       <c r="M29" s="7" t="n">
-        <v>1.27</v>
+        <v>2.42</v>
       </c>
       <c r="N29" s="10" t="inlineStr"/>
       <c r="O29" s="11" t="inlineStr"/>
@@ -2434,27 +2392,27 @@
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>03:02</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>✅ Hamish Stewart</t>
+          <t>✅ Mili Poljicak</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Blaise Bicknell</t>
+          <t>Buvaysar Gadamauri</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
+          <t>Challenger - ATP Challenger Shymkent II, Kazakhstan Men Singles</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -2463,16 +2421,16 @@
         </is>
       </c>
       <c r="G30" s="13" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>1.58</v>
+        <v>1.32</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="J30" s="12" t="n">
-        <v>5.2</v>
+        <v>75.7</v>
+      </c>
+      <c r="J30" s="15" t="n">
+        <v>18.8</v>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
@@ -2485,7 +2443,7 @@
         </is>
       </c>
       <c r="M30" s="13" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="N30" s="10" t="inlineStr"/>
       <c r="O30" s="11" t="inlineStr"/>
@@ -2495,27 +2453,27 @@
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>03:02</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>✅ David Goffin</t>
+          <t>✅ Arthur Fils</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Thomas Faurel</t>
+          <t>Jannik Sinner</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -2524,20 +2482,20 @@
         </is>
       </c>
       <c r="G31" s="7" t="n">
-        <v>1.61</v>
+        <v>5.5</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>1.29</v>
+        <v>4.82</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="J31" s="9" t="n">
-        <v>24.8</v>
+        <v>20.7</v>
+      </c>
+      <c r="J31" s="15" t="n">
+        <v>14</v>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -2546,7 +2504,7 @@
         </is>
       </c>
       <c r="M31" s="7" t="n">
-        <v>1.61</v>
+        <v>5.5</v>
       </c>
       <c r="N31" s="10" t="inlineStr"/>
       <c r="O31" s="11" t="inlineStr"/>
@@ -2556,27 +2514,27 @@
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>03:02</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>✅ Adrian Mannarino</t>
+          <t>✅ Mirra Andreeva</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Jesper De Jong</t>
+          <t>Marta Kostyuk</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+          <t>WTA - WTA Madrid, Spain Women Singles</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -2585,20 +2543,20 @@
         </is>
       </c>
       <c r="G32" s="13" t="n">
-        <v>4.8</v>
+        <v>1.67</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>3.86</v>
+        <v>1.47</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="J32" s="9" t="n">
-        <v>24.3</v>
+        <v>68.09999999999999</v>
+      </c>
+      <c r="J32" s="15" t="n">
+        <v>13.8</v>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>TA-clay+forma</t>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr">
@@ -2607,7 +2565,7 @@
         </is>
       </c>
       <c r="M32" s="13" t="n">
-        <v>4.8</v>
+        <v>1.67</v>
       </c>
       <c r="N32" s="10" t="inlineStr"/>
       <c r="O32" s="11" t="inlineStr"/>
@@ -2617,27 +2575,27 @@
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>03:02</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>✅ David Jorda Sanchis</t>
+          <t>✅ Antoine Ghibaudo</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Sandro Kopp</t>
+          <t>Andrej Nedic</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
+          <t>Challenger - ATP Challenger Shymkent II, Kazakhstan Men Singles</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -2646,20 +2604,20 @@
         </is>
       </c>
       <c r="G33" s="7" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>1.84</v>
+        <v>2.39</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="J33" s="9" t="n">
-        <v>22.5</v>
+        <v>41.8</v>
+      </c>
+      <c r="J33" s="15" t="n">
+        <v>12.8</v>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -2668,7 +2626,7 @@
         </is>
       </c>
       <c r="M33" s="7" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="N33" s="10" t="inlineStr"/>
       <c r="O33" s="11" t="inlineStr"/>
@@ -2678,27 +2636,27 @@
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>03:02</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>✅ Rudolf Molleker</t>
+          <t>✅ Yibing Wu</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Henri Squire</t>
+          <t>Ethan Quinn</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -2707,20 +2665,20 @@
         </is>
       </c>
       <c r="G34" s="13" t="n">
-        <v>2.52</v>
+        <v>1.8</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>2.08</v>
+        <v>1.6</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="J34" s="9" t="n">
-        <v>20.9</v>
+        <v>62.4</v>
+      </c>
+      <c r="J34" s="15" t="n">
+        <v>12.4</v>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+          <t>TA-clay+forma</t>
         </is>
       </c>
       <c r="L34" s="12" t="inlineStr">
@@ -2729,7 +2687,7 @@
         </is>
       </c>
       <c r="M34" s="13" t="n">
-        <v>2.52</v>
+        <v>1.8</v>
       </c>
       <c r="N34" s="10" t="inlineStr"/>
       <c r="O34" s="11" t="inlineStr"/>
@@ -2739,49 +2697,49 @@
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>03:02</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>✅ Jonas Forejtek</t>
+          <t>✅ Fajing Sun</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Zdenek Kolar</t>
+          <t>Mark Lajal</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
+          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>CLAY</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="G35" s="7" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>1.7</v>
+        <v>2.34</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="J35" s="14" t="n">
-        <v>17.4</v>
+        <v>42.8</v>
+      </c>
+      <c r="J35" s="15" t="n">
+        <v>12.2</v>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+          <t>TA-hard+forma+fat(0.0/-0.3)</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -2790,7 +2748,7 @@
         </is>
       </c>
       <c r="M35" s="7" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="N35" s="10" t="inlineStr"/>
       <c r="O35" s="11" t="inlineStr"/>
@@ -2800,27 +2758,27 @@
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>03:02</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>✅ Arthur Fils</t>
+          <t>✅ Jesper De Jong</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Jiri Lehecka</t>
+          <t>Gianluca Cadenasso</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>ATP - ATP Madrid, Spain Men Singles</t>
+          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -2832,17 +2790,17 @@
         <v>1.57</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="J36" s="14" t="n">
-        <v>15.8</v>
+        <v>69.8</v>
+      </c>
+      <c r="J36" s="12" t="n">
+        <v>9.6</v>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>TA-clay+forma</t>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
         </is>
       </c>
       <c r="L36" s="12" t="inlineStr">
@@ -2861,12 +2819,12 @@
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>03:02</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -2876,7 +2834,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Martin Krumich</t>
+          <t>Miguel Damas</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2890,20 +2848,20 @@
         </is>
       </c>
       <c r="G37" s="7" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>76.09999999999999</v>
-      </c>
-      <c r="J37" s="14" t="n">
-        <v>14.2</v>
+        <v>80.5</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>7</v>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+          <t>TA-clay+forma</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -2912,7 +2870,7 @@
         </is>
       </c>
       <c r="M37" s="7" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="N37" s="10" t="inlineStr"/>
       <c r="O37" s="11" t="inlineStr"/>
@@ -2922,27 +2880,27 @@
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>03:02</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>✅ Damir Dzumhur</t>
+          <t>✅ Roman Safiullin</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Emilio Nava</t>
+          <t>David Jorda Sanchis</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
@@ -2951,16 +2909,16 @@
         </is>
       </c>
       <c r="G38" s="13" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>2.21</v>
+        <v>1.12</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="J38" s="14" t="n">
-        <v>13.3</v>
+        <v>88.90000000000001</v>
+      </c>
+      <c r="J38" s="12" t="n">
+        <v>6.7</v>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
@@ -2973,7 +2931,7 @@
         </is>
       </c>
       <c r="M38" s="13" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="N38" s="10" t="inlineStr"/>
       <c r="O38" s="11" t="inlineStr"/>
@@ -2983,27 +2941,27 @@
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>03:02</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>✅ Mert Alkaya</t>
+          <t>✅ Alexander Zverev</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Paul Jubb</t>
+          <t>Alexander Blockx</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
+          <t>ATP - ATP Madrid, Spain Men Singles</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -3012,20 +2970,20 @@
         </is>
       </c>
       <c r="G39" s="7" t="n">
-        <v>2.1</v>
+        <v>1.28</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>1.87</v>
+        <v>1.22</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="J39" s="14" t="n">
-        <v>12.6</v>
+        <v>82.2</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>5.2</v>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+          <t>TA-clay+forma</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -3034,7 +2992,7 @@
         </is>
       </c>
       <c r="M39" s="7" t="n">
-        <v>2.1</v>
+        <v>1.28</v>
       </c>
       <c r="N39" s="10" t="inlineStr"/>
       <c r="O39" s="11" t="inlineStr"/>
@@ -3044,27 +3002,27 @@
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>03:02</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>✅ Lorenzo Sonego</t>
+          <t>✅ Ignacio Buse</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>Mattia Bellucci</t>
+          <t>Alejandro Tabilo</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
+          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
@@ -3073,20 +3031,20 @@
         </is>
       </c>
       <c r="G40" s="13" t="n">
-        <v>1.66</v>
+        <v>2.15</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>1.5</v>
+        <v>2.05</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="J40" s="14" t="n">
-        <v>10.4</v>
+        <v>48.9</v>
+      </c>
+      <c r="J40" s="12" t="n">
+        <v>5.1</v>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>TA-clay+forma</t>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr">
@@ -3095,1415 +3053,12 @@
         </is>
       </c>
       <c r="M40" s="13" t="n">
-        <v>1.66</v>
+        <v>2.15</v>
       </c>
       <c r="N40" s="10" t="inlineStr"/>
       <c r="O40" s="11" t="inlineStr"/>
       <c r="P40" s="12" t="inlineStr"/>
       <c r="Q40" s="12" t="inlineStr"/>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>✅ Vitaliy Sachko</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>Nikolas Sanchez Izquierdo</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H41" s="8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="I41" s="5" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="J41" s="5" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>TA-clay+forma</t>
-        </is>
-      </c>
-      <c r="L41" s="5" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M41" s="7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="N41" s="10" t="inlineStr"/>
-      <c r="O41" s="11" t="inlineStr"/>
-      <c r="P41" s="5" t="inlineStr"/>
-      <c r="Q41" s="5" t="inlineStr"/>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>✅ Mirra Andreeva</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>Hailey Baptiste</t>
-        </is>
-      </c>
-      <c r="E42" s="12" t="inlineStr">
-        <is>
-          <t>WTA - WTA Madrid, Spain Women Singles</t>
-        </is>
-      </c>
-      <c r="F42" s="12" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G42" s="13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="I42" s="12" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="J42" s="12" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="K42" s="12" t="inlineStr">
-        <is>
-          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
-        </is>
-      </c>
-      <c r="L42" s="12" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M42" s="13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N42" s="10" t="inlineStr"/>
-      <c r="O42" s="11" t="inlineStr"/>
-      <c r="P42" s="12" t="inlineStr"/>
-      <c r="Q42" s="12" t="inlineStr"/>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>✅ Adam Walton</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Jie Cui</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="I43" s="5" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="J43" s="5" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>TA-hard+forma</t>
-        </is>
-      </c>
-      <c r="L43" s="5" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M43" s="7" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="N43" s="10" t="inlineStr"/>
-      <c r="O43" s="11" t="inlineStr"/>
-      <c r="P43" s="5" t="inlineStr"/>
-      <c r="Q43" s="5" t="inlineStr"/>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>✅ Hamish Stewart</t>
-        </is>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
-        <is>
-          <t>Blaise Bicknell</t>
-        </is>
-      </c>
-      <c r="E44" s="12" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
-        </is>
-      </c>
-      <c r="F44" s="12" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G44" s="13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="H44" s="8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="I44" s="12" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="J44" s="12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="K44" s="12" t="inlineStr">
-        <is>
-          <t>TA-clay+forma</t>
-        </is>
-      </c>
-      <c r="L44" s="12" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M44" s="13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="N44" s="10" t="inlineStr"/>
-      <c r="O44" s="11" t="inlineStr"/>
-      <c r="P44" s="12" t="inlineStr"/>
-      <c r="Q44" s="12" t="inlineStr"/>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>02:36</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>✅ Alexander Binda</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>Manas Dhamne</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Shymkent II, Kazakhstan Men Singles</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H45" s="8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="I45" s="5" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="J45" s="18" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
-        </is>
-      </c>
-      <c r="L45" s="5" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M45" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N45" s="10" t="inlineStr"/>
-      <c r="O45" s="11" t="inlineStr"/>
-      <c r="P45" s="5" t="inlineStr"/>
-      <c r="Q45" s="5" t="inlineStr"/>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t>02:36</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>✅ Kimmer Coppejans</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>Pol Martin Tiffon</t>
-        </is>
-      </c>
-      <c r="E46" s="12" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
-        </is>
-      </c>
-      <c r="F46" s="12" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G46" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H46" s="8" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="I46" s="12" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="J46" s="9" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="K46" s="12" t="inlineStr">
-        <is>
-          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
-        </is>
-      </c>
-      <c r="L46" s="12" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M46" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="N46" s="10" t="inlineStr"/>
-      <c r="O46" s="11" t="inlineStr"/>
-      <c r="P46" s="12" t="inlineStr"/>
-      <c r="Q46" s="12" t="inlineStr"/>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>02:36</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>✅ Rinky Hijikata</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>Zizou Bergs</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H47" s="8" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="I47" s="5" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="J47" s="9" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>TA-clay+forma+fat(0.0/-0.3)</t>
-        </is>
-      </c>
-      <c r="L47" s="5" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M47" s="7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N47" s="10" t="inlineStr"/>
-      <c r="O47" s="11" t="inlineStr"/>
-      <c r="P47" s="5" t="inlineStr"/>
-      <c r="Q47" s="5" t="inlineStr"/>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B48" s="12" t="inlineStr">
-        <is>
-          <t>02:36</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>✅ Laslo Djere</t>
-        </is>
-      </c>
-      <c r="D48" s="12" t="inlineStr">
-        <is>
-          <t>Lukas Neumayer</t>
-        </is>
-      </c>
-      <c r="E48" s="12" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
-        </is>
-      </c>
-      <c r="F48" s="12" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G48" s="13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="H48" s="8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="I48" s="12" t="n">
-        <v>74.3</v>
-      </c>
-      <c r="J48" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="K48" s="12" t="inlineStr">
-        <is>
-          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
-        </is>
-      </c>
-      <c r="L48" s="12" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M48" s="13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="N48" s="10" t="inlineStr"/>
-      <c r="O48" s="11" t="inlineStr"/>
-      <c r="P48" s="12" t="inlineStr"/>
-      <c r="Q48" s="12" t="inlineStr"/>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>02:36</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>✅ Alex Bolt</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>Keegan Smith</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="H49" s="8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="I49" s="5" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="J49" s="9" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>TA-hard+forma+fat(-0.3/-0.3)</t>
-        </is>
-      </c>
-      <c r="L49" s="5" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M49" s="7" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="N49" s="10" t="inlineStr"/>
-      <c r="O49" s="11" t="inlineStr"/>
-      <c r="P49" s="5" t="inlineStr"/>
-      <c r="Q49" s="5" t="inlineStr"/>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B50" s="12" t="inlineStr">
-        <is>
-          <t>02:36</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>✅ Marcos Giron</t>
-        </is>
-      </c>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>Roman Andres Burruchaga</t>
-        </is>
-      </c>
-      <c r="E50" s="12" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
-        </is>
-      </c>
-      <c r="F50" s="12" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G50" s="13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H50" s="8" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="I50" s="12" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="J50" s="9" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="K50" s="12" t="inlineStr">
-        <is>
-          <t>TA-clay+forma</t>
-        </is>
-      </c>
-      <c r="L50" s="12" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M50" s="13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N50" s="10" t="inlineStr"/>
-      <c r="O50" s="11" t="inlineStr"/>
-      <c r="P50" s="12" t="inlineStr"/>
-      <c r="Q50" s="12" t="inlineStr"/>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>02:36</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>✅ Matteo Arnaldi</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>Nuno Borges</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H51" s="8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="I51" s="5" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="J51" s="9" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>TA-clay+forma+fat(-0.3/0.0)</t>
-        </is>
-      </c>
-      <c r="L51" s="5" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M51" s="7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N51" s="10" t="inlineStr"/>
-      <c r="O51" s="11" t="inlineStr"/>
-      <c r="P51" s="5" t="inlineStr"/>
-      <c r="Q51" s="5" t="inlineStr"/>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="12" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B52" s="12" t="inlineStr">
-        <is>
-          <t>02:36</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>✅ Mert Alkaya</t>
-        </is>
-      </c>
-      <c r="D52" s="12" t="inlineStr">
-        <is>
-          <t>Gauthier Onclin</t>
-        </is>
-      </c>
-      <c r="E52" s="12" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
-        </is>
-      </c>
-      <c r="F52" s="12" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G52" s="13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="H52" s="8" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="I52" s="12" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="J52" s="14" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="K52" s="12" t="inlineStr">
-        <is>
-          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
-        </is>
-      </c>
-      <c r="L52" s="12" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M52" s="13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N52" s="10" t="inlineStr"/>
-      <c r="O52" s="11" t="inlineStr"/>
-      <c r="P52" s="12" t="inlineStr"/>
-      <c r="Q52" s="12" t="inlineStr"/>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>02:36</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>✅ Hamish Stewart</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>Eliakim Coulibaly</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Abidjan 2, Cote d Ivoire, Men Singles</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="H53" s="8" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="I53" s="5" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="J53" s="14" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>TA-clay+forma</t>
-        </is>
-      </c>
-      <c r="L53" s="5" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M53" s="7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="N53" s="10" t="inlineStr"/>
-      <c r="O53" s="11" t="inlineStr"/>
-      <c r="P53" s="5" t="inlineStr"/>
-      <c r="Q53" s="5" t="inlineStr"/>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="12" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B54" s="12" t="inlineStr">
-        <is>
-          <t>02:36</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>✅ Mili Poljicak</t>
-        </is>
-      </c>
-      <c r="D54" s="12" t="inlineStr">
-        <is>
-          <t>Buvaysar Gadamauri</t>
-        </is>
-      </c>
-      <c r="E54" s="12" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Shymkent II, Kazakhstan Men Singles</t>
-        </is>
-      </c>
-      <c r="F54" s="12" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G54" s="13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="H54" s="8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="I54" s="12" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="J54" s="14" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="K54" s="12" t="inlineStr">
-        <is>
-          <t>TA-clay+forma</t>
-        </is>
-      </c>
-      <c r="L54" s="12" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M54" s="13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="N54" s="10" t="inlineStr"/>
-      <c r="O54" s="11" t="inlineStr"/>
-      <c r="P54" s="12" t="inlineStr"/>
-      <c r="Q54" s="12" t="inlineStr"/>
-    </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>02:36</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>✅ Antoine Ghibaudo</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>Andrej Nedic</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Shymkent II, Kazakhstan Men Singles</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="H55" s="8" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="I55" s="5" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="J55" s="14" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="K55" s="5" t="inlineStr">
-        <is>
-          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
-        </is>
-      </c>
-      <c r="L55" s="5" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M55" s="7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N55" s="10" t="inlineStr"/>
-      <c r="O55" s="11" t="inlineStr"/>
-      <c r="P55" s="5" t="inlineStr"/>
-      <c r="Q55" s="5" t="inlineStr"/>
-    </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="12" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B56" s="12" t="inlineStr">
-        <is>
-          <t>02:36</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>✅ Arthur Fils</t>
-        </is>
-      </c>
-      <c r="D56" s="12" t="inlineStr">
-        <is>
-          <t>Jannik Sinner</t>
-        </is>
-      </c>
-      <c r="E56" s="12" t="inlineStr">
-        <is>
-          <t>ATP - ATP Madrid, Spain Men Singles</t>
-        </is>
-      </c>
-      <c r="F56" s="12" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G56" s="13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H56" s="8" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="I56" s="12" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="J56" s="14" t="n">
-        <v>14</v>
-      </c>
-      <c r="K56" s="12" t="inlineStr">
-        <is>
-          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
-        </is>
-      </c>
-      <c r="L56" s="12" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M56" s="13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N56" s="10" t="inlineStr"/>
-      <c r="O56" s="11" t="inlineStr"/>
-      <c r="P56" s="12" t="inlineStr"/>
-      <c r="Q56" s="12" t="inlineStr"/>
-    </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>02:36</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>✅ Yibing Wu</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>Ethan Quinn</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H57" s="8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="I57" s="5" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="J57" s="14" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>TA-clay+forma</t>
-        </is>
-      </c>
-      <c r="L57" s="5" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M57" s="7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="N57" s="10" t="inlineStr"/>
-      <c r="O57" s="11" t="inlineStr"/>
-      <c r="P57" s="5" t="inlineStr"/>
-      <c r="Q57" s="5" t="inlineStr"/>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="12" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B58" s="12" t="inlineStr">
-        <is>
-          <t>02:36</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>✅ Fajing Sun</t>
-        </is>
-      </c>
-      <c r="D58" s="12" t="inlineStr">
-        <is>
-          <t>Mark Lajal</t>
-        </is>
-      </c>
-      <c r="E58" s="12" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
-        </is>
-      </c>
-      <c r="F58" s="12" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-      <c r="G58" s="13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="H58" s="8" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="I58" s="12" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="J58" s="14" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="K58" s="12" t="inlineStr">
-        <is>
-          <t>TA-hard+forma+fat(0.0/-0.3)</t>
-        </is>
-      </c>
-      <c r="L58" s="12" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M58" s="13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="N58" s="10" t="inlineStr"/>
-      <c r="O58" s="11" t="inlineStr"/>
-      <c r="P58" s="12" t="inlineStr"/>
-      <c r="Q58" s="12" t="inlineStr"/>
-    </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>02:36</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>✅ Jesper De Jong</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>Gianluca Cadenasso</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="H59" s="8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="I59" s="5" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="J59" s="5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="K59" s="5" t="inlineStr">
-        <is>
-          <t>TA-clay+forma+fat(-0.3/0.0)</t>
-        </is>
-      </c>
-      <c r="L59" s="5" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M59" s="7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="N59" s="10" t="inlineStr"/>
-      <c r="O59" s="11" t="inlineStr"/>
-      <c r="P59" s="5" t="inlineStr"/>
-      <c r="Q59" s="5" t="inlineStr"/>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="12" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B60" s="12" t="inlineStr">
-        <is>
-          <t>02:36</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>✅ Jaime Faria</t>
-        </is>
-      </c>
-      <c r="D60" s="12" t="inlineStr">
-        <is>
-          <t>Miguel Damas</t>
-        </is>
-      </c>
-      <c r="E60" s="12" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
-        </is>
-      </c>
-      <c r="F60" s="12" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G60" s="13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="H60" s="8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="I60" s="12" t="n">
-        <v>80.5</v>
-      </c>
-      <c r="J60" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K60" s="12" t="inlineStr">
-        <is>
-          <t>TA-clay+forma</t>
-        </is>
-      </c>
-      <c r="L60" s="12" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M60" s="13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="N60" s="10" t="inlineStr"/>
-      <c r="O60" s="11" t="inlineStr"/>
-      <c r="P60" s="12" t="inlineStr"/>
-      <c r="Q60" s="12" t="inlineStr"/>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>02:36</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>✅ Roman Safiullin</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>David Jorda Sanchis</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Mauthausen, Austria Men Singles</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H61" s="8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="I61" s="5" t="n">
-        <v>88.90000000000001</v>
-      </c>
-      <c r="J61" s="5" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="K61" s="5" t="inlineStr">
-        <is>
-          <t>TA-clay+forma</t>
-        </is>
-      </c>
-      <c r="L61" s="5" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M61" s="7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N61" s="10" t="inlineStr"/>
-      <c r="O61" s="11" t="inlineStr"/>
-      <c r="P61" s="5" t="inlineStr"/>
-      <c r="Q61" s="5" t="inlineStr"/>
-    </row>
-    <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="12" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B62" s="12" t="inlineStr">
-        <is>
-          <t>02:36</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>✅ Alexander Zverev</t>
-        </is>
-      </c>
-      <c r="D62" s="12" t="inlineStr">
-        <is>
-          <t>Alexander Blockx</t>
-        </is>
-      </c>
-      <c r="E62" s="12" t="inlineStr">
-        <is>
-          <t>ATP - ATP Madrid, Spain Men Singles</t>
-        </is>
-      </c>
-      <c r="F62" s="12" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G62" s="13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="H62" s="8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="I62" s="12" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="J62" s="12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="K62" s="12" t="inlineStr">
-        <is>
-          <t>TA-clay+forma</t>
-        </is>
-      </c>
-      <c r="L62" s="12" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M62" s="13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="N62" s="10" t="inlineStr"/>
-      <c r="O62" s="11" t="inlineStr"/>
-      <c r="P62" s="12" t="inlineStr"/>
-      <c r="Q62" s="12" t="inlineStr"/>
-    </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B63" s="5" t="inlineStr">
-        <is>
-          <t>02:36</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>✅ Ignacio Buse</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>Alejandro Tabilo</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="G63" s="7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="H63" s="8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="I63" s="5" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="J63" s="5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K63" s="5" t="inlineStr">
-        <is>
-          <t>TA-clay+forma+fat(-0.3/0.0)</t>
-        </is>
-      </c>
-      <c r="L63" s="5" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-      <c r="M63" s="7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="N63" s="10" t="inlineStr"/>
-      <c r="O63" s="11" t="inlineStr"/>
-      <c r="P63" s="5" t="inlineStr"/>
-      <c r="Q63" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4516,7 +3071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4533,89 +3088,90 @@
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>Ora</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>Punta su (handicap)</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>Avversario</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>Handicap</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>Quota</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
+      <c r="G1" s="16" t="inlineStr">
         <is>
           <t>Prob %</t>
         </is>
       </c>
-      <c r="H1" s="15" t="inlineStr">
+      <c r="H1" s="16" t="inlineStr">
         <is>
           <t>EV %</t>
         </is>
       </c>
-      <c r="I1" s="15" t="inlineStr">
+      <c r="I1" s="16" t="inlineStr">
         <is>
           <t>Torneo</t>
         </is>
       </c>
-      <c r="J1" s="15" t="inlineStr">
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>Superficie</t>
         </is>
       </c>
-      <c r="K1" s="15" t="inlineStr">
+      <c r="K1" s="16" t="inlineStr">
         <is>
           <t>Elo Diff</t>
         </is>
       </c>
-      <c r="L1" s="15" t="inlineStr">
+      <c r="L1" s="16" t="inlineStr">
         <is>
           <t>Margine Atteso</t>
         </is>
       </c>
-      <c r="M1" s="15" t="inlineStr">
+      <c r="M1" s="16" t="inlineStr">
         <is>
           <t>Elo Usato</t>
         </is>
       </c>
-      <c r="N1" s="15" t="inlineStr">
+      <c r="N1" s="16" t="inlineStr">
         <is>
           <t>Fonte</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B2" s="16" t="inlineStr">
-        <is>
-          <t>02:30</t>
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
@@ -4623,45 +3179,45 @@
           <t>✅ Kimmer Coppejans  +1.5</t>
         </is>
       </c>
-      <c r="D2" s="16" t="inlineStr">
+      <c r="D2" s="17" t="inlineStr">
         <is>
           <t>Pol Martin Tiffon</t>
         </is>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>1.5</v>
       </c>
-      <c r="F2" s="17" t="n">
+      <c r="F2" s="18" t="n">
         <v>1.8</v>
       </c>
-      <c r="G2" s="16" t="n">
+      <c r="G2" s="17" t="n">
         <v>77.90000000000001</v>
       </c>
-      <c r="H2" s="18" t="n">
+      <c r="H2" s="9" t="n">
         <v>40.2</v>
       </c>
-      <c r="I2" s="16" t="inlineStr">
+      <c r="I2" s="17" t="inlineStr">
         <is>
           <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
         </is>
       </c>
-      <c r="J2" s="16" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="K2" s="16" t="n">
+      <c r="J2" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K2" s="17" t="n">
         <v>134</v>
       </c>
-      <c r="L2" s="16" t="n">
+      <c r="L2" s="17" t="n">
         <v>2.19</v>
       </c>
-      <c r="M2" s="16" t="inlineStr">
+      <c r="M2" s="17" t="inlineStr">
         <is>
           <t>TA-clay+forma+fat(-0.3/-0.3)</t>
         </is>
       </c>
-      <c r="N2" s="16" t="inlineStr">
+      <c r="N2" s="17" t="inlineStr">
         <is>
           <t>odds-api.io</t>
         </is>
@@ -4675,7 +3231,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr">
@@ -4697,7 +3253,7 @@
       <c r="G3" s="12" t="n">
         <v>71.2</v>
       </c>
-      <c r="H3" s="18" t="n">
+      <c r="H3" s="9" t="n">
         <v>33.2</v>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -4728,14 +3284,14 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>02:30</t>
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -4743,45 +3299,45 @@
           <t>✅ Fajing Sun  +2.5</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>Mark Lajal</t>
         </is>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>2.5</v>
       </c>
-      <c r="F4" s="17" t="n">
+      <c r="F4" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="G4" s="16" t="n">
+      <c r="G4" s="17" t="n">
         <v>64.2</v>
       </c>
-      <c r="H4" s="9" t="n">
+      <c r="H4" s="14" t="n">
         <v>28.4</v>
       </c>
-      <c r="I4" s="16" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
         </is>
       </c>
-      <c r="J4" s="16" t="inlineStr">
+      <c r="J4" s="17" t="inlineStr">
         <is>
           <t>HARD</t>
         </is>
       </c>
-      <c r="K4" s="16" t="n">
+      <c r="K4" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="L4" s="16" t="n">
+      <c r="L4" s="17" t="n">
         <v>0.75</v>
       </c>
-      <c r="M4" s="16" t="inlineStr">
+      <c r="M4" s="17" t="inlineStr">
         <is>
           <t>TA-hard+forma+fat(0.0/-0.3)</t>
         </is>
       </c>
-      <c r="N4" s="16" t="inlineStr">
+      <c r="N4" s="17" t="inlineStr">
         <is>
           <t>odds-api.io</t>
         </is>
@@ -4795,7 +3351,7 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -4817,7 +3373,7 @@
       <c r="G5" s="12" t="n">
         <v>66.2</v>
       </c>
-      <c r="H5" s="9" t="n">
+      <c r="H5" s="14" t="n">
         <v>25.8</v>
       </c>
       <c r="I5" s="12" t="inlineStr">
@@ -4848,14 +3404,14 @@
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>02:30</t>
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -4863,45 +3419,45 @@
           <t>✅ Matteo Arnaldi  +1.5</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>Nuno Borges</t>
         </is>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>1.5</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="18" t="n">
         <v>1.83</v>
       </c>
-      <c r="G6" s="16" t="n">
+      <c r="G6" s="17" t="n">
         <v>68.5</v>
       </c>
-      <c r="H6" s="9" t="n">
+      <c r="H6" s="14" t="n">
         <v>25.3</v>
       </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="K6" s="16" t="n">
+      <c r="J6" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K6" s="17" t="n">
         <v>54</v>
       </c>
-      <c r="L6" s="16" t="n">
+      <c r="L6" s="17" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="M6" s="16" t="inlineStr">
+      <c r="M6" s="17" t="inlineStr">
         <is>
           <t>TA-clay+forma+fat(-0.3/0.0)</t>
         </is>
       </c>
-      <c r="N6" s="16" t="inlineStr">
+      <c r="N6" s="17" t="inlineStr">
         <is>
           <t>odds-api.io</t>
         </is>
@@ -4915,7 +3471,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -4937,7 +3493,7 @@
       <c r="G7" s="12" t="n">
         <v>68.3</v>
       </c>
-      <c r="H7" s="9" t="n">
+      <c r="H7" s="14" t="n">
         <v>25</v>
       </c>
       <c r="I7" s="12" t="inlineStr">
@@ -4968,14 +3524,14 @@
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>02:30</t>
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -4983,45 +3539,45 @@
           <t>✅ Alex Bolt  -2.5</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>Keegan Smith</t>
         </is>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>-2.5</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="18" t="n">
         <v>1.9</v>
       </c>
-      <c r="G8" s="16" t="n">
+      <c r="G8" s="17" t="n">
         <v>63.8</v>
       </c>
-      <c r="H8" s="9" t="n">
+      <c r="H8" s="14" t="n">
         <v>21.3</v>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J8" s="17" t="inlineStr">
         <is>
           <t>HARD</t>
         </is>
       </c>
-      <c r="K8" s="16" t="n">
+      <c r="K8" s="17" t="n">
         <v>290</v>
       </c>
-      <c r="L8" s="16" t="n">
+      <c r="L8" s="17" t="n">
         <v>4.2</v>
       </c>
-      <c r="M8" s="16" t="inlineStr">
+      <c r="M8" s="17" t="inlineStr">
         <is>
           <t>TA-hard+forma+fat(-0.3/-0.3)</t>
         </is>
       </c>
-      <c r="N8" s="16" t="inlineStr">
+      <c r="N8" s="17" t="inlineStr">
         <is>
           <t>odds-api.io</t>
         </is>
@@ -5035,7 +3591,7 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -5057,7 +3613,7 @@
       <c r="G9" s="12" t="n">
         <v>60.7</v>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="H9" s="14" t="n">
         <v>15.3</v>
       </c>
       <c r="I9" s="12" t="inlineStr">
@@ -5088,14 +3644,14 @@
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>02:30</t>
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -5103,45 +3659,45 @@
           <t>✅ Alexis Galarneau  +2.5</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>Adam Walton</t>
         </is>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>2.5</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="18" t="n">
         <v>1.83</v>
       </c>
-      <c r="G10" s="16" t="n">
+      <c r="G10" s="17" t="n">
         <v>62.7</v>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="H10" s="15" t="n">
         <v>14.8</v>
       </c>
-      <c r="I10" s="16" t="inlineStr">
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="J10" s="17" t="inlineStr">
         <is>
           <t>HARD</t>
         </is>
       </c>
-      <c r="K10" s="16" t="n">
+      <c r="K10" s="17" t="n">
         <v>64</v>
       </c>
-      <c r="L10" s="16" t="n">
+      <c r="L10" s="17" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="M10" s="16" t="inlineStr">
+      <c r="M10" s="17" t="inlineStr">
         <is>
           <t>TA-hard+forma+fat(-0.3/0.0)</t>
         </is>
       </c>
-      <c r="N10" s="16" t="inlineStr">
+      <c r="N10" s="17" t="inlineStr">
         <is>
           <t>odds-api.io</t>
         </is>
@@ -5155,7 +3711,7 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -5177,7 +3733,7 @@
       <c r="G11" s="12" t="n">
         <v>61.3</v>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="H11" s="15" t="n">
         <v>13.3</v>
       </c>
       <c r="I11" s="12" t="inlineStr">
@@ -5208,14 +3764,14 @@
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>02:30</t>
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -5223,45 +3779,45 @@
           <t>✅ Nerman Fatic  -0.5</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>Zdenek Kolar</t>
         </is>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="18" t="n">
         <v>1.83</v>
       </c>
-      <c r="G12" s="16" t="n">
+      <c r="G12" s="17" t="n">
         <v>59.7</v>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="H12" s="15" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="I12" s="16" t="inlineStr">
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
         </is>
       </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="K12" s="16" t="n">
+      <c r="J12" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K12" s="17" t="n">
         <v>104</v>
       </c>
-      <c r="L12" s="16" t="n">
+      <c r="L12" s="17" t="n">
         <v>1.68</v>
       </c>
-      <c r="M12" s="16" t="inlineStr">
+      <c r="M12" s="17" t="inlineStr">
         <is>
           <t>TA-clay+forma</t>
         </is>
       </c>
-      <c r="N12" s="16" t="inlineStr">
+      <c r="N12" s="17" t="inlineStr">
         <is>
           <t>odds-api.io</t>
         </is>
@@ -5275,7 +3831,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>02:30</t>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -5297,7 +3853,7 @@
       <c r="G13" s="12" t="n">
         <v>60.7</v>
       </c>
-      <c r="H13" s="14" t="n">
+      <c r="H13" s="15" t="n">
         <v>6.3</v>
       </c>
       <c r="I13" s="12" t="inlineStr">
@@ -5328,14 +3884,14 @@
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>02:30</t>
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>02:40</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -5343,59 +3899,59 @@
           <t>✅ Matteo Berrettini  +0.5</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>Hubert Hurkacz</t>
         </is>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="F14" s="17" t="n">
+      <c r="F14" s="18" t="n">
         <v>1.85</v>
       </c>
-      <c r="G14" s="16" t="n">
+      <c r="G14" s="17" t="n">
         <v>57.4</v>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="H14" s="15" t="n">
         <v>6.1</v>
       </c>
-      <c r="I14" s="16" t="inlineStr">
+      <c r="I14" s="17" t="inlineStr">
         <is>
           <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
         </is>
       </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="K14" s="16" t="n">
+      <c r="J14" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K14" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="L14" s="16" t="n">
+      <c r="L14" s="17" t="n">
         <v>0.39</v>
       </c>
-      <c r="M14" s="16" t="inlineStr">
+      <c r="M14" s="17" t="inlineStr">
         <is>
           <t>TA-clay+forma</t>
         </is>
       </c>
-      <c r="N14" s="16" t="inlineStr">
+      <c r="N14" s="17" t="inlineStr">
         <is>
           <t>odds-api.io</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>02:37</t>
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>03:03</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -5403,47 +3959,52 @@
           <t>✅ Kimmer Coppejans  +1.5</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="17" t="inlineStr">
         <is>
           <t>Pol Martin Tiffon</t>
         </is>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>1.5</v>
       </c>
-      <c r="F15" s="17" t="n">
+      <c r="F15" s="18" t="n">
         <v>1.8</v>
       </c>
-      <c r="G15" s="16" t="n">
+      <c r="G15" s="17" t="n">
         <v>77.90000000000001</v>
       </c>
-      <c r="H15" s="18" t="n">
+      <c r="H15" s="9" t="n">
         <v>40.2</v>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I15" s="17" t="inlineStr">
         <is>
           <t>Challenger - ATP Challenger Aix en Provence, France Men Singles</t>
         </is>
       </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="K15" s="16" t="n">
+      <c r="J15" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K15" s="17" t="n">
         <v>134</v>
       </c>
-      <c r="L15" s="16" t="n">
+      <c r="L15" s="17" t="n">
         <v>2.19</v>
       </c>
-      <c r="M15" s="16" t="inlineStr">
+      <c r="M15" s="17" t="inlineStr">
         <is>
           <t>TA-clay+forma+fat(-0.3/-0.3)</t>
         </is>
       </c>
-      <c r="N15" s="16" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
+      <c r="N15" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="O15" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
         </is>
       </c>
     </row>
@@ -5455,7 +4016,7 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>02:37</t>
+          <t>03:03</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -5477,7 +4038,7 @@
       <c r="G16" s="12" t="n">
         <v>71.2</v>
       </c>
-      <c r="H16" s="18" t="n">
+      <c r="H16" s="9" t="n">
         <v>33.2</v>
       </c>
       <c r="I16" s="12" t="inlineStr">
@@ -5506,16 +4067,21 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>02:37</t>
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>03:03</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -5523,47 +4089,52 @@
           <t>✅ Fajing Sun  +2.5</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>Mark Lajal</t>
         </is>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>2.5</v>
       </c>
-      <c r="F17" s="17" t="n">
+      <c r="F17" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="G17" s="16" t="n">
+      <c r="G17" s="17" t="n">
         <v>64.2</v>
       </c>
-      <c r="H17" s="9" t="n">
+      <c r="H17" s="14" t="n">
         <v>28.4</v>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I17" s="17" t="inlineStr">
         <is>
           <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
         </is>
       </c>
-      <c r="J17" s="16" t="inlineStr">
+      <c r="J17" s="17" t="inlineStr">
         <is>
           <t>HARD</t>
         </is>
       </c>
-      <c r="K17" s="16" t="n">
+      <c r="K17" s="17" t="n">
         <v>50</v>
       </c>
-      <c r="L17" s="16" t="n">
+      <c r="L17" s="17" t="n">
         <v>0.75</v>
       </c>
-      <c r="M17" s="16" t="inlineStr">
+      <c r="M17" s="17" t="inlineStr">
         <is>
           <t>TA-hard+forma+fat(0.0/-0.3)</t>
         </is>
       </c>
-      <c r="N17" s="16" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
+      <c r="N17" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="O17" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
         </is>
       </c>
     </row>
@@ -5575,7 +4146,7 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>02:37</t>
+          <t>03:03</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -5597,7 +4168,7 @@
       <c r="G18" s="12" t="n">
         <v>66.2</v>
       </c>
-      <c r="H18" s="9" t="n">
+      <c r="H18" s="14" t="n">
         <v>25.8</v>
       </c>
       <c r="I18" s="12" t="inlineStr">
@@ -5626,16 +4197,21 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>02:37</t>
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>03:03</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -5643,47 +4219,52 @@
           <t>✅ Matteo Arnaldi  +1.5</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>Nuno Borges</t>
         </is>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>1.5</v>
       </c>
-      <c r="F19" s="17" t="n">
+      <c r="F19" s="18" t="n">
         <v>1.83</v>
       </c>
-      <c r="G19" s="16" t="n">
+      <c r="G19" s="17" t="n">
         <v>68.5</v>
       </c>
-      <c r="H19" s="9" t="n">
+      <c r="H19" s="14" t="n">
         <v>25.3</v>
       </c>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="I19" s="17" t="inlineStr">
         <is>
           <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
         </is>
       </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="K19" s="16" t="n">
+      <c r="J19" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K19" s="17" t="n">
         <v>54</v>
       </c>
-      <c r="L19" s="16" t="n">
+      <c r="L19" s="17" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="M19" s="16" t="inlineStr">
+      <c r="M19" s="17" t="inlineStr">
         <is>
           <t>TA-clay+forma+fat(-0.3/0.0)</t>
         </is>
       </c>
-      <c r="N19" s="16" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
+      <c r="N19" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="O19" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
         </is>
       </c>
     </row>
@@ -5695,7 +4276,7 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>02:37</t>
+          <t>03:03</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -5717,7 +4298,7 @@
       <c r="G20" s="12" t="n">
         <v>68.3</v>
       </c>
-      <c r="H20" s="9" t="n">
+      <c r="H20" s="14" t="n">
         <v>25</v>
       </c>
       <c r="I20" s="12" t="inlineStr">
@@ -5746,16 +4327,21 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>02:37</t>
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>03:03</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -5763,47 +4349,52 @@
           <t>✅ Alex Bolt  -2.5</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>Keegan Smith</t>
         </is>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>-2.5</v>
       </c>
-      <c r="F21" s="17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G21" s="16" t="n">
+      <c r="F21" s="18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G21" s="17" t="n">
         <v>63.8</v>
       </c>
-      <c r="H21" s="9" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="H21" s="14" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="I21" s="17" t="inlineStr">
         <is>
           <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
         </is>
       </c>
-      <c r="J21" s="16" t="inlineStr">
+      <c r="J21" s="17" t="inlineStr">
         <is>
           <t>HARD</t>
         </is>
       </c>
-      <c r="K21" s="16" t="n">
+      <c r="K21" s="17" t="n">
         <v>290</v>
       </c>
-      <c r="L21" s="16" t="n">
+      <c r="L21" s="17" t="n">
         <v>4.2</v>
       </c>
-      <c r="M21" s="16" t="inlineStr">
+      <c r="M21" s="17" t="inlineStr">
         <is>
           <t>TA-hard+forma+fat(-0.3/-0.3)</t>
         </is>
       </c>
-      <c r="N21" s="16" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
+      <c r="N21" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="O21" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
         </is>
       </c>
     </row>
@@ -5815,7 +4406,7 @@
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>02:37</t>
+          <t>03:03</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -5837,7 +4428,7 @@
       <c r="G22" s="12" t="n">
         <v>60.7</v>
       </c>
-      <c r="H22" s="9" t="n">
+      <c r="H22" s="14" t="n">
         <v>15.3</v>
       </c>
       <c r="I22" s="12" t="inlineStr">
@@ -5866,16 +4457,21 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>02:37</t>
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>03:03</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -5883,47 +4479,52 @@
           <t>✅ Alexis Galarneau  +2.5</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D23" s="17" t="inlineStr">
         <is>
           <t>Adam Walton</t>
         </is>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>2.5</v>
       </c>
-      <c r="F23" s="17" t="n">
+      <c r="F23" s="18" t="n">
         <v>1.83</v>
       </c>
-      <c r="G23" s="16" t="n">
+      <c r="G23" s="17" t="n">
         <v>62.7</v>
       </c>
-      <c r="H23" s="14" t="n">
+      <c r="H23" s="15" t="n">
         <v>14.8</v>
       </c>
-      <c r="I23" s="16" t="inlineStr">
+      <c r="I23" s="17" t="inlineStr">
         <is>
           <t>Challenger - ATP Challenger Jiujiang, China Men Singles</t>
         </is>
       </c>
-      <c r="J23" s="16" t="inlineStr">
+      <c r="J23" s="17" t="inlineStr">
         <is>
           <t>HARD</t>
         </is>
       </c>
-      <c r="K23" s="16" t="n">
+      <c r="K23" s="17" t="n">
         <v>64</v>
       </c>
-      <c r="L23" s="16" t="n">
+      <c r="L23" s="17" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="M23" s="16" t="inlineStr">
+      <c r="M23" s="17" t="inlineStr">
         <is>
           <t>TA-hard+forma+fat(-0.3/0.0)</t>
         </is>
       </c>
-      <c r="N23" s="16" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
+      <c r="N23" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="O23" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
         </is>
       </c>
     </row>
@@ -5935,7 +4536,7 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>02:37</t>
+          <t>03:03</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -5957,7 +4558,7 @@
       <c r="G24" s="12" t="n">
         <v>61.3</v>
       </c>
-      <c r="H24" s="14" t="n">
+      <c r="H24" s="15" t="n">
         <v>13.3</v>
       </c>
       <c r="I24" s="12" t="inlineStr">
@@ -5986,16 +4587,21 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="O24" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>02:37</t>
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>03:03</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -6003,47 +4609,52 @@
           <t>✅ Nerman Fatic  -0.5</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
         <is>
           <t>Zdenek Kolar</t>
         </is>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="E25" s="17" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F25" s="17" t="n">
+      <c r="F25" s="18" t="n">
         <v>1.83</v>
       </c>
-      <c r="G25" s="16" t="n">
+      <c r="G25" s="17" t="n">
         <v>59.7</v>
       </c>
-      <c r="H25" s="14" t="n">
+      <c r="H25" s="15" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="I25" s="16" t="inlineStr">
+      <c r="I25" s="17" t="inlineStr">
         <is>
           <t>Challenger - ATP Challenger Ostrava, Czech Republic Men Singles</t>
         </is>
       </c>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="K25" s="16" t="n">
+      <c r="J25" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K25" s="17" t="n">
         <v>104</v>
       </c>
-      <c r="L25" s="16" t="n">
+      <c r="L25" s="17" t="n">
         <v>1.68</v>
       </c>
-      <c r="M25" s="16" t="inlineStr">
+      <c r="M25" s="17" t="inlineStr">
         <is>
           <t>TA-clay+forma</t>
         </is>
       </c>
-      <c r="N25" s="16" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
+      <c r="N25" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="O25" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
         </is>
       </c>
     </row>
@@ -6055,7 +4666,7 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>02:37</t>
+          <t>03:03</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -6077,7 +4688,7 @@
       <c r="G26" s="12" t="n">
         <v>60.7</v>
       </c>
-      <c r="H26" s="14" t="n">
+      <c r="H26" s="15" t="n">
         <v>6.3</v>
       </c>
       <c r="I26" s="12" t="inlineStr">
@@ -6106,16 +4717,21 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="O26" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>02:37</t>
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>03:03</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -6123,47 +4739,52 @@
           <t>✅ Matteo Berrettini  +0.5</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>Hubert Hurkacz</t>
         </is>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="E27" s="17" t="n">
         <v>0.5</v>
       </c>
-      <c r="F27" s="17" t="n">
+      <c r="F27" s="18" t="n">
         <v>1.85</v>
       </c>
-      <c r="G27" s="16" t="n">
+      <c r="G27" s="17" t="n">
         <v>57.4</v>
       </c>
-      <c r="H27" s="14" t="n">
+      <c r="H27" s="15" t="n">
         <v>6.1</v>
       </c>
-      <c r="I27" s="16" t="inlineStr">
+      <c r="I27" s="17" t="inlineStr">
         <is>
           <t>Challenger - ATP Challenger Cagliari, Italy Men Singles</t>
         </is>
       </c>
-      <c r="J27" s="16" t="inlineStr">
-        <is>
-          <t>CLAY</t>
-        </is>
-      </c>
-      <c r="K27" s="16" t="n">
+      <c r="J27" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="K27" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="L27" s="16" t="n">
+      <c r="L27" s="17" t="n">
         <v>0.39</v>
       </c>
-      <c r="M27" s="16" t="inlineStr">
+      <c r="M27" s="17" t="inlineStr">
         <is>
           <t>TA-clay+forma</t>
         </is>
       </c>
-      <c r="N27" s="16" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
+      <c r="N27" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="O27" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
         </is>
       </c>
     </row>

--- a/data/value_bets_log.xlsx
+++ b/data/value_bets_log.xlsx
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:Q96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -922,8 +922,14 @@
       </c>
       <c r="N5" s="10" t="inlineStr"/>
       <c r="O5" s="11" t="inlineStr"/>
-      <c r="P5" s="12" t="inlineStr"/>
-      <c r="Q5" s="12" t="inlineStr"/>
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q5" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
@@ -1044,8 +1050,14 @@
       </c>
       <c r="N7" s="10" t="inlineStr"/>
       <c r="O7" s="11" t="inlineStr"/>
-      <c r="P7" s="12" t="inlineStr"/>
-      <c r="Q7" s="12" t="inlineStr"/>
+      <c r="P7" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q7" s="12" t="n">
+        <v>1.75</v>
+      </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
@@ -1166,8 +1178,14 @@
       </c>
       <c r="N9" s="10" t="inlineStr"/>
       <c r="O9" s="11" t="inlineStr"/>
-      <c r="P9" s="12" t="inlineStr"/>
-      <c r="Q9" s="12" t="inlineStr"/>
+      <c r="P9" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q9" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
@@ -1227,8 +1245,14 @@
       </c>
       <c r="N10" s="10" t="inlineStr"/>
       <c r="O10" s="11" t="inlineStr"/>
-      <c r="P10" s="5" t="inlineStr"/>
-      <c r="Q10" s="5" t="inlineStr"/>
+      <c r="P10" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
@@ -1288,8 +1312,14 @@
       </c>
       <c r="N11" s="10" t="inlineStr"/>
       <c r="O11" s="11" t="inlineStr"/>
-      <c r="P11" s="12" t="inlineStr"/>
-      <c r="Q11" s="12" t="inlineStr"/>
+      <c r="P11" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q11" s="12" t="n">
+        <v>1.25</v>
+      </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
@@ -1349,8 +1379,14 @@
       </c>
       <c r="N12" s="10" t="inlineStr"/>
       <c r="O12" s="11" t="inlineStr"/>
-      <c r="P12" s="5" t="inlineStr"/>
-      <c r="Q12" s="5" t="inlineStr"/>
+      <c r="P12" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
@@ -1715,8 +1751,14 @@
       </c>
       <c r="N18" s="10" t="inlineStr"/>
       <c r="O18" s="11" t="inlineStr"/>
-      <c r="P18" s="5" t="inlineStr"/>
-      <c r="Q18" s="5" t="inlineStr"/>
+      <c r="P18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q18" s="5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
@@ -1776,8 +1818,14 @@
       </c>
       <c r="N19" s="10" t="inlineStr"/>
       <c r="O19" s="11" t="inlineStr"/>
-      <c r="P19" s="12" t="inlineStr"/>
-      <c r="Q19" s="12" t="inlineStr"/>
+      <c r="P19" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q19" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
@@ -1837,8 +1885,14 @@
       </c>
       <c r="N20" s="10" t="inlineStr"/>
       <c r="O20" s="11" t="inlineStr"/>
-      <c r="P20" s="5" t="inlineStr"/>
-      <c r="Q20" s="5" t="inlineStr"/>
+      <c r="P20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q20" s="5" t="n">
+        <v>0.53</v>
+      </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
@@ -1959,8 +2013,14 @@
       </c>
       <c r="N22" s="10" t="inlineStr"/>
       <c r="O22" s="11" t="inlineStr"/>
-      <c r="P22" s="5" t="inlineStr"/>
-      <c r="Q22" s="5" t="inlineStr"/>
+      <c r="P22" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q22" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
@@ -2081,8 +2141,14 @@
       </c>
       <c r="N24" s="10" t="inlineStr"/>
       <c r="O24" s="11" t="inlineStr"/>
-      <c r="P24" s="5" t="inlineStr"/>
-      <c r="Q24" s="5" t="inlineStr"/>
+      <c r="P24" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q24" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
@@ -2264,8 +2330,14 @@
       </c>
       <c r="N27" s="10" t="inlineStr"/>
       <c r="O27" s="11" t="inlineStr"/>
-      <c r="P27" s="12" t="inlineStr"/>
-      <c r="Q27" s="12" t="inlineStr"/>
+      <c r="P27" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q27" s="12" t="n">
+        <v>1.25</v>
+      </c>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
@@ -2325,8 +2397,14 @@
       </c>
       <c r="N28" s="10" t="inlineStr"/>
       <c r="O28" s="11" t="inlineStr"/>
-      <c r="P28" s="5" t="inlineStr"/>
-      <c r="Q28" s="5" t="inlineStr"/>
+      <c r="P28" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q28" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
@@ -2447,8 +2525,14 @@
       </c>
       <c r="N30" s="10" t="inlineStr"/>
       <c r="O30" s="11" t="inlineStr"/>
-      <c r="P30" s="5" t="inlineStr"/>
-      <c r="Q30" s="5" t="inlineStr"/>
+      <c r="P30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q30" s="5" t="n">
+        <v>0.71</v>
+      </c>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="12" t="inlineStr">
@@ -2569,8 +2653,14 @@
       </c>
       <c r="N32" s="10" t="inlineStr"/>
       <c r="O32" s="11" t="inlineStr"/>
-      <c r="P32" s="5" t="inlineStr"/>
-      <c r="Q32" s="5" t="inlineStr"/>
+      <c r="P32" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q32" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="12" t="inlineStr">
@@ -2630,8 +2720,14 @@
       </c>
       <c r="N33" s="10" t="inlineStr"/>
       <c r="O33" s="11" t="inlineStr"/>
-      <c r="P33" s="12" t="inlineStr"/>
-      <c r="Q33" s="12" t="inlineStr"/>
+      <c r="P33" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q33" s="12" t="n">
+        <v>0.58</v>
+      </c>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
@@ -2752,8 +2848,14 @@
       </c>
       <c r="N35" s="10" t="inlineStr"/>
       <c r="O35" s="11" t="inlineStr"/>
-      <c r="P35" s="12" t="inlineStr"/>
-      <c r="Q35" s="12" t="inlineStr"/>
+      <c r="P35" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q35" s="12" t="n">
+        <v>0.45</v>
+      </c>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
@@ -2874,8 +2976,14 @@
       </c>
       <c r="N37" s="10" t="inlineStr"/>
       <c r="O37" s="11" t="inlineStr"/>
-      <c r="P37" s="12" t="inlineStr"/>
-      <c r="Q37" s="12" t="inlineStr"/>
+      <c r="P37" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q37" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
@@ -3118,9 +3226,3582 @@
       </c>
       <c r="N41" s="10" t="inlineStr"/>
       <c r="O41" s="11" t="inlineStr"/>
-      <c r="P41" s="12" t="inlineStr"/>
-      <c r="Q41" s="12" t="inlineStr"/>
-    </row>
+      <c r="P41" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q41" s="12" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>✅ Iiro Vasa</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Michael Geerts</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Brazzaville, Republic of Congo Men Singles</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>128.3</v>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M42" s="7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="N42" s="10" t="inlineStr"/>
+      <c r="O42" s="11" t="inlineStr"/>
+      <c r="P42" s="5" t="inlineStr"/>
+      <c r="Q42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>✅ McCartney Kessler</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>Iva Jovic</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G43" s="13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I43" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="K43" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L43" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M43" s="13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N43" s="10" t="inlineStr"/>
+      <c r="O43" s="11" t="inlineStr"/>
+      <c r="P43" s="12" t="inlineStr"/>
+      <c r="Q43" s="12" t="inlineStr"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>✅ Clement Chidekh</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Martin Krumich</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Francavilla, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.6/-0.3)</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M44" s="7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="N44" s="10" t="inlineStr"/>
+      <c r="O44" s="11" t="inlineStr"/>
+      <c r="P44" s="5" t="inlineStr"/>
+      <c r="Q44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>✅ Bianca Andreescu</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>Belinda Bencic</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G45" s="13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="I45" s="12" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="K45" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L45" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M45" s="13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N45" s="10" t="inlineStr"/>
+      <c r="O45" s="11" t="inlineStr"/>
+      <c r="P45" s="12" t="inlineStr"/>
+      <c r="Q45" s="12" t="inlineStr"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>✅ Sinja Kraus</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Elisabetta Cocciaretto</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="H46" s="8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I46" s="5" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.6)</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M46" s="7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="N46" s="10" t="inlineStr"/>
+      <c r="O46" s="11" t="inlineStr"/>
+      <c r="P46" s="5" t="inlineStr"/>
+      <c r="Q46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>✅ August Holmgren</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>Guy Den Ouden</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Francavilla, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I47" s="12" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>63</v>
+      </c>
+      <c r="K47" s="12" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="L47" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M47" s="13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N47" s="10" t="inlineStr"/>
+      <c r="O47" s="11" t="inlineStr"/>
+      <c r="P47" s="12" t="inlineStr"/>
+      <c r="Q47" s="12" t="inlineStr"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>✅ Anastasia Zakharova</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Linda Noskova</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H48" s="8" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="I48" s="5" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M48" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="N48" s="10" t="inlineStr"/>
+      <c r="O48" s="11" t="inlineStr"/>
+      <c r="P48" s="5" t="inlineStr"/>
+      <c r="Q48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>✅ Buvaysar Gadamauri</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>Juan Carlos Prado Angelo</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Francavilla, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G49" s="13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H49" s="8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I49" s="12" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="K49" s="12" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="L49" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M49" s="13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="N49" s="10" t="inlineStr"/>
+      <c r="O49" s="11" t="inlineStr"/>
+      <c r="P49" s="12" t="inlineStr"/>
+      <c r="Q49" s="12" t="inlineStr"/>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>✅ Jenson Brooksby</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Sebastian Baez</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H50" s="8" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M50" s="7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N50" s="10" t="inlineStr"/>
+      <c r="O50" s="11" t="inlineStr"/>
+      <c r="P50" s="5" t="inlineStr"/>
+      <c r="Q50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>✅ Stefanos Sakellaridis</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>Gustavo Heide</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Francavilla, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G51" s="13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H51" s="8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I51" s="12" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="K51" s="12" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="L51" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M51" s="13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N51" s="10" t="inlineStr"/>
+      <c r="O51" s="11" t="inlineStr"/>
+      <c r="P51" s="12" t="inlineStr"/>
+      <c r="Q51" s="12" t="inlineStr"/>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>✅ Jan-Lennard Struff</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Francisco Comesana</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="H52" s="8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="J52" s="14" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.6)</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M52" s="7" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="N52" s="10" t="inlineStr"/>
+      <c r="O52" s="11" t="inlineStr"/>
+      <c r="P52" s="5" t="inlineStr"/>
+      <c r="Q52" s="5" t="inlineStr"/>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>✅ Lois Boisson</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>Katerina Siniakova</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G53" s="13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H53" s="8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="I53" s="12" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="J53" s="14" t="n">
+        <v>42</v>
+      </c>
+      <c r="K53" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L53" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M53" s="13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N53" s="10" t="inlineStr"/>
+      <c r="O53" s="11" t="inlineStr"/>
+      <c r="P53" s="12" t="inlineStr"/>
+      <c r="Q53" s="12" t="inlineStr"/>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>✅ Federica Urgesi</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>Viktorija Golubic</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H54" s="8" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J54" s="14" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.6)</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M54" s="7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N54" s="10" t="inlineStr"/>
+      <c r="O54" s="11" t="inlineStr"/>
+      <c r="P54" s="5" t="inlineStr"/>
+      <c r="Q54" s="5" t="inlineStr"/>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>✅ Ann Li</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>Liudmila Samsonova</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G55" s="13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H55" s="8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I55" s="12" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="J55" s="14" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="K55" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L55" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M55" s="13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N55" s="10" t="inlineStr"/>
+      <c r="O55" s="11" t="inlineStr"/>
+      <c r="P55" s="12" t="inlineStr"/>
+      <c r="Q55" s="12" t="inlineStr"/>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>✅ Simona Waltert</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Yuliia Starodubtseva</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="H56" s="8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="J56" s="14" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.6)</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M56" s="7" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N56" s="10" t="inlineStr"/>
+      <c r="O56" s="11" t="inlineStr"/>
+      <c r="P56" s="5" t="inlineStr"/>
+      <c r="Q56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>✅ Caty McNally</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>Daria Kasatkina</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G57" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H57" s="8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I57" s="12" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="J57" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="K57" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L57" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M57" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N57" s="10" t="inlineStr"/>
+      <c r="O57" s="11" t="inlineStr"/>
+      <c r="P57" s="12" t="inlineStr"/>
+      <c r="Q57" s="12" t="inlineStr"/>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>✅ Roberto Bautista Agut</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Francesco Maestrelli</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H58" s="8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="J58" s="14" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M58" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N58" s="10" t="inlineStr"/>
+      <c r="O58" s="11" t="inlineStr"/>
+      <c r="P58" s="5" t="inlineStr"/>
+      <c r="Q58" s="5" t="inlineStr"/>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>✅ Yulia Putintseva</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>Tereza Valentova</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G59" s="13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H59" s="8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I59" s="12" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="J59" s="14" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="K59" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L59" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="N59" s="10" t="inlineStr"/>
+      <c r="O59" s="11" t="inlineStr"/>
+      <c r="P59" s="12" t="inlineStr"/>
+      <c r="Q59" s="12" t="inlineStr"/>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>✅ Vit Kopriva</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Fabian Marozsan</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="H60" s="8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="J60" s="14" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M60" s="7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="N60" s="10" t="inlineStr"/>
+      <c r="O60" s="11" t="inlineStr"/>
+      <c r="P60" s="5" t="inlineStr"/>
+      <c r="Q60" s="5" t="inlineStr"/>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>✅ Alexander Blockx</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>Federico Cina</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F61" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G61" s="13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="H61" s="8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I61" s="12" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="J61" s="14" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="K61" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L61" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M61" s="13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="N61" s="10" t="inlineStr"/>
+      <c r="O61" s="11" t="inlineStr"/>
+      <c r="P61" s="12" t="inlineStr"/>
+      <c r="Q61" s="12" t="inlineStr"/>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>✅ Rebeka Masarova</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Oksana Selekhmeteva</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H62" s="8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="J62" s="14" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.6)</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M62" s="7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="N62" s="10" t="inlineStr"/>
+      <c r="O62" s="11" t="inlineStr"/>
+      <c r="P62" s="5" t="inlineStr"/>
+      <c r="Q62" s="5" t="inlineStr"/>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>✅ Leolia Jeanjean</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>Beatriz Haddad Maia</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F63" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G63" s="13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H63" s="8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I63" s="12" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="J63" s="14" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="K63" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.6/0.0)</t>
+        </is>
+      </c>
+      <c r="L63" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N63" s="10" t="inlineStr"/>
+      <c r="O63" s="11" t="inlineStr"/>
+      <c r="P63" s="12" t="inlineStr"/>
+      <c r="Q63" s="12" t="inlineStr"/>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>✅ Denis Shapovalov</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Mariano Navone</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="H64" s="8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="J64" s="14" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M64" s="7" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="N64" s="10" t="inlineStr"/>
+      <c r="O64" s="11" t="inlineStr"/>
+      <c r="P64" s="5" t="inlineStr"/>
+      <c r="Q64" s="5" t="inlineStr"/>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>✅ Stefanos Tsitsipas</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>Tomas Machac</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G65" s="13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H65" s="8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I65" s="12" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="J65" s="14" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="K65" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L65" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M65" s="13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="N65" s="10" t="inlineStr"/>
+      <c r="O65" s="11" t="inlineStr"/>
+      <c r="P65" s="12" t="inlineStr"/>
+      <c r="Q65" s="12" t="inlineStr"/>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>✅ Matteo Arnaldi</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Jaume Munar</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H66" s="8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="J66" s="14" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M66" s="7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="N66" s="10" t="inlineStr"/>
+      <c r="O66" s="11" t="inlineStr"/>
+      <c r="P66" s="5" t="inlineStr"/>
+      <c r="Q66" s="5" t="inlineStr"/>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>✅ Karolina Pliskova</t>
+        </is>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>Jessica Bouzas Maneiro</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F67" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G67" s="13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H67" s="8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I67" s="12" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="J67" s="14" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="K67" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L67" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M67" s="13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="N67" s="10" t="inlineStr"/>
+      <c r="O67" s="11" t="inlineStr"/>
+      <c r="P67" s="12" t="inlineStr"/>
+      <c r="Q67" s="12" t="inlineStr"/>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>✅ Alina Korneeva</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Panna Udvardy</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H68" s="8" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="J68" s="15" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.6)</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M68" s="7" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="N68" s="10" t="inlineStr"/>
+      <c r="O68" s="11" t="inlineStr"/>
+      <c r="P68" s="5" t="inlineStr"/>
+      <c r="Q68" s="5" t="inlineStr"/>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>✅ Andre Ilagan</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>Dane Sweeny</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Wuxi, China Men Singles</t>
+        </is>
+      </c>
+      <c r="F69" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G69" s="13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H69" s="8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I69" s="12" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="J69" s="15" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="K69" s="12" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.6/-0.3)</t>
+        </is>
+      </c>
+      <c r="L69" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M69" s="13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N69" s="10" t="inlineStr"/>
+      <c r="O69" s="11" t="inlineStr"/>
+      <c r="P69" s="12" t="inlineStr"/>
+      <c r="Q69" s="12" t="inlineStr"/>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>✅ Nishesh Basavareddy</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Jay Clarke</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Francavilla, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H70" s="8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="J70" s="15" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M70" s="7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="N70" s="10" t="inlineStr"/>
+      <c r="O70" s="11" t="inlineStr"/>
+      <c r="P70" s="5" t="inlineStr"/>
+      <c r="Q70" s="5" t="inlineStr"/>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>✅ Dino Prizmic</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>Marton Fucsovics</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G71" s="13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H71" s="8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I71" s="12" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="J71" s="15" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="K71" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.6)</t>
+        </is>
+      </c>
+      <c r="L71" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M71" s="13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N71" s="10" t="inlineStr"/>
+      <c r="O71" s="11" t="inlineStr"/>
+      <c r="P71" s="12" t="inlineStr"/>
+      <c r="Q71" s="12" t="inlineStr"/>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>✅ Taylor Townsend</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Nuria Brancaccio</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H72" s="8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="J72" s="15" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.6/0.0)</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M72" s="7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="N72" s="10" t="inlineStr"/>
+      <c r="O72" s="11" t="inlineStr"/>
+      <c r="P72" s="5" t="inlineStr"/>
+      <c r="Q72" s="5" t="inlineStr"/>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>✅ Zeynep Sonmez</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>Jessica Pegula</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G73" s="13" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="H73" s="8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I73" s="12" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="J73" s="15" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="K73" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L73" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M73" s="13" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="N73" s="10" t="inlineStr"/>
+      <c r="O73" s="11" t="inlineStr"/>
+      <c r="P73" s="12" t="inlineStr"/>
+      <c r="Q73" s="12" t="inlineStr"/>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>✅ Roman Andres Burruchaga</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Mattia Bellucci</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H74" s="8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="J74" s="15" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="K74" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M74" s="7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="N74" s="10" t="inlineStr"/>
+      <c r="O74" s="11" t="inlineStr"/>
+      <c r="P74" s="5" t="inlineStr"/>
+      <c r="Q74" s="5" t="inlineStr"/>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>✅ Oleksandra Oliynykova</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>Clara Tauson</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G75" s="13" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="H75" s="8" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="I75" s="12" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="J75" s="15" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="K75" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L75" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M75" s="13" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="N75" s="10" t="inlineStr"/>
+      <c r="O75" s="11" t="inlineStr"/>
+      <c r="P75" s="12" t="inlineStr"/>
+      <c r="Q75" s="12" t="inlineStr"/>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>✅ Marco Trungelliti</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Zachary Svajda</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H76" s="8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="J76" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="K76" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M76" s="7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="N76" s="10" t="inlineStr"/>
+      <c r="O76" s="11" t="inlineStr"/>
+      <c r="P76" s="5" t="inlineStr"/>
+      <c r="Q76" s="5" t="inlineStr"/>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>✅ Qinwen Zheng</t>
+        </is>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>Cristina Bucsa</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G77" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H77" s="8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="I77" s="12" t="n">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="J77" s="15" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="K77" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L77" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M77" s="13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N77" s="10" t="inlineStr"/>
+      <c r="O77" s="11" t="inlineStr"/>
+      <c r="P77" s="12" t="inlineStr"/>
+      <c r="Q77" s="12" t="inlineStr"/>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>✅ Magda Linette</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Tatjana Maria</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="H78" s="8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="J78" s="15" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M78" s="7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="N78" s="10" t="inlineStr"/>
+      <c r="O78" s="11" t="inlineStr"/>
+      <c r="P78" s="5" t="inlineStr"/>
+      <c r="Q78" s="5" t="inlineStr"/>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>✅ Alastair Gray</t>
+        </is>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>Jie Cui</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Wuxi, China Men Singles</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G79" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H79" s="8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I79" s="12" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="J79" s="15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K79" s="12" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="L79" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M79" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N79" s="10" t="inlineStr"/>
+      <c r="O79" s="11" t="inlineStr"/>
+      <c r="P79" s="12" t="inlineStr"/>
+      <c r="Q79" s="12" t="inlineStr"/>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>✅ Matteo Berrettini</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Alexei Popyrin</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H80" s="8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="J80" s="15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M80" s="7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="N80" s="10" t="inlineStr"/>
+      <c r="O80" s="11" t="inlineStr"/>
+      <c r="P80" s="5" t="inlineStr"/>
+      <c r="Q80" s="5" t="inlineStr"/>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>✅ Jesper De Jong</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>Nuno Borges</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F81" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G81" s="13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H81" s="8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I81" s="12" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="J81" s="15" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="K81" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.6/0.0)</t>
+        </is>
+      </c>
+      <c r="L81" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M81" s="13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="N81" s="10" t="inlineStr"/>
+      <c r="O81" s="11" t="inlineStr"/>
+      <c r="P81" s="12" t="inlineStr"/>
+      <c r="Q81" s="12" t="inlineStr"/>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>✅ Frederico Ferreira Silva</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Chun Hsin Tseng</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Francavilla, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H82" s="8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M82" s="7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N82" s="10" t="inlineStr"/>
+      <c r="O82" s="11" t="inlineStr"/>
+      <c r="P82" s="5" t="inlineStr"/>
+      <c r="Q82" s="5" t="inlineStr"/>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>✅ Sara Bejlek</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>Laura Siegemund</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F83" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G83" s="13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H83" s="8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I83" s="12" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="J83" s="12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="K83" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L83" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M83" s="13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="N83" s="10" t="inlineStr"/>
+      <c r="O83" s="11" t="inlineStr"/>
+      <c r="P83" s="12" t="inlineStr"/>
+      <c r="Q83" s="12" t="inlineStr"/>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>✅ Hernan Casanova</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Mateus Alves</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Santos, Brazil Men Singles</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H84" s="8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="K84" s="5" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="L84" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M84" s="7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="N84" s="10" t="inlineStr"/>
+      <c r="O84" s="11" t="inlineStr"/>
+      <c r="P84" s="5" t="inlineStr"/>
+      <c r="Q84" s="5" t="inlineStr"/>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>✅ Hamad Medjedovic</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>Valentin Royer</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F85" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G85" s="13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H85" s="8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I85" s="12" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="J85" s="12" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K85" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L85" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M85" s="13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="N85" s="10" t="inlineStr"/>
+      <c r="O85" s="11" t="inlineStr"/>
+      <c r="P85" s="12" t="inlineStr"/>
+      <c r="Q85" s="12" t="inlineStr"/>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>✅ Alejandro Tabilo</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Pablo Carreno Busta</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H86" s="8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L86" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M86" s="7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="N86" s="10" t="inlineStr"/>
+      <c r="O86" s="11" t="inlineStr"/>
+      <c r="P86" s="5" t="inlineStr"/>
+      <c r="Q86" s="5" t="inlineStr"/>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>✅ Botic Van de Zandschulp</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>Alexandre Muller</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F87" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G87" s="13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H87" s="8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="I87" s="12" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="J87" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K87" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L87" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M87" s="13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N87" s="10" t="inlineStr"/>
+      <c r="O87" s="11" t="inlineStr"/>
+      <c r="P87" s="12" t="inlineStr"/>
+      <c r="Q87" s="12" t="inlineStr"/>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>✅ Ignacio Buse</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Lorenzo Sonego</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H88" s="8" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K88" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L88" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M88" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N88" s="10" t="inlineStr"/>
+      <c r="O88" s="11" t="inlineStr"/>
+      <c r="P88" s="5" t="inlineStr"/>
+      <c r="Q88" s="5" t="inlineStr"/>
+    </row>
+    <row r="89" ht="22" customHeight="1">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>✅ Katie Boulter</t>
+        </is>
+      </c>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>Eva Lys</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F89" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G89" s="13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H89" s="8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I89" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="J89" s="12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K89" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L89" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M89" s="13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="N89" s="10" t="inlineStr"/>
+      <c r="O89" s="11" t="inlineStr"/>
+      <c r="P89" s="12" t="inlineStr"/>
+      <c r="Q89" s="12" t="inlineStr"/>
+    </row>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>✅ Zhizhen Zhang</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Daniel Altmaier</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H90" s="8" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="K90" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L90" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M90" s="7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N90" s="10" t="inlineStr"/>
+      <c r="O90" s="11" t="inlineStr"/>
+      <c r="P90" s="5" t="inlineStr"/>
+      <c r="Q90" s="5" t="inlineStr"/>
+    </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>✅ Digvijay Pratap Singh</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t>Karan (IND) Singh</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Brazzaville, Republic of Congo Men Singles</t>
+        </is>
+      </c>
+      <c r="F91" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G91" s="13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H91" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I91" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="J91" s="12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K91" s="12" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="L91" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M91" s="13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N91" s="10" t="inlineStr"/>
+      <c r="O91" s="11" t="inlineStr"/>
+      <c r="P91" s="12" t="inlineStr"/>
+      <c r="Q91" s="12" t="inlineStr"/>
+    </row>
+    <row r="92" ht="22" customHeight="1">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>✅ Nikolas Sanchez Izquierdo</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Facundo Diaz Acosta</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Francavilla, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H92" s="8" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K92" s="5" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="L92" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M92" s="7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N92" s="10" t="inlineStr"/>
+      <c r="O92" s="11" t="inlineStr"/>
+      <c r="P92" s="5" t="inlineStr"/>
+      <c r="Q92" s="5" t="inlineStr"/>
+    </row>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>✅ Lilli Tagger</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>Maria Sakkari</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F93" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G93" s="13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H93" s="8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I93" s="12" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="J93" s="12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K93" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.6/0.0)</t>
+        </is>
+      </c>
+      <c r="L93" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M93" s="13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N93" s="10" t="inlineStr"/>
+      <c r="O93" s="11" t="inlineStr"/>
+      <c r="P93" s="12" t="inlineStr"/>
+      <c r="Q93" s="12" t="inlineStr"/>
+    </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>✅ Mikhail Kukushkin</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Mark Lajal</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Wuxi, China Men Singles</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="H94" s="8" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="K94" s="5" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="L94" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M94" s="7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="N94" s="10" t="inlineStr"/>
+      <c r="O94" s="11" t="inlineStr"/>
+      <c r="P94" s="5" t="inlineStr"/>
+      <c r="Q94" s="5" t="inlineStr"/>
+    </row>
+    <row r="95" ht="22" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>03:05</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>✅ Tamara Korpatsch</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>Solana Sierra</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H95" s="8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K95" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.6)</t>
+        </is>
+      </c>
+      <c r="L95" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M95" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N95" s="10" t="inlineStr"/>
+      <c r="O95" s="11" t="inlineStr"/>
+      <c r="P95" s="5" t="inlineStr"/>
+      <c r="Q95" s="5" t="inlineStr"/>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>03:17</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>✅ Noemi Basiletti</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>Ajla Tomljanovic</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F96" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G96" s="13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="H96" s="8" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="I96" s="12" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J96" s="12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K96" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.6/-0.6)</t>
+        </is>
+      </c>
+      <c r="L96" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M96" s="13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N96" s="10" t="inlineStr"/>
+      <c r="O96" s="11" t="inlineStr"/>
+      <c r="P96" s="12" t="inlineStr"/>
+      <c r="Q96" s="12" t="inlineStr"/>
+    </row>
+    <row r="97" ht="22" customHeight="1"/>
+    <row r="98" ht="22" customHeight="1"/>
+    <row r="99" ht="22" customHeight="1"/>
+    <row r="100" ht="22" customHeight="1"/>
+    <row r="101" ht="22" customHeight="1"/>
+    <row r="102" ht="22" customHeight="1"/>
+    <row r="103" ht="22" customHeight="1"/>
+    <row r="104" ht="22" customHeight="1"/>
+    <row r="105" ht="22" customHeight="1"/>
+    <row r="106" ht="22" customHeight="1"/>
+    <row r="107" ht="22" customHeight="1"/>
+    <row r="108" ht="22" customHeight="1"/>
+    <row r="109" ht="22" customHeight="1"/>
+    <row r="110" ht="22" customHeight="1"/>
+    <row r="111" ht="22" customHeight="1"/>
+    <row r="112" ht="22" customHeight="1"/>
+    <row r="113" ht="22" customHeight="1"/>
+    <row r="114" ht="22" customHeight="1"/>
+    <row r="115" ht="22" customHeight="1"/>
+    <row r="116" ht="22" customHeight="1"/>
+    <row r="117" ht="22" customHeight="1"/>
+    <row r="118" ht="22" customHeight="1"/>
+    <row r="119" ht="22" customHeight="1"/>
+    <row r="120" ht="22" customHeight="1"/>
+    <row r="121" ht="22" customHeight="1"/>
+    <row r="122" ht="22" customHeight="1"/>
+    <row r="123" ht="22" customHeight="1"/>
+    <row r="124" ht="22" customHeight="1"/>
+    <row r="125" ht="22" customHeight="1"/>
+    <row r="126" ht="22" customHeight="1"/>
+    <row r="127" ht="22" customHeight="1"/>
+    <row r="128" ht="22" customHeight="1"/>
+    <row r="129" ht="22" customHeight="1"/>
+    <row r="130" ht="22" customHeight="1"/>
+    <row r="131" ht="22" customHeight="1"/>
+    <row r="132" ht="22" customHeight="1"/>
+    <row r="133" ht="22" customHeight="1"/>
+    <row r="134" ht="22" customHeight="1"/>
+    <row r="135" ht="22" customHeight="1"/>
+    <row r="136" ht="22" customHeight="1"/>
+    <row r="137" ht="22" customHeight="1"/>
+    <row r="138" ht="22" customHeight="1"/>
+    <row r="139" ht="22" customHeight="1"/>
+    <row r="140" ht="22" customHeight="1"/>
+    <row r="141" ht="22" customHeight="1"/>
+    <row r="142" ht="22" customHeight="1"/>
+    <row r="143" ht="22" customHeight="1"/>
+    <row r="144" ht="22" customHeight="1"/>
+    <row r="145" ht="22" customHeight="1"/>
+    <row r="146" ht="22" customHeight="1"/>
+    <row r="147" ht="22" customHeight="1"/>
+    <row r="148" ht="22" customHeight="1"/>
+    <row r="149" ht="22" customHeight="1"/>
+    <row r="150" ht="22" customHeight="1"/>
+    <row r="151" ht="22" customHeight="1"/>
+    <row r="152" ht="22" customHeight="1"/>
+    <row r="153" ht="22" customHeight="1"/>
+    <row r="154" ht="22" customHeight="1"/>
+    <row r="155" ht="22" customHeight="1"/>
+    <row r="156" ht="22" customHeight="1"/>
+    <row r="157" ht="22" customHeight="1"/>
+    <row r="158" ht="22" customHeight="1"/>
+    <row r="159" ht="22" customHeight="1"/>
+    <row r="160" ht="22" customHeight="1"/>
+    <row r="161" ht="22" customHeight="1"/>
+    <row r="162" ht="22" customHeight="1"/>
+    <row r="163" ht="22" customHeight="1"/>
+    <row r="164" ht="22" customHeight="1"/>
+    <row r="165" ht="22" customHeight="1"/>
+    <row r="166" ht="22" customHeight="1"/>
+    <row r="167" ht="22" customHeight="1"/>
+    <row r="168" ht="22" customHeight="1"/>
+    <row r="169" ht="22" customHeight="1"/>
+    <row r="170" ht="22" customHeight="1"/>
+    <row r="171" ht="22" customHeight="1"/>
+    <row r="172" ht="22" customHeight="1"/>
+    <row r="173" ht="22" customHeight="1"/>
+    <row r="174" ht="22" customHeight="1"/>
+    <row r="175" ht="22" customHeight="1"/>
+    <row r="176" ht="22" customHeight="1"/>
+    <row r="177" ht="22" customHeight="1"/>
+    <row r="178" ht="22" customHeight="1"/>
+    <row r="179" ht="22" customHeight="1"/>
+    <row r="180" ht="22" customHeight="1"/>
+    <row r="181" ht="22" customHeight="1"/>
+    <row r="182" ht="22" customHeight="1"/>
+    <row r="183" ht="22" customHeight="1"/>
+    <row r="184" ht="22" customHeight="1"/>
+    <row r="185" ht="22" customHeight="1"/>
+    <row r="186" ht="22" customHeight="1"/>
+    <row r="187" ht="22" customHeight="1"/>
+    <row r="188" ht="22" customHeight="1"/>
+    <row r="189" ht="22" customHeight="1"/>
+    <row r="190" ht="22" customHeight="1"/>
+    <row r="191" ht="22" customHeight="1"/>
+    <row r="192" ht="22" customHeight="1"/>
+    <row r="193" ht="22" customHeight="1"/>
+    <row r="194" ht="22" customHeight="1"/>
+    <row r="195" ht="22" customHeight="1"/>
+    <row r="196" ht="22" customHeight="1"/>
+    <row r="197" ht="22" customHeight="1"/>
+    <row r="198" ht="22" customHeight="1"/>
+    <row r="199" ht="22" customHeight="1"/>
+    <row r="200" ht="22" customHeight="1"/>
+    <row r="201" ht="22" customHeight="1"/>
+    <row r="202" ht="22" customHeight="1"/>
+    <row r="203" ht="22" customHeight="1"/>
+    <row r="204" ht="22" customHeight="1"/>
+    <row r="205" ht="22" customHeight="1"/>
+    <row r="206" ht="22" customHeight="1"/>
+    <row r="207" ht="22" customHeight="1"/>
+    <row r="208" ht="22" customHeight="1"/>
+    <row r="209" ht="22" customHeight="1"/>
+    <row r="210" ht="22" customHeight="1"/>
+    <row r="211" ht="22" customHeight="1"/>
+    <row r="212" ht="22" customHeight="1"/>
+    <row r="213" ht="22" customHeight="1"/>
+    <row r="214" ht="22" customHeight="1"/>
+    <row r="215" ht="22" customHeight="1"/>
+    <row r="216" ht="22" customHeight="1"/>
+    <row r="217" ht="22" customHeight="1"/>
+    <row r="218" ht="22" customHeight="1"/>
+    <row r="219" ht="22" customHeight="1"/>
+    <row r="220" ht="22" customHeight="1"/>
+    <row r="221" ht="22" customHeight="1"/>
+    <row r="222" ht="22" customHeight="1"/>
+    <row r="223" ht="22" customHeight="1"/>
+    <row r="224" ht="22" customHeight="1"/>
+    <row r="225" ht="22" customHeight="1"/>
+    <row r="226" ht="22" customHeight="1"/>
+    <row r="227" ht="22" customHeight="1"/>
+    <row r="228" ht="22" customHeight="1"/>
+    <row r="229" ht="22" customHeight="1"/>
+    <row r="230" ht="22" customHeight="1"/>
+    <row r="231" ht="22" customHeight="1"/>
+    <row r="232" ht="22" customHeight="1"/>
+    <row r="233" ht="22" customHeight="1"/>
+    <row r="234" ht="22" customHeight="1"/>
+    <row r="235" ht="22" customHeight="1"/>
+    <row r="236" ht="22" customHeight="1"/>
+    <row r="237" ht="22" customHeight="1"/>
+    <row r="238" ht="22" customHeight="1"/>
+    <row r="239" ht="22" customHeight="1"/>
+    <row r="240" ht="22" customHeight="1"/>
+    <row r="241" ht="22" customHeight="1"/>
+    <row r="242" ht="22" customHeight="1"/>
+    <row r="243" ht="22" customHeight="1"/>
+    <row r="244" ht="22" customHeight="1"/>
+    <row r="245" ht="22" customHeight="1"/>
+    <row r="246" ht="22" customHeight="1"/>
+    <row r="247" ht="22" customHeight="1"/>
+    <row r="248" ht="22" customHeight="1"/>
+    <row r="249" ht="22" customHeight="1"/>
+    <row r="250" ht="22" customHeight="1"/>
+    <row r="251" ht="22" customHeight="1"/>
+    <row r="252" ht="22" customHeight="1"/>
+    <row r="253" ht="22" customHeight="1"/>
+    <row r="254" ht="22" customHeight="1"/>
+    <row r="255" ht="22" customHeight="1"/>
+    <row r="256" ht="22" customHeight="1"/>
+    <row r="257" ht="22" customHeight="1"/>
+    <row r="258" ht="22" customHeight="1"/>
+    <row r="259" ht="22" customHeight="1"/>
+    <row r="260" ht="22" customHeight="1"/>
+    <row r="261" ht="22" customHeight="1"/>
+    <row r="262" ht="22" customHeight="1"/>
+    <row r="263" ht="22" customHeight="1"/>
+    <row r="264" ht="22" customHeight="1"/>
+    <row r="265" ht="22" customHeight="1"/>
+    <row r="266" ht="22" customHeight="1"/>
+    <row r="267" ht="22" customHeight="1"/>
+    <row r="268" ht="22" customHeight="1"/>
+    <row r="269" ht="22" customHeight="1"/>
+    <row r="270" ht="22" customHeight="1"/>
+    <row r="271" ht="22" customHeight="1"/>
+    <row r="272" ht="22" customHeight="1"/>
+    <row r="273" ht="22" customHeight="1"/>
+    <row r="274" ht="22" customHeight="1"/>
+    <row r="275" ht="22" customHeight="1"/>
+    <row r="276" ht="22" customHeight="1"/>
+    <row r="277" ht="22" customHeight="1"/>
+    <row r="278" ht="22" customHeight="1"/>
+    <row r="279" ht="22" customHeight="1"/>
+    <row r="280" ht="22" customHeight="1"/>
+    <row r="281" ht="22" customHeight="1"/>
+    <row r="282" ht="22" customHeight="1"/>
+    <row r="283" ht="22" customHeight="1"/>
+    <row r="284" ht="22" customHeight="1"/>
+    <row r="285" ht="22" customHeight="1"/>
+    <row r="286" ht="22" customHeight="1"/>
+    <row r="287" ht="22" customHeight="1"/>
+    <row r="288" ht="22" customHeight="1"/>
+    <row r="289" ht="22" customHeight="1"/>
+    <row r="290" ht="22" customHeight="1"/>
+    <row r="291" ht="22" customHeight="1"/>
+    <row r="292" ht="22" customHeight="1"/>
+    <row r="293" ht="22" customHeight="1"/>
+    <row r="294" ht="22" customHeight="1"/>
+    <row r="295" ht="22" customHeight="1"/>
+    <row r="296" ht="22" customHeight="1"/>
+    <row r="297" ht="22" customHeight="1"/>
+    <row r="298" ht="22" customHeight="1"/>
+    <row r="299" ht="22" customHeight="1"/>
+    <row r="300" ht="22" customHeight="1"/>
+    <row r="301" ht="22" customHeight="1"/>
+    <row r="302" ht="22" customHeight="1"/>
+    <row r="303" ht="22" customHeight="1"/>
+    <row r="304" ht="22" customHeight="1"/>
+    <row r="305" ht="22" customHeight="1"/>
+    <row r="306" ht="22" customHeight="1"/>
+    <row r="307" ht="22" customHeight="1"/>
+    <row r="308" ht="22" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3132,7 +6813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P39"/>
+  <dimension ref="A1:P87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5743,6 +9424,3350 @@
         </is>
       </c>
     </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>✅ McCartney Kessler  +4.5</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>Iva Jovic</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G40" s="18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H40" s="17" t="inlineStr"/>
+      <c r="I40" s="17" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="K40" s="17" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L40" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M40" s="17" t="n">
+        <v>92</v>
+      </c>
+      <c r="N40" s="17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O40" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="P40" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>✅ Clement Chidekh  +3.5</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>Martin Krumich</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H41" s="12" t="inlineStr"/>
+      <c r="I41" s="12" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="K41" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Francavilla, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L41" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="M41" s="12" t="n">
+        <v>202</v>
+      </c>
+      <c r="N41" s="12" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="O41" s="12" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.6/-0.3)</t>
+        </is>
+      </c>
+      <c r="P41" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>✅ August Holmgren  +1.5</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>Guy Den Ouden</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F42" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G42" s="18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H42" s="17" t="inlineStr"/>
+      <c r="I42" s="17" t="n">
+        <v>85</v>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="K42" s="17" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Francavilla, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L42" s="17" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="M42" s="17" t="n">
+        <v>216</v>
+      </c>
+      <c r="N42" s="17" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="O42" s="17" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="P42" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>✅ Lisa Pigato  +0.5</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>Tyra Caterina Grant</t>
+        </is>
+      </c>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G43" s="13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H43" s="12" t="inlineStr"/>
+      <c r="I43" s="12" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>53</v>
+      </c>
+      <c r="K43" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L43" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M43" s="12" t="n">
+        <v>264</v>
+      </c>
+      <c r="N43" s="12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O43" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P43" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>✅ Bianca Andreescu  +5.5</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="inlineStr">
+        <is>
+          <t>Belinda Bencic</t>
+        </is>
+      </c>
+      <c r="E44" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F44" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G44" s="18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H44" s="17" t="inlineStr"/>
+      <c r="I44" s="17" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="K44" s="17" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L44" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M44" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="N44" s="17" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="O44" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="P44" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>✅ Buvaysar Gadamauri  +1.5</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>Juan Carlos Prado Angelo</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G45" s="13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H45" s="12" t="inlineStr"/>
+      <c r="I45" s="12" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="K45" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Francavilla, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L45" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="M45" s="12" t="n">
+        <v>190</v>
+      </c>
+      <c r="N45" s="12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O45" s="12" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="P45" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>✅ Jan-Lennard Struff  +2.5</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="inlineStr">
+        <is>
+          <t>Francisco Comesana</t>
+        </is>
+      </c>
+      <c r="E46" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G46" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" s="17" t="inlineStr"/>
+      <c r="I46" s="17" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="K46" s="17" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L46" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M46" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="N46" s="17" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="O46" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.6)</t>
+        </is>
+      </c>
+      <c r="P46" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>✅ Stefanos Sakellaridis  +3.5</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>Gustavo Heide</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H47" s="12" t="inlineStr"/>
+      <c r="I47" s="12" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="K47" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Francavilla, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L47" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="M47" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="N47" s="12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="O47" s="12" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="P47" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>✅ Jenson Brooksby  +4.5</t>
+        </is>
+      </c>
+      <c r="D48" s="17" t="inlineStr">
+        <is>
+          <t>Sebastian Baez</t>
+        </is>
+      </c>
+      <c r="E48" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F48" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G48" s="18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H48" s="17" t="inlineStr"/>
+      <c r="I48" s="17" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="K48" s="17" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L48" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M48" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="N48" s="17" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="O48" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P48" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>✅ Lois Boisson  +4.5</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>Katerina Siniakova</t>
+        </is>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F49" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G49" s="13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H49" s="12" t="inlineStr"/>
+      <c r="I49" s="12" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="K49" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L49" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M49" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="N49" s="12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O49" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P49" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>✅ Barbora Krejcikova  +6.5</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="inlineStr">
+        <is>
+          <t>Aryna Sabalenka</t>
+        </is>
+      </c>
+      <c r="E50" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F50" s="17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G50" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" s="17" t="inlineStr"/>
+      <c r="I50" s="17" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="K50" s="17" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L50" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M50" s="17" t="n">
+        <v>340</v>
+      </c>
+      <c r="N50" s="17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O50" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="P50" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>✅ Yulia Putintseva  +2.5</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>Tereza Valentova</t>
+        </is>
+      </c>
+      <c r="E51" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G51" s="13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H51" s="12" t="inlineStr"/>
+      <c r="I51" s="12" t="n">
+        <v>76</v>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="K51" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L51" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M51" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="N51" s="12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="O51" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P51" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>✅ Oleksandra Oliynykova  +3.5</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="inlineStr">
+        <is>
+          <t>Clara Tauson</t>
+        </is>
+      </c>
+      <c r="E52" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G52" s="18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H52" s="17" t="inlineStr"/>
+      <c r="I52" s="17" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="K52" s="17" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L52" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M52" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="N52" s="17" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="O52" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="P52" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>✅ Zeynep Sonmez  +5.5</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>Jessica Pegula</t>
+        </is>
+      </c>
+      <c r="E53" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F53" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G53" s="13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H53" s="12" t="inlineStr"/>
+      <c r="I53" s="12" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="K53" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L53" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M53" s="12" t="n">
+        <v>188</v>
+      </c>
+      <c r="N53" s="12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O53" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="P53" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>✅ Dalibor Svrcina  +0.5</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
+        <is>
+          <t>Miomir Kecmanovic</t>
+        </is>
+      </c>
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G54" s="18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H54" s="17" t="inlineStr"/>
+      <c r="I54" s="17" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="K54" s="17" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L54" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M54" s="17" t="n">
+        <v>142</v>
+      </c>
+      <c r="N54" s="17" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="O54" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.6/0.0)</t>
+        </is>
+      </c>
+      <c r="P54" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>✅ Vit Kopriva  +1.5</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>Fabian Marozsan</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G55" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H55" s="12" t="inlineStr"/>
+      <c r="I55" s="12" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="K55" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L55" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M55" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="N55" s="12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="O55" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P55" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>✅ Vit Kopriva  +2.5</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>Fabian Marozsan</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G56" s="18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H56" s="17" t="inlineStr"/>
+      <c r="I56" s="17" t="n">
+        <v>73</v>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="K56" s="17" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L56" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M56" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="N56" s="17" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="O56" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P56" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>✅ Denis Shapovalov  +2.5</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>Mariano Navone</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G57" s="13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H57" s="12" t="inlineStr"/>
+      <c r="I57" s="12" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="J57" s="14" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="K57" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L57" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M57" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="N57" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="O57" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P57" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>✅ Andre Ilagan  +3.5</t>
+        </is>
+      </c>
+      <c r="D58" s="17" t="inlineStr">
+        <is>
+          <t>Dane Sweeny</t>
+        </is>
+      </c>
+      <c r="E58" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F58" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G58" s="18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H58" s="17" t="inlineStr"/>
+      <c r="I58" s="17" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="J58" s="14" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="K58" s="17" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Wuxi, China Men Singles</t>
+        </is>
+      </c>
+      <c r="L58" s="17" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="M58" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="N58" s="17" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="O58" s="17" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.6/-0.3)</t>
+        </is>
+      </c>
+      <c r="P58" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>✅ Caty McNally  +0.5</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>Daria Kasatkina</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G59" s="13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H59" s="12" t="inlineStr"/>
+      <c r="I59" s="12" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="J59" s="14" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="K59" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L59" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M59" s="12" t="n">
+        <v>111</v>
+      </c>
+      <c r="N59" s="12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O59" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P59" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>✅ Mikhail Kukushkin  +2.5</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="inlineStr">
+        <is>
+          <t>Mark Lajal</t>
+        </is>
+      </c>
+      <c r="E60" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G60" s="18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H60" s="17" t="inlineStr"/>
+      <c r="I60" s="17" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="J60" s="14" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="K60" s="17" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Wuxi, China Men Singles</t>
+        </is>
+      </c>
+      <c r="L60" s="17" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="M60" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="N60" s="17" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="O60" s="17" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="P60" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>✅ Janice Tjen  +4.5</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>Peyton Stearns</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F61" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G61" s="13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H61" s="12" t="inlineStr"/>
+      <c r="I61" s="12" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="J61" s="14" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="K61" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L61" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M61" s="12" t="n">
+        <v>128</v>
+      </c>
+      <c r="N61" s="12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O61" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P61" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>✅ Lucrezia Stefanini  +6.5</t>
+        </is>
+      </c>
+      <c r="D62" s="17" t="inlineStr">
+        <is>
+          <t>Jelena Ostapenko</t>
+        </is>
+      </c>
+      <c r="E62" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F62" s="17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G62" s="18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H62" s="17" t="inlineStr"/>
+      <c r="I62" s="17" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="J62" s="14" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="K62" s="17" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L62" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M62" s="17" t="n">
+        <v>400</v>
+      </c>
+      <c r="N62" s="17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O62" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P62" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>✅ Antonia Ruzic  +6.5</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>Mirra Andreeva</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F63" s="12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G63" s="13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H63" s="12" t="inlineStr"/>
+      <c r="I63" s="12" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="J63" s="14" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="K63" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L63" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M63" s="12" t="n">
+        <v>378</v>
+      </c>
+      <c r="N63" s="12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O63" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="P63" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>✅ Zhizhen Zhang  +2.5</t>
+        </is>
+      </c>
+      <c r="D64" s="17" t="inlineStr">
+        <is>
+          <t>Daniel Altmaier</t>
+        </is>
+      </c>
+      <c r="E64" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F64" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G64" s="18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H64" s="17" t="inlineStr"/>
+      <c r="I64" s="17" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="J64" s="14" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="K64" s="17" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L64" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M64" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="N64" s="17" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="O64" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P64" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>✅ Anastasia Zakharova  +6.5</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>Linda Noskova</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G65" s="13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H65" s="12" t="inlineStr"/>
+      <c r="I65" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="J65" s="14" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="K65" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L65" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M65" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="N65" s="12" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="O65" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="P65" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>✅ Stefanos Tsitsipas  +0.0</t>
+        </is>
+      </c>
+      <c r="D66" s="17" t="inlineStr">
+        <is>
+          <t>Tomas Machac</t>
+        </is>
+      </c>
+      <c r="E66" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H66" s="17" t="inlineStr"/>
+      <c r="I66" s="17" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="J66" s="14" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="K66" s="17" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L66" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M66" s="17" t="n">
+        <v>149</v>
+      </c>
+      <c r="N66" s="17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O66" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P66" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>✅ Marcos Giron  +2.5</t>
+        </is>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>Marin Cilic</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F67" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G67" s="13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H67" s="12" t="inlineStr"/>
+      <c r="I67" s="12" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="J67" s="14" t="n">
+        <v>19</v>
+      </c>
+      <c r="K67" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L67" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M67" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="N67" s="12" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="O67" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P67" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>✅ Beatriz Haddad Maia  +3.5</t>
+        </is>
+      </c>
+      <c r="D68" s="17" t="inlineStr">
+        <is>
+          <t>Jaqueline Cristian</t>
+        </is>
+      </c>
+      <c r="E68" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F68" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G68" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H68" s="17" t="inlineStr"/>
+      <c r="I68" s="17" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="J68" s="14" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="K68" s="17" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L68" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M68" s="17" t="n">
+        <v>171</v>
+      </c>
+      <c r="N68" s="17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O68" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P68" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>✅ Cristina Bucsa  +5.5</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>Qinwen Zheng</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F69" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G69" s="13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H69" s="12" t="inlineStr"/>
+      <c r="I69" s="12" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="J69" s="14" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="K69" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L69" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M69" s="12" t="n">
+        <v>452</v>
+      </c>
+      <c r="N69" s="12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O69" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="P69" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B70" s="17" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>✅ Yannick Hanfmann  +2.5</t>
+        </is>
+      </c>
+      <c r="D70" s="17" t="inlineStr">
+        <is>
+          <t>Hubert Hurkacz</t>
+        </is>
+      </c>
+      <c r="E70" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F70" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G70" s="18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H70" s="17" t="inlineStr"/>
+      <c r="I70" s="17" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="J70" s="15" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="K70" s="17" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L70" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M70" s="17" t="n">
+        <v>117</v>
+      </c>
+      <c r="N70" s="17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="O70" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P70" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>✅ Adrian Mannarino  +4.5</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>Damir Dzumhur</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G71" s="13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H71" s="12" t="inlineStr"/>
+      <c r="I71" s="12" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="J71" s="15" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="K71" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L71" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M71" s="12" t="n">
+        <v>178</v>
+      </c>
+      <c r="N71" s="12" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O71" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P71" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B72" s="17" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>✅ Eva Lys  +3.5</t>
+        </is>
+      </c>
+      <c r="D72" s="17" t="inlineStr">
+        <is>
+          <t>Katie Boulter</t>
+        </is>
+      </c>
+      <c r="E72" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F72" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G72" s="18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H72" s="17" t="inlineStr"/>
+      <c r="I72" s="17" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="J72" s="15" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="K72" s="17" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L72" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M72" s="17" t="n">
+        <v>123</v>
+      </c>
+      <c r="N72" s="17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O72" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P72" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>✅ Alexandra Eala  +0.5</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>Magdalena Frech</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G73" s="13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H73" s="12" t="inlineStr"/>
+      <c r="I73" s="12" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="J73" s="15" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="K73" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L73" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M73" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="N73" s="12" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="O73" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P73" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B74" s="17" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>✅ Giovanni Mpetshi Perricard  +2.5</t>
+        </is>
+      </c>
+      <c r="D74" s="17" t="inlineStr">
+        <is>
+          <t>Jacob Fearnley</t>
+        </is>
+      </c>
+      <c r="E74" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F74" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G74" s="18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H74" s="17" t="inlineStr"/>
+      <c r="I74" s="17" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="J74" s="15" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="K74" s="17" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L74" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M74" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="N74" s="17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="O74" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.6/0.0)</t>
+        </is>
+      </c>
+      <c r="P74" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>✅ Roberto Bautista Agut  -2.5</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>Francesco Maestrelli</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F75" s="12" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="G75" s="13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H75" s="12" t="inlineStr"/>
+      <c r="I75" s="12" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="J75" s="15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K75" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L75" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M75" s="12" t="n">
+        <v>332</v>
+      </c>
+      <c r="N75" s="12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O75" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P75" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B76" s="17" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>✅ Janice Tjen  -1.5</t>
+        </is>
+      </c>
+      <c r="D76" s="17" t="inlineStr">
+        <is>
+          <t>Peyton Stearns</t>
+        </is>
+      </c>
+      <c r="E76" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F76" s="17" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="G76" s="18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H76" s="17" t="inlineStr"/>
+      <c r="I76" s="17" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J76" s="15" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="K76" s="17" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L76" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M76" s="17" t="n">
+        <v>128</v>
+      </c>
+      <c r="N76" s="17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O76" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P76" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>✅ Laura Siegemund  +3.5</t>
+        </is>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>Sara Bejlek</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F77" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G77" s="13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H77" s="12" t="inlineStr"/>
+      <c r="I77" s="12" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="J77" s="15" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K77" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L77" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M77" s="12" t="n">
+        <v>152</v>
+      </c>
+      <c r="N77" s="12" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O77" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P77" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B78" s="17" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>✅ Alexander Shevchenko  +3.5</t>
+        </is>
+      </c>
+      <c r="D78" s="17" t="inlineStr">
+        <is>
+          <t>Camilo Ugo Carabelli</t>
+        </is>
+      </c>
+      <c r="E78" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F78" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G78" s="18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H78" s="17" t="inlineStr"/>
+      <c r="I78" s="17" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="J78" s="15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="K78" s="17" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L78" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M78" s="17" t="n">
+        <v>154</v>
+      </c>
+      <c r="N78" s="17" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="O78" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P78" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>✅ Jesper De Jong  +0.5</t>
+        </is>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>Nuno Borges</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F79" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G79" s="13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H79" s="12" t="inlineStr"/>
+      <c r="I79" s="12" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="J79" s="15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K79" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L79" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M79" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="N79" s="12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="O79" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.6/0.0)</t>
+        </is>
+      </c>
+      <c r="P79" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B80" s="17" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>✅ Rio Noguchi  +1.5</t>
+        </is>
+      </c>
+      <c r="D80" s="17" t="inlineStr">
+        <is>
+          <t>Fajing Sun</t>
+        </is>
+      </c>
+      <c r="E80" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F80" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G80" s="18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H80" s="17" t="inlineStr"/>
+      <c r="I80" s="17" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="J80" s="15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K80" s="17" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Wuxi, China Men Singles</t>
+        </is>
+      </c>
+      <c r="L80" s="17" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="M80" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="N80" s="17" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="O80" s="17" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="P80" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t>02:38</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>✅ Gianluca Cadenasso  +2.5</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>Thiago Agustin Tirante</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F81" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G81" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H81" s="12" t="inlineStr"/>
+      <c r="I81" s="12" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="J81" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K81" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L81" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M81" s="12" t="n">
+        <v>135</v>
+      </c>
+      <c r="N81" s="12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O81" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P81" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>03:06</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>✅ Sinja Kraus  +2.5</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>Elisabetta Cocciaretto</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F82" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G82" s="13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H82" s="12" t="inlineStr"/>
+      <c r="I82" s="12" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="J82" s="9" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="K82" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L82" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M82" s="12" t="n">
+        <v>160</v>
+      </c>
+      <c r="N82" s="12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O82" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.6)</t>
+        </is>
+      </c>
+      <c r="P82" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t>03:06</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>✅ Ann Li  +1.5</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>Liudmila Samsonova</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F83" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G83" s="13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H83" s="12" t="inlineStr"/>
+      <c r="I83" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="K83" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L83" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M83" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="N83" s="12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="O83" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="P83" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B84" s="17" t="inlineStr">
+        <is>
+          <t>03:06</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>✅ Noemi Basiletti  +5.5</t>
+        </is>
+      </c>
+      <c r="D84" s="17" t="inlineStr">
+        <is>
+          <t>Ajla Tomljanovic</t>
+        </is>
+      </c>
+      <c r="E84" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F84" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G84" s="18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H84" s="17" t="inlineStr"/>
+      <c r="I84" s="17" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="J84" s="14" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="K84" s="17" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L84" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M84" s="17" t="n">
+        <v>195</v>
+      </c>
+      <c r="N84" s="17" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="O84" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.6/-0.6)</t>
+        </is>
+      </c>
+      <c r="P84" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>03:06</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>✅ Dalma Galfi  +4.5</t>
+        </is>
+      </c>
+      <c r="D85" s="17" t="inlineStr">
+        <is>
+          <t>Anastasia Potapova</t>
+        </is>
+      </c>
+      <c r="E85" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F85" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G85" s="18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H85" s="17" t="inlineStr"/>
+      <c r="I85" s="17" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="J85" s="14" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="K85" s="17" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L85" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M85" s="17" t="n">
+        <v>165</v>
+      </c>
+      <c r="N85" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O85" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.6/-0.6)</t>
+        </is>
+      </c>
+      <c r="P85" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B86" s="12" t="inlineStr">
+        <is>
+          <t>03:06</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>✅ Lilli Tagger  +2.5</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>Maria Sakkari</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F86" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G86" s="13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H86" s="12" t="inlineStr"/>
+      <c r="I86" s="12" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="J86" s="14" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="K86" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L86" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M86" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="N86" s="12" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="O86" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.6/0.0)</t>
+        </is>
+      </c>
+      <c r="P86" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>03:45</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>✅ Stefanos Tsitsipas  +0.0</t>
+        </is>
+      </c>
+      <c r="D87" s="17" t="inlineStr">
+        <is>
+          <t>Tomas Machac</t>
+        </is>
+      </c>
+      <c r="E87" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F87" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H87" s="17" t="inlineStr"/>
+      <c r="I87" s="17" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="J87" s="14" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="K87" s="17" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L87" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M87" s="17" t="n">
+        <v>149</v>
+      </c>
+      <c r="N87" s="17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O87" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P87" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="1"/>
+    <row r="89" ht="22" customHeight="1"/>
+    <row r="90" ht="22" customHeight="1"/>
+    <row r="91" ht="22" customHeight="1"/>
+    <row r="92" ht="22" customHeight="1"/>
+    <row r="93" ht="22" customHeight="1"/>
+    <row r="94" ht="22" customHeight="1"/>
+    <row r="95" ht="22" customHeight="1"/>
+    <row r="96" ht="22" customHeight="1"/>
+    <row r="97" ht="22" customHeight="1"/>
+    <row r="98" ht="22" customHeight="1"/>
+    <row r="99" ht="22" customHeight="1"/>
+    <row r="100" ht="22" customHeight="1"/>
+    <row r="101" ht="22" customHeight="1"/>
+    <row r="102" ht="22" customHeight="1"/>
+    <row r="103" ht="22" customHeight="1"/>
+    <row r="104" ht="22" customHeight="1"/>
+    <row r="105" ht="22" customHeight="1"/>
+    <row r="106" ht="22" customHeight="1"/>
+    <row r="107" ht="22" customHeight="1"/>
+    <row r="108" ht="22" customHeight="1"/>
+    <row r="109" ht="22" customHeight="1"/>
+    <row r="110" ht="22" customHeight="1"/>
+    <row r="111" ht="22" customHeight="1"/>
+    <row r="112" ht="22" customHeight="1"/>
+    <row r="113" ht="22" customHeight="1"/>
+    <row r="114" ht="22" customHeight="1"/>
+    <row r="115" ht="22" customHeight="1"/>
+    <row r="116" ht="22" customHeight="1"/>
+    <row r="117" ht="22" customHeight="1"/>
+    <row r="118" ht="22" customHeight="1"/>
+    <row r="119" ht="22" customHeight="1"/>
+    <row r="120" ht="22" customHeight="1"/>
+    <row r="121" ht="22" customHeight="1"/>
+    <row r="122" ht="22" customHeight="1"/>
+    <row r="123" ht="22" customHeight="1"/>
+    <row r="124" ht="22" customHeight="1"/>
+    <row r="125" ht="22" customHeight="1"/>
+    <row r="126" ht="22" customHeight="1"/>
+    <row r="127" ht="22" customHeight="1"/>
+    <row r="128" ht="22" customHeight="1"/>
+    <row r="129" ht="22" customHeight="1"/>
+    <row r="130" ht="22" customHeight="1"/>
+    <row r="131" ht="22" customHeight="1"/>
+    <row r="132" ht="22" customHeight="1"/>
+    <row r="133" ht="22" customHeight="1"/>
+    <row r="134" ht="22" customHeight="1"/>
+    <row r="135" ht="22" customHeight="1"/>
+    <row r="136" ht="22" customHeight="1"/>
+    <row r="137" ht="22" customHeight="1"/>
+    <row r="138" ht="22" customHeight="1"/>
+    <row r="139" ht="22" customHeight="1"/>
+    <row r="140" ht="22" customHeight="1"/>
+    <row r="141" ht="22" customHeight="1"/>
+    <row r="142" ht="22" customHeight="1"/>
+    <row r="143" ht="22" customHeight="1"/>
+    <row r="144" ht="22" customHeight="1"/>
+    <row r="145" ht="22" customHeight="1"/>
+    <row r="146" ht="22" customHeight="1"/>
+    <row r="147" ht="22" customHeight="1"/>
+    <row r="148" ht="22" customHeight="1"/>
+    <row r="149" ht="22" customHeight="1"/>
+    <row r="150" ht="22" customHeight="1"/>
+    <row r="151" ht="22" customHeight="1"/>
+    <row r="152" ht="22" customHeight="1"/>
+    <row r="153" ht="22" customHeight="1"/>
+    <row r="154" ht="22" customHeight="1"/>
+    <row r="155" ht="22" customHeight="1"/>
+    <row r="156" ht="22" customHeight="1"/>
+    <row r="157" ht="22" customHeight="1"/>
+    <row r="158" ht="22" customHeight="1"/>
+    <row r="159" ht="22" customHeight="1"/>
+    <row r="160" ht="22" customHeight="1"/>
+    <row r="161" ht="22" customHeight="1"/>
+    <row r="162" ht="22" customHeight="1"/>
+    <row r="163" ht="22" customHeight="1"/>
+    <row r="164" ht="22" customHeight="1"/>
+    <row r="165" ht="22" customHeight="1"/>
+    <row r="166" ht="22" customHeight="1"/>
+    <row r="167" ht="22" customHeight="1"/>
+    <row r="168" ht="22" customHeight="1"/>
+    <row r="169" ht="22" customHeight="1"/>
+    <row r="170" ht="22" customHeight="1"/>
+    <row r="171" ht="22" customHeight="1"/>
+    <row r="172" ht="22" customHeight="1"/>
+    <row r="173" ht="22" customHeight="1"/>
+    <row r="174" ht="22" customHeight="1"/>
+    <row r="175" ht="22" customHeight="1"/>
+    <row r="176" ht="22" customHeight="1"/>
+    <row r="177" ht="22" customHeight="1"/>
+    <row r="178" ht="22" customHeight="1"/>
+    <row r="179" ht="22" customHeight="1"/>
+    <row r="180" ht="22" customHeight="1"/>
+    <row r="181" ht="22" customHeight="1"/>
+    <row r="182" ht="22" customHeight="1"/>
+    <row r="183" ht="22" customHeight="1"/>
+    <row r="184" ht="22" customHeight="1"/>
+    <row r="185" ht="22" customHeight="1"/>
+    <row r="186" ht="22" customHeight="1"/>
+    <row r="187" ht="22" customHeight="1"/>
+    <row r="188" ht="22" customHeight="1"/>
+    <row r="189" ht="22" customHeight="1"/>
+    <row r="190" ht="22" customHeight="1"/>
+    <row r="191" ht="22" customHeight="1"/>
+    <row r="192" ht="22" customHeight="1"/>
+    <row r="193" ht="22" customHeight="1"/>
+    <row r="194" ht="22" customHeight="1"/>
+    <row r="195" ht="22" customHeight="1"/>
+    <row r="196" ht="22" customHeight="1"/>
+    <row r="197" ht="22" customHeight="1"/>
+    <row r="198" ht="22" customHeight="1"/>
+    <row r="199" ht="22" customHeight="1"/>
+    <row r="200" ht="22" customHeight="1"/>
+    <row r="201" ht="22" customHeight="1"/>
+    <row r="202" ht="22" customHeight="1"/>
+    <row r="203" ht="22" customHeight="1"/>
+    <row r="204" ht="22" customHeight="1"/>
+    <row r="205" ht="22" customHeight="1"/>
+    <row r="206" ht="22" customHeight="1"/>
+    <row r="207" ht="22" customHeight="1"/>
+    <row r="208" ht="22" customHeight="1"/>
+    <row r="209" ht="22" customHeight="1"/>
+    <row r="210" ht="22" customHeight="1"/>
+    <row r="211" ht="22" customHeight="1"/>
+    <row r="212" ht="22" customHeight="1"/>
+    <row r="213" ht="22" customHeight="1"/>
+    <row r="214" ht="22" customHeight="1"/>
+    <row r="215" ht="22" customHeight="1"/>
+    <row r="216" ht="22" customHeight="1"/>
+    <row r="217" ht="22" customHeight="1"/>
+    <row r="218" ht="22" customHeight="1"/>
+    <row r="219" ht="22" customHeight="1"/>
+    <row r="220" ht="22" customHeight="1"/>
+    <row r="221" ht="22" customHeight="1"/>
+    <row r="222" ht="22" customHeight="1"/>
+    <row r="223" ht="22" customHeight="1"/>
+    <row r="224" ht="22" customHeight="1"/>
+    <row r="225" ht="22" customHeight="1"/>
+    <row r="226" ht="22" customHeight="1"/>
+    <row r="227" ht="22" customHeight="1"/>
+    <row r="228" ht="22" customHeight="1"/>
+    <row r="229" ht="22" customHeight="1"/>
+    <row r="230" ht="22" customHeight="1"/>
+    <row r="231" ht="22" customHeight="1"/>
+    <row r="232" ht="22" customHeight="1"/>
+    <row r="233" ht="22" customHeight="1"/>
+    <row r="234" ht="22" customHeight="1"/>
+    <row r="235" ht="22" customHeight="1"/>
+    <row r="236" ht="22" customHeight="1"/>
+    <row r="237" ht="22" customHeight="1"/>
+    <row r="238" ht="22" customHeight="1"/>
+    <row r="239" ht="22" customHeight="1"/>
+    <row r="240" ht="22" customHeight="1"/>
+    <row r="241" ht="22" customHeight="1"/>
+    <row r="242" ht="22" customHeight="1"/>
+    <row r="243" ht="22" customHeight="1"/>
+    <row r="244" ht="22" customHeight="1"/>
+    <row r="245" ht="22" customHeight="1"/>
+    <row r="246" ht="22" customHeight="1"/>
+    <row r="247" ht="22" customHeight="1"/>
+    <row r="248" ht="22" customHeight="1"/>
+    <row r="249" ht="22" customHeight="1"/>
+    <row r="250" ht="22" customHeight="1"/>
+    <row r="251" ht="22" customHeight="1"/>
+    <row r="252" ht="22" customHeight="1"/>
+    <row r="253" ht="22" customHeight="1"/>
+    <row r="254" ht="22" customHeight="1"/>
+    <row r="255" ht="22" customHeight="1"/>
+    <row r="256" ht="22" customHeight="1"/>
+    <row r="257" ht="22" customHeight="1"/>
+    <row r="258" ht="22" customHeight="1"/>
+    <row r="259" ht="22" customHeight="1"/>
+    <row r="260" ht="22" customHeight="1"/>
+    <row r="261" ht="22" customHeight="1"/>
+    <row r="262" ht="22" customHeight="1"/>
+    <row r="263" ht="22" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/value_bets_log.xlsx
+++ b/data/value_bets_log.xlsx
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q96"/>
+  <dimension ref="A1:Q131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3293,8 +3293,14 @@
       </c>
       <c r="N42" s="10" t="inlineStr"/>
       <c r="O42" s="11" t="inlineStr"/>
-      <c r="P42" s="5" t="inlineStr"/>
-      <c r="Q42" s="5" t="inlineStr"/>
+      <c r="P42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q42" s="5" t="n">
+        <v>5.6</v>
+      </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="12" t="inlineStr">
@@ -3354,8 +3360,14 @@
       </c>
       <c r="N43" s="10" t="inlineStr"/>
       <c r="O43" s="11" t="inlineStr"/>
-      <c r="P43" s="12" t="inlineStr"/>
-      <c r="Q43" s="12" t="inlineStr"/>
+      <c r="P43" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q43" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
@@ -3476,8 +3488,14 @@
       </c>
       <c r="N45" s="10" t="inlineStr"/>
       <c r="O45" s="11" t="inlineStr"/>
-      <c r="P45" s="12" t="inlineStr"/>
-      <c r="Q45" s="12" t="inlineStr"/>
+      <c r="P45" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q45" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
@@ -3659,8 +3677,14 @@
       </c>
       <c r="N48" s="10" t="inlineStr"/>
       <c r="O48" s="11" t="inlineStr"/>
-      <c r="P48" s="5" t="inlineStr"/>
-      <c r="Q48" s="5" t="inlineStr"/>
+      <c r="P48" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q48" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="12" t="inlineStr">
@@ -4147,8 +4171,14 @@
       </c>
       <c r="N56" s="10" t="inlineStr"/>
       <c r="O56" s="11" t="inlineStr"/>
-      <c r="P56" s="5" t="inlineStr"/>
-      <c r="Q56" s="5" t="inlineStr"/>
+      <c r="P56" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q56" s="5" t="n">
+        <v>1.27</v>
+      </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="12" t="inlineStr">
@@ -4452,8 +4482,14 @@
       </c>
       <c r="N61" s="10" t="inlineStr"/>
       <c r="O61" s="11" t="inlineStr"/>
-      <c r="P61" s="12" t="inlineStr"/>
-      <c r="Q61" s="12" t="inlineStr"/>
+      <c r="P61" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q61" s="12" t="n">
+        <v>0.28</v>
+      </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="5" t="inlineStr">
@@ -4574,8 +4610,14 @@
       </c>
       <c r="N63" s="10" t="inlineStr"/>
       <c r="O63" s="11" t="inlineStr"/>
-      <c r="P63" s="12" t="inlineStr"/>
-      <c r="Q63" s="12" t="inlineStr"/>
+      <c r="P63" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q63" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
@@ -4635,8 +4677,14 @@
       </c>
       <c r="N64" s="10" t="inlineStr"/>
       <c r="O64" s="11" t="inlineStr"/>
-      <c r="P64" s="5" t="inlineStr"/>
-      <c r="Q64" s="5" t="inlineStr"/>
+      <c r="P64" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q64" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="12" t="inlineStr">
@@ -4696,8 +4744,14 @@
       </c>
       <c r="N65" s="10" t="inlineStr"/>
       <c r="O65" s="11" t="inlineStr"/>
-      <c r="P65" s="12" t="inlineStr"/>
-      <c r="Q65" s="12" t="inlineStr"/>
+      <c r="P65" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q65" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
@@ -5001,8 +5055,14 @@
       </c>
       <c r="N70" s="10" t="inlineStr"/>
       <c r="O70" s="11" t="inlineStr"/>
-      <c r="P70" s="5" t="inlineStr"/>
-      <c r="Q70" s="5" t="inlineStr"/>
+      <c r="P70" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q70" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="12" t="inlineStr">
@@ -5062,8 +5122,14 @@
       </c>
       <c r="N71" s="10" t="inlineStr"/>
       <c r="O71" s="11" t="inlineStr"/>
-      <c r="P71" s="12" t="inlineStr"/>
-      <c r="Q71" s="12" t="inlineStr"/>
+      <c r="P71" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q71" s="12" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
@@ -5123,8 +5189,14 @@
       </c>
       <c r="N72" s="10" t="inlineStr"/>
       <c r="O72" s="11" t="inlineStr"/>
-      <c r="P72" s="5" t="inlineStr"/>
-      <c r="Q72" s="5" t="inlineStr"/>
+      <c r="P72" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q72" s="5" t="n">
+        <v>0.32</v>
+      </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="12" t="inlineStr">
@@ -5306,8 +5378,14 @@
       </c>
       <c r="N75" s="10" t="inlineStr"/>
       <c r="O75" s="11" t="inlineStr"/>
-      <c r="P75" s="12" t="inlineStr"/>
-      <c r="Q75" s="12" t="inlineStr"/>
+      <c r="P75" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q75" s="12" t="n">
+        <v>1.37</v>
+      </c>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
@@ -5428,8 +5506,14 @@
       </c>
       <c r="N77" s="10" t="inlineStr"/>
       <c r="O77" s="11" t="inlineStr"/>
-      <c r="P77" s="12" t="inlineStr"/>
-      <c r="Q77" s="12" t="inlineStr"/>
+      <c r="P77" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q77" s="12" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="5" t="inlineStr">
@@ -5611,8 +5695,14 @@
       </c>
       <c r="N80" s="10" t="inlineStr"/>
       <c r="O80" s="11" t="inlineStr"/>
-      <c r="P80" s="5" t="inlineStr"/>
-      <c r="Q80" s="5" t="inlineStr"/>
+      <c r="P80" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q80" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="12" t="inlineStr">
@@ -5855,8 +5945,14 @@
       </c>
       <c r="N84" s="10" t="inlineStr"/>
       <c r="O84" s="11" t="inlineStr"/>
-      <c r="P84" s="5" t="inlineStr"/>
-      <c r="Q84" s="5" t="inlineStr"/>
+      <c r="P84" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q84" s="5" t="n">
+        <v>0.53</v>
+      </c>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="12" t="inlineStr">
@@ -5916,8 +6012,14 @@
       </c>
       <c r="N85" s="10" t="inlineStr"/>
       <c r="O85" s="11" t="inlineStr"/>
-      <c r="P85" s="12" t="inlineStr"/>
-      <c r="Q85" s="12" t="inlineStr"/>
+      <c r="P85" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q85" s="12" t="n">
+        <v>0.36</v>
+      </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
@@ -6099,8 +6201,14 @@
       </c>
       <c r="N88" s="10" t="inlineStr"/>
       <c r="O88" s="11" t="inlineStr"/>
-      <c r="P88" s="5" t="inlineStr"/>
-      <c r="Q88" s="5" t="inlineStr"/>
+      <c r="P88" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q88" s="5" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="12" t="inlineStr">
@@ -6343,8 +6451,14 @@
       </c>
       <c r="N92" s="10" t="inlineStr"/>
       <c r="O92" s="11" t="inlineStr"/>
-      <c r="P92" s="5" t="inlineStr"/>
-      <c r="Q92" s="5" t="inlineStr"/>
+      <c r="P92" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q92" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="12" t="inlineStr">
@@ -6587,44 +6701,2150 @@
       </c>
       <c r="N96" s="10" t="inlineStr"/>
       <c r="O96" s="11" t="inlineStr"/>
-      <c r="P96" s="12" t="inlineStr"/>
-      <c r="Q96" s="12" t="inlineStr"/>
-    </row>
-    <row r="97" ht="22" customHeight="1"/>
-    <row r="98" ht="22" customHeight="1"/>
-    <row r="99" ht="22" customHeight="1"/>
-    <row r="100" ht="22" customHeight="1"/>
-    <row r="101" ht="22" customHeight="1"/>
-    <row r="102" ht="22" customHeight="1"/>
-    <row r="103" ht="22" customHeight="1"/>
-    <row r="104" ht="22" customHeight="1"/>
-    <row r="105" ht="22" customHeight="1"/>
-    <row r="106" ht="22" customHeight="1"/>
-    <row r="107" ht="22" customHeight="1"/>
-    <row r="108" ht="22" customHeight="1"/>
-    <row r="109" ht="22" customHeight="1"/>
-    <row r="110" ht="22" customHeight="1"/>
-    <row r="111" ht="22" customHeight="1"/>
-    <row r="112" ht="22" customHeight="1"/>
-    <row r="113" ht="22" customHeight="1"/>
-    <row r="114" ht="22" customHeight="1"/>
-    <row r="115" ht="22" customHeight="1"/>
-    <row r="116" ht="22" customHeight="1"/>
-    <row r="117" ht="22" customHeight="1"/>
-    <row r="118" ht="22" customHeight="1"/>
-    <row r="119" ht="22" customHeight="1"/>
-    <row r="120" ht="22" customHeight="1"/>
-    <row r="121" ht="22" customHeight="1"/>
-    <row r="122" ht="22" customHeight="1"/>
-    <row r="123" ht="22" customHeight="1"/>
-    <row r="124" ht="22" customHeight="1"/>
-    <row r="125" ht="22" customHeight="1"/>
-    <row r="126" ht="22" customHeight="1"/>
-    <row r="127" ht="22" customHeight="1"/>
-    <row r="128" ht="22" customHeight="1"/>
-    <row r="129" ht="22" customHeight="1"/>
-    <row r="130" ht="22" customHeight="1"/>
-    <row r="131" ht="22" customHeight="1"/>
+      <c r="P96" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q96" s="12" t="n">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="97" ht="22" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>✅ Caty McNally</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Iga Swiatek</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H97" s="8" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="K97" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L97" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M97" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="N97" s="10" t="inlineStr"/>
+      <c r="O97" s="11" t="inlineStr"/>
+      <c r="P97" s="5" t="inlineStr"/>
+      <c r="Q97" s="5" t="inlineStr"/>
+    </row>
+    <row r="98" ht="22" customHeight="1">
+      <c r="A98" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B98" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>✅ Matteo Arnaldi</t>
+        </is>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>Alex de Minaur</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F98" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G98" s="13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H98" s="8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I98" s="12" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="J98" s="9" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="K98" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L98" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M98" s="13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N98" s="10" t="inlineStr"/>
+      <c r="O98" s="11" t="inlineStr"/>
+      <c r="P98" s="12" t="inlineStr"/>
+      <c r="Q98" s="12" t="inlineStr"/>
+    </row>
+    <row r="99" ht="22" customHeight="1">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>✅ Damir Dzumhur</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Learner Tien</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="H99" s="8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="J99" s="9" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="K99" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L99" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M99" s="7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="N99" s="10" t="inlineStr"/>
+      <c r="O99" s="11" t="inlineStr"/>
+      <c r="P99" s="5" t="inlineStr"/>
+      <c r="Q99" s="5" t="inlineStr"/>
+    </row>
+    <row r="100" ht="22" customHeight="1">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>✅ Roberto Bautista Agut</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>Brandon Nakashima</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F100" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G100" s="13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H100" s="8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I100" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="K100" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L100" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M100" s="13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N100" s="10" t="inlineStr"/>
+      <c r="O100" s="11" t="inlineStr"/>
+      <c r="P100" s="12" t="inlineStr"/>
+      <c r="Q100" s="12" t="inlineStr"/>
+    </row>
+    <row r="101" ht="22" customHeight="1">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>✅ Oleksandra Oliynykova</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>Linda Noskova</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="H101" s="8" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="J101" s="9" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="K101" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="L101" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M101" s="7" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N101" s="10" t="inlineStr"/>
+      <c r="O101" s="11" t="inlineStr"/>
+      <c r="P101" s="5" t="inlineStr"/>
+      <c r="Q101" s="5" t="inlineStr"/>
+    </row>
+    <row r="102" ht="22" customHeight="1">
+      <c r="A102" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>✅ Rebeka Masarova</t>
+        </is>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>Leylah Fernandez</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F102" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G102" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H102" s="8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="I102" s="12" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="J102" s="14" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="K102" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L102" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M102" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="N102" s="10" t="inlineStr"/>
+      <c r="O102" s="11" t="inlineStr"/>
+      <c r="P102" s="12" t="inlineStr"/>
+      <c r="Q102" s="12" t="inlineStr"/>
+    </row>
+    <row r="103" ht="22" customHeight="1">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>✅ Pablo Llamas Ruiz</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>Corentin Moutet</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H103" s="8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="J103" s="14" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="K103" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L103" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M103" s="7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="N103" s="10" t="inlineStr"/>
+      <c r="O103" s="11" t="inlineStr"/>
+      <c r="P103" s="5" t="inlineStr"/>
+      <c r="Q103" s="5" t="inlineStr"/>
+    </row>
+    <row r="104" ht="22" customHeight="1">
+      <c r="A104" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>✅ Ann Li</t>
+        </is>
+      </c>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>Liudmila Samsonova</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F104" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G104" s="13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H104" s="8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I104" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="J104" s="14" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="K104" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L104" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M104" s="13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N104" s="10" t="inlineStr"/>
+      <c r="O104" s="11" t="inlineStr"/>
+      <c r="P104" s="12" t="inlineStr"/>
+      <c r="Q104" s="12" t="inlineStr"/>
+    </row>
+    <row r="105" ht="22" customHeight="1">
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>✅ Talia Gibson</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>Diana Shnaider</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H105" s="8" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="J105" s="14" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="K105" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L105" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M105" s="7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N105" s="10" t="inlineStr"/>
+      <c r="O105" s="11" t="inlineStr"/>
+      <c r="P105" s="5" t="inlineStr"/>
+      <c r="Q105" s="5" t="inlineStr"/>
+    </row>
+    <row r="106" ht="22" customHeight="1">
+      <c r="A106" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>✅ Miguel Tobon</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>Matheus Pucinelli de Almeida</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Santos, Brazil Men Singles</t>
+        </is>
+      </c>
+      <c r="F106" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G106" s="13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H106" s="8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="I106" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="J106" s="14" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="K106" s="12" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.6/-0.3)</t>
+        </is>
+      </c>
+      <c r="L106" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M106" s="13" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="N106" s="10" t="inlineStr"/>
+      <c r="O106" s="11" t="inlineStr"/>
+      <c r="P106" s="12" t="inlineStr"/>
+      <c r="Q106" s="12" t="inlineStr"/>
+    </row>
+    <row r="107" ht="22" customHeight="1">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>✅ Anastasia Potapova</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>Karolina Muchova</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H107" s="8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="J107" s="14" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="K107" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L107" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M107" s="7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N107" s="10" t="inlineStr"/>
+      <c r="O107" s="11" t="inlineStr"/>
+      <c r="P107" s="5" t="inlineStr"/>
+      <c r="Q107" s="5" t="inlineStr"/>
+    </row>
+    <row r="108" ht="22" customHeight="1">
+      <c r="A108" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>✅ Simona Waltert</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>Hailey Baptiste</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F108" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G108" s="13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="H108" s="8" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I108" s="12" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="J108" s="14" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="K108" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L108" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M108" s="13" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N108" s="10" t="inlineStr"/>
+      <c r="O108" s="11" t="inlineStr"/>
+      <c r="P108" s="12" t="inlineStr"/>
+      <c r="Q108" s="12" t="inlineStr"/>
+    </row>
+    <row r="109" ht="22" customHeight="1">
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>✅ Eva Lys</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>Naomi Osaka</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H109" s="8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="J109" s="14" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="K109" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L109" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M109" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N109" s="10" t="inlineStr"/>
+      <c r="O109" s="11" t="inlineStr"/>
+      <c r="P109" s="5" t="inlineStr"/>
+      <c r="Q109" s="5" t="inlineStr"/>
+    </row>
+    <row r="110" ht="22" customHeight="1">
+      <c r="A110" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B110" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>✅ Aleksandar Vukic</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>Tommy Paul</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F110" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G110" s="13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H110" s="8" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="I110" s="12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="J110" s="14" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="K110" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L110" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M110" s="13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N110" s="10" t="inlineStr"/>
+      <c r="O110" s="11" t="inlineStr"/>
+      <c r="P110" s="12" t="inlineStr"/>
+      <c r="Q110" s="12" t="inlineStr"/>
+    </row>
+    <row r="111" ht="22" customHeight="1">
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>✅ Maria Sakkari</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>Elena Rybakina</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H111" s="8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J111" s="14" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="K111" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L111" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M111" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="N111" s="10" t="inlineStr"/>
+      <c r="O111" s="11" t="inlineStr"/>
+      <c r="P111" s="5" t="inlineStr"/>
+      <c r="Q111" s="5" t="inlineStr"/>
+    </row>
+    <row r="112" ht="22" customHeight="1">
+      <c r="A112" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>✅ Giovanni Mpetshi Perricard</t>
+        </is>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>Lorenzo Musetti</t>
+        </is>
+      </c>
+      <c r="E112" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F112" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G112" s="13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H112" s="8" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="I112" s="12" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="J112" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="K112" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+h2h(+0.32)+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L112" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M112" s="13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N112" s="10" t="inlineStr"/>
+      <c r="O112" s="11" t="inlineStr"/>
+      <c r="P112" s="12" t="inlineStr"/>
+      <c r="Q112" s="12" t="inlineStr"/>
+    </row>
+    <row r="113" ht="22" customHeight="1">
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>✅ Alejandro Tabilo</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>Francisco Cerundolo</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="H113" s="8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="J113" s="14" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="K113" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L113" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M113" s="7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="N113" s="10" t="inlineStr"/>
+      <c r="O113" s="11" t="inlineStr"/>
+      <c r="P113" s="5" t="inlineStr"/>
+      <c r="Q113" s="5" t="inlineStr"/>
+    </row>
+    <row r="114" ht="22" customHeight="1">
+      <c r="A114" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B114" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>✅ Franco Roncadelli</t>
+        </is>
+      </c>
+      <c r="D114" s="12" t="inlineStr">
+        <is>
+          <t>Joao Eduardo Schiessl</t>
+        </is>
+      </c>
+      <c r="E114" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Santos, Brazil Men Singles</t>
+        </is>
+      </c>
+      <c r="F114" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G114" s="13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H114" s="8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="I114" s="12" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="J114" s="14" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="K114" s="12" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L114" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M114" s="13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="N114" s="10" t="inlineStr"/>
+      <c r="O114" s="11" t="inlineStr"/>
+      <c r="P114" s="12" t="inlineStr"/>
+      <c r="Q114" s="12" t="inlineStr"/>
+    </row>
+    <row r="115" ht="22" customHeight="1">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>✅ Alexei Popyrin</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>Jakub Mensik</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H115" s="8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="J115" s="14" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="K115" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L115" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M115" s="7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N115" s="10" t="inlineStr"/>
+      <c r="O115" s="11" t="inlineStr"/>
+      <c r="P115" s="5" t="inlineStr"/>
+      <c r="Q115" s="5" t="inlineStr"/>
+    </row>
+    <row r="116" ht="22" customHeight="1">
+      <c r="A116" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B116" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>✅ Yannick Hanfmann</t>
+        </is>
+      </c>
+      <c r="D116" s="12" t="inlineStr">
+        <is>
+          <t>Luciano Darderi</t>
+        </is>
+      </c>
+      <c r="E116" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F116" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G116" s="13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="H116" s="8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I116" s="12" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="J116" s="14" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="K116" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L116" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M116" s="13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N116" s="10" t="inlineStr"/>
+      <c r="O116" s="11" t="inlineStr"/>
+      <c r="P116" s="12" t="inlineStr"/>
+      <c r="Q116" s="12" t="inlineStr"/>
+    </row>
+    <row r="117" ht="22" customHeight="1">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>✅ Jasmine Paolini</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>Elise Mertens</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H117" s="8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="J117" s="14" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="K117" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="L117" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M117" s="7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N117" s="10" t="inlineStr"/>
+      <c r="O117" s="11" t="inlineStr"/>
+      <c r="P117" s="5" t="inlineStr"/>
+      <c r="Q117" s="5" t="inlineStr"/>
+    </row>
+    <row r="118" ht="22" customHeight="1">
+      <c r="A118" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B118" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>✅ Zeynep Sonmez</t>
+        </is>
+      </c>
+      <c r="D118" s="12" t="inlineStr">
+        <is>
+          <t>Jessica Pegula</t>
+        </is>
+      </c>
+      <c r="E118" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F118" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G118" s="13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="H118" s="8" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="I118" s="12" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="J118" s="14" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="K118" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L118" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M118" s="13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N118" s="10" t="inlineStr"/>
+      <c r="O118" s="11" t="inlineStr"/>
+      <c r="P118" s="12" t="inlineStr"/>
+      <c r="Q118" s="12" t="inlineStr"/>
+    </row>
+    <row r="119" ht="22" customHeight="1">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>✅ Rio Noguchi</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>Jie Cui</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Wuxi, China Men Singles</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="H119" s="8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="J119" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="K119" s="5" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="L119" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M119" s="7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="N119" s="10" t="inlineStr"/>
+      <c r="O119" s="11" t="inlineStr"/>
+      <c r="P119" s="5" t="inlineStr"/>
+      <c r="Q119" s="5" t="inlineStr"/>
+    </row>
+    <row r="120" ht="22" customHeight="1">
+      <c r="A120" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B120" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>✅ Karolina Pliskova</t>
+        </is>
+      </c>
+      <c r="D120" s="12" t="inlineStr">
+        <is>
+          <t>Jaqueline Cristian</t>
+        </is>
+      </c>
+      <c r="E120" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F120" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G120" s="13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H120" s="8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I120" s="12" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="J120" s="14" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="K120" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L120" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M120" s="13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="N120" s="10" t="inlineStr"/>
+      <c r="O120" s="11" t="inlineStr"/>
+      <c r="P120" s="12" t="inlineStr"/>
+      <c r="Q120" s="12" t="inlineStr"/>
+    </row>
+    <row r="121" ht="22" customHeight="1">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>✅ Noemi Basiletti</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>Elina Svitolina</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H121" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="I121" s="5" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J121" s="14" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="K121" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L121" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M121" s="7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="N121" s="10" t="inlineStr"/>
+      <c r="O121" s="11" t="inlineStr"/>
+      <c r="P121" s="5" t="inlineStr"/>
+      <c r="Q121" s="5" t="inlineStr"/>
+    </row>
+    <row r="122" ht="22" customHeight="1">
+      <c r="A122" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B122" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>✅ Vit Kopriva</t>
+        </is>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>Ugo Humbert</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F122" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G122" s="13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H122" s="8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="I122" s="12" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="J122" s="14" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="K122" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L122" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M122" s="13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N122" s="10" t="inlineStr"/>
+      <c r="O122" s="11" t="inlineStr"/>
+      <c r="P122" s="12" t="inlineStr"/>
+      <c r="Q122" s="12" t="inlineStr"/>
+    </row>
+    <row r="123" ht="22" customHeight="1">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>✅ Alexander Blockx</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>Tallon Griekspoor</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H123" s="8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="J123" s="15" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="K123" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L123" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M123" s="7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="N123" s="10" t="inlineStr"/>
+      <c r="O123" s="11" t="inlineStr"/>
+      <c r="P123" s="5" t="inlineStr"/>
+      <c r="Q123" s="5" t="inlineStr"/>
+    </row>
+    <row r="124" ht="22" customHeight="1">
+      <c r="A124" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>✅ Alexander Shevchenko</t>
+        </is>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>Karen Khachanov</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F124" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G124" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H124" s="8" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="I124" s="12" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="J124" s="15" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="K124" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L124" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M124" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="N124" s="10" t="inlineStr"/>
+      <c r="O124" s="11" t="inlineStr"/>
+      <c r="P124" s="12" t="inlineStr"/>
+      <c r="Q124" s="12" t="inlineStr"/>
+    </row>
+    <row r="125" ht="22" customHeight="1">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>✅ Tyra Caterina Grant</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>Victoria Mboko</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H125" s="8" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="I125" s="5" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="J125" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="K125" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L125" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M125" s="7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N125" s="10" t="inlineStr"/>
+      <c r="O125" s="11" t="inlineStr"/>
+      <c r="P125" s="5" t="inlineStr"/>
+      <c r="Q125" s="5" t="inlineStr"/>
+    </row>
+    <row r="126" ht="22" customHeight="1">
+      <c r="A126" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B126" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>✅ Anna Kalinskaya</t>
+        </is>
+      </c>
+      <c r="D126" s="12" t="inlineStr">
+        <is>
+          <t>Belinda Bencic</t>
+        </is>
+      </c>
+      <c r="E126" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F126" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G126" s="13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H126" s="8" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="I126" s="12" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="J126" s="15" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="K126" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="L126" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M126" s="13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N126" s="10" t="inlineStr"/>
+      <c r="O126" s="11" t="inlineStr"/>
+      <c r="P126" s="12" t="inlineStr"/>
+      <c r="Q126" s="12" t="inlineStr"/>
+    </row>
+    <row r="127" ht="22" customHeight="1">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>✅ Jan-Lennard Struff</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>Jiri Lehecka</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="H127" s="8" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="I127" s="5" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J127" s="15" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="K127" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="L127" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M127" s="7" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="N127" s="10" t="inlineStr"/>
+      <c r="O127" s="11" t="inlineStr"/>
+      <c r="P127" s="5" t="inlineStr"/>
+      <c r="Q127" s="5" t="inlineStr"/>
+    </row>
+    <row r="128" ht="22" customHeight="1">
+      <c r="A128" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B128" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>✅ Botic Van de Zandschulp</t>
+        </is>
+      </c>
+      <c r="D128" s="12" t="inlineStr">
+        <is>
+          <t>Aleksandar Kovacevic</t>
+        </is>
+      </c>
+      <c r="E128" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F128" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G128" s="13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="H128" s="8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="I128" s="12" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="J128" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="K128" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L128" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M128" s="13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="N128" s="10" t="inlineStr"/>
+      <c r="O128" s="11" t="inlineStr"/>
+      <c r="P128" s="12" t="inlineStr"/>
+      <c r="Q128" s="12" t="inlineStr"/>
+    </row>
+    <row r="129" ht="22" customHeight="1">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>✅ Emma Navarro</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>Elisabetta Cocciaretto</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="H129" s="8" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="J129" s="15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="K129" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="L129" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M129" s="7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="N129" s="10" t="inlineStr"/>
+      <c r="O129" s="11" t="inlineStr"/>
+      <c r="P129" s="5" t="inlineStr"/>
+      <c r="Q129" s="5" t="inlineStr"/>
+    </row>
+    <row r="130" ht="22" customHeight="1">
+      <c r="A130" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B130" s="12" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>✅ Cristian Garin</t>
+        </is>
+      </c>
+      <c r="D130" s="12" t="inlineStr">
+        <is>
+          <t>Alejandro Davidovich Fokina</t>
+        </is>
+      </c>
+      <c r="E130" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F130" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G130" s="13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H130" s="8" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I130" s="12" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="J130" s="12" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="K130" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L130" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M130" s="13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N130" s="10" t="inlineStr"/>
+      <c r="O130" s="11" t="inlineStr"/>
+      <c r="P130" s="12" t="inlineStr"/>
+      <c r="Q130" s="12" t="inlineStr"/>
+    </row>
+    <row r="131" ht="22" customHeight="1">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>02:10</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>✅ Ben Shelton</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>Nikoloz Basilashvili</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H131" s="8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="I131" s="5" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="J131" s="5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K131" s="5" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="L131" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M131" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N131" s="10" t="inlineStr"/>
+      <c r="O131" s="11" t="inlineStr"/>
+      <c r="P131" s="5" t="inlineStr"/>
+      <c r="Q131" s="5" t="inlineStr"/>
+    </row>
     <row r="132" ht="22" customHeight="1"/>
     <row r="133" ht="22" customHeight="1"/>
     <row r="134" ht="22" customHeight="1"/>
@@ -6813,7 +9033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P87"/>
+  <dimension ref="A1:P129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12529,22 +14749,22 @@
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="17" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B87" s="17" t="inlineStr">
         <is>
-          <t>03:45</t>
+          <t>02:11</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>✅ Stefanos Tsitsipas  +0.0</t>
+          <t>✅ Matteo Arnaldi  +3.5</t>
         </is>
       </c>
       <c r="D87" s="17" t="inlineStr">
         <is>
-          <t>Tomas Machac</t>
+          <t>Alex de Minaur</t>
         </is>
       </c>
       <c r="E87" s="17" t="inlineStr">
@@ -12553,17 +14773,17 @@
         </is>
       </c>
       <c r="F87" s="17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="G87" s="18" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="H87" s="17" t="inlineStr"/>
       <c r="I87" s="17" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="J87" s="14" t="n">
-        <v>20.2</v>
+        <v>80.5</v>
+      </c>
+      <c r="J87" s="9" t="n">
+        <v>61</v>
       </c>
       <c r="K87" s="17" t="inlineStr">
         <is>
@@ -12576,64 +14796,2794 @@
         </is>
       </c>
       <c r="M87" s="17" t="n">
-        <v>149</v>
+        <v>41</v>
       </c>
       <c r="N87" s="17" t="n">
-        <v>2.34</v>
+        <v>0.63</v>
       </c>
       <c r="O87" s="17" t="inlineStr">
         <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="P87" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B88" s="12" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>✅ Damir Dzumhur  +2.5</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>Learner Tien</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F88" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G88" s="13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H88" s="12" t="inlineStr"/>
+      <c r="I88" s="12" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="J88" s="9" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="K88" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L88" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M88" s="12" t="n">
+        <v>155</v>
+      </c>
+      <c r="N88" s="12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O88" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="P88" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="1">
+      <c r="A89" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B89" s="17" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>✅ Roberto Bautista Agut  +2.5</t>
+        </is>
+      </c>
+      <c r="D89" s="17" t="inlineStr">
+        <is>
+          <t>Brandon Nakashima</t>
+        </is>
+      </c>
+      <c r="E89" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F89" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G89" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H89" s="17" t="inlineStr"/>
+      <c r="I89" s="17" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="J89" s="9" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="K89" s="17" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L89" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M89" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="N89" s="17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="O89" s="17" t="inlineStr">
+        <is>
           <t>TA-clay+forma</t>
         </is>
       </c>
-      <c r="P87" s="17" t="inlineStr">
-        <is>
-          <t>odds-api.io</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="22" customHeight="1"/>
-    <row r="89" ht="22" customHeight="1"/>
-    <row r="90" ht="22" customHeight="1"/>
-    <row r="91" ht="22" customHeight="1"/>
-    <row r="92" ht="22" customHeight="1"/>
-    <row r="93" ht="22" customHeight="1"/>
-    <row r="94" ht="22" customHeight="1"/>
-    <row r="95" ht="22" customHeight="1"/>
-    <row r="96" ht="22" customHeight="1"/>
-    <row r="97" ht="22" customHeight="1"/>
-    <row r="98" ht="22" customHeight="1"/>
-    <row r="99" ht="22" customHeight="1"/>
-    <row r="100" ht="22" customHeight="1"/>
-    <row r="101" ht="22" customHeight="1"/>
-    <row r="102" ht="22" customHeight="1"/>
-    <row r="103" ht="22" customHeight="1"/>
-    <row r="104" ht="22" customHeight="1"/>
-    <row r="105" ht="22" customHeight="1"/>
-    <row r="106" ht="22" customHeight="1"/>
-    <row r="107" ht="22" customHeight="1"/>
-    <row r="108" ht="22" customHeight="1"/>
-    <row r="109" ht="22" customHeight="1"/>
-    <row r="110" ht="22" customHeight="1"/>
-    <row r="111" ht="22" customHeight="1"/>
-    <row r="112" ht="22" customHeight="1"/>
-    <row r="113" ht="22" customHeight="1"/>
-    <row r="114" ht="22" customHeight="1"/>
-    <row r="115" ht="22" customHeight="1"/>
-    <row r="116" ht="22" customHeight="1"/>
-    <row r="117" ht="22" customHeight="1"/>
-    <row r="118" ht="22" customHeight="1"/>
-    <row r="119" ht="22" customHeight="1"/>
-    <row r="120" ht="22" customHeight="1"/>
-    <row r="121" ht="22" customHeight="1"/>
-    <row r="122" ht="22" customHeight="1"/>
-    <row r="123" ht="22" customHeight="1"/>
-    <row r="124" ht="22" customHeight="1"/>
-    <row r="125" ht="22" customHeight="1"/>
-    <row r="126" ht="22" customHeight="1"/>
-    <row r="127" ht="22" customHeight="1"/>
-    <row r="128" ht="22" customHeight="1"/>
-    <row r="129" ht="22" customHeight="1"/>
+      <c r="P89" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B90" s="12" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>✅ Rebeka Masarova  +3.5</t>
+        </is>
+      </c>
+      <c r="D90" s="12" t="inlineStr">
+        <is>
+          <t>Leylah Fernandez</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F90" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G90" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H90" s="12" t="inlineStr"/>
+      <c r="I90" s="12" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="J90" s="9" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="K90" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L90" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M90" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="N90" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="O90" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="P90" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B91" s="17" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>✅ Ann Li  +2.5</t>
+        </is>
+      </c>
+      <c r="D91" s="17" t="inlineStr">
+        <is>
+          <t>Liudmila Samsonova</t>
+        </is>
+      </c>
+      <c r="E91" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F91" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G91" s="18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H91" s="17" t="inlineStr"/>
+      <c r="I91" s="17" t="n">
+        <v>82</v>
+      </c>
+      <c r="J91" s="9" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="K91" s="17" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L91" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M91" s="17" t="n">
+        <v>115</v>
+      </c>
+      <c r="N91" s="17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O91" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P91" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="22" customHeight="1">
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B92" s="12" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>✅ Caty McNally  +6.5</t>
+        </is>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>Iga Swiatek</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F92" s="12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G92" s="13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H92" s="12" t="inlineStr"/>
+      <c r="I92" s="12" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="J92" s="9" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="K92" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L92" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M92" s="12" t="n">
+        <v>164</v>
+      </c>
+      <c r="N92" s="12" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O92" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="P92" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B93" s="17" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>✅ Simona Waltert  +3.5</t>
+        </is>
+      </c>
+      <c r="D93" s="17" t="inlineStr">
+        <is>
+          <t>Hailey Baptiste</t>
+        </is>
+      </c>
+      <c r="E93" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F93" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G93" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H93" s="17" t="inlineStr"/>
+      <c r="I93" s="17" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="J93" s="9" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="K93" s="17" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L93" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M93" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="N93" s="17" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="O93" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="P93" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>✅ Oleksandra Oliynykova  +5.5</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>Linda Noskova</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F94" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G94" s="13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H94" s="12" t="inlineStr"/>
+      <c r="I94" s="12" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="J94" s="9" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="K94" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L94" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M94" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="N94" s="12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O94" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="P94" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="22" customHeight="1">
+      <c r="A95" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B95" s="17" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>✅ Anastasia Potapova  +3.5</t>
+        </is>
+      </c>
+      <c r="D95" s="17" t="inlineStr">
+        <is>
+          <t>Karolina Muchova</t>
+        </is>
+      </c>
+      <c r="E95" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F95" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G95" s="18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H95" s="17" t="inlineStr"/>
+      <c r="I95" s="17" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="J95" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="K95" s="17" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L95" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M95" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="N95" s="17" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="O95" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="P95" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>✅ Pablo Llamas Ruiz  +1.5</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>Corentin Moutet</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F96" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G96" s="13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H96" s="12" t="inlineStr"/>
+      <c r="I96" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="J96" s="9" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="K96" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L96" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M96" s="12" t="n">
+        <v>136</v>
+      </c>
+      <c r="N96" s="12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O96" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="P96" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="22" customHeight="1">
+      <c r="A97" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B97" s="17" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>✅ Talia Gibson  +5.5</t>
+        </is>
+      </c>
+      <c r="D97" s="17" t="inlineStr">
+        <is>
+          <t>Diana Shnaider</t>
+        </is>
+      </c>
+      <c r="E97" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F97" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G97" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H97" s="17" t="inlineStr"/>
+      <c r="I97" s="17" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="K97" s="17" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L97" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M97" s="17" t="n">
+        <v>184</v>
+      </c>
+      <c r="N97" s="17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O97" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P97" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="22" customHeight="1">
+      <c r="A98" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B98" s="12" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>✅ Eva Lys  +4.5</t>
+        </is>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>Naomi Osaka</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F98" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G98" s="13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H98" s="12" t="inlineStr"/>
+      <c r="I98" s="12" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="J98" s="9" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="K98" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L98" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M98" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="N98" s="12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O98" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="P98" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="22" customHeight="1">
+      <c r="A99" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B99" s="17" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>✅ Maria Sakkari  +5.5</t>
+        </is>
+      </c>
+      <c r="D99" s="17" t="inlineStr">
+        <is>
+          <t>Elena Rybakina</t>
+        </is>
+      </c>
+      <c r="E99" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F99" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G99" s="18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H99" s="17" t="inlineStr"/>
+      <c r="I99" s="17" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="J99" s="9" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="K99" s="17" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L99" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M99" s="17" t="n">
+        <v>222</v>
+      </c>
+      <c r="N99" s="17" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="O99" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="P99" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="22" customHeight="1">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>✅ Yannick Hanfmann  +1.5</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>Luciano Darderi</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F100" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G100" s="13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H100" s="12" t="inlineStr"/>
+      <c r="I100" s="12" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="K100" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L100" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M100" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="N100" s="12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="O100" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="P100" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="1">
+      <c r="A101" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B101" s="17" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>✅ Noemi Basiletti  +7.5</t>
+        </is>
+      </c>
+      <c r="D101" s="17" t="inlineStr">
+        <is>
+          <t>Elina Svitolina</t>
+        </is>
+      </c>
+      <c r="E101" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F101" s="17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G101" s="18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H101" s="17" t="inlineStr"/>
+      <c r="I101" s="17" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="J101" s="9" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="K101" s="17" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L101" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M101" s="17" t="n">
+        <v>400</v>
+      </c>
+      <c r="N101" s="17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O101" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="P101" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="22" customHeight="1">
+      <c r="A102" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>✅ Viktorija Golubic  +7.5</t>
+        </is>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>Mirra Andreeva</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F102" s="12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G102" s="13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H102" s="12" t="inlineStr"/>
+      <c r="I102" s="12" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="J102" s="9" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="K102" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L102" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M102" s="12" t="n">
+        <v>408</v>
+      </c>
+      <c r="N102" s="12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O102" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.6/-0.3)</t>
+        </is>
+      </c>
+      <c r="P102" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="22" customHeight="1">
+      <c r="A103" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B103" s="17" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>✅ Zeynep Sonmez  +5.5</t>
+        </is>
+      </c>
+      <c r="D103" s="17" t="inlineStr">
+        <is>
+          <t>Jessica Pegula</t>
+        </is>
+      </c>
+      <c r="E103" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F103" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G103" s="18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H103" s="17" t="inlineStr"/>
+      <c r="I103" s="17" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="K103" s="17" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L103" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M103" s="17" t="n">
+        <v>158</v>
+      </c>
+      <c r="N103" s="17" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="O103" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P103" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="22" customHeight="1">
+      <c r="A104" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>✅ Yannick Hanfmann  +2.5</t>
+        </is>
+      </c>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>Luciano Darderi</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F104" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G104" s="13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H104" s="12" t="inlineStr"/>
+      <c r="I104" s="12" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="J104" s="9" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="K104" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L104" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M104" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="N104" s="12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="O104" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="P104" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="1">
+      <c r="A105" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B105" s="17" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>✅ Alejandro Tabilo  +2.5</t>
+        </is>
+      </c>
+      <c r="D105" s="17" t="inlineStr">
+        <is>
+          <t>Francisco Cerundolo</t>
+        </is>
+      </c>
+      <c r="E105" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F105" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G105" s="18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H105" s="17" t="inlineStr"/>
+      <c r="I105" s="17" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="J105" s="9" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="K105" s="17" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L105" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M105" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="N105" s="17" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="O105" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="P105" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="22" customHeight="1">
+      <c r="A106" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>✅ Tyra Caterina Grant  +4.5</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>Victoria Mboko</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F106" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G106" s="13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H106" s="12" t="inlineStr"/>
+      <c r="I106" s="12" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="K106" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L106" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M106" s="12" t="n">
+        <v>124</v>
+      </c>
+      <c r="N106" s="12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="O106" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P106" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="22" customHeight="1">
+      <c r="A107" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B107" s="17" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>✅ Emma Navarro  +2.5</t>
+        </is>
+      </c>
+      <c r="D107" s="17" t="inlineStr">
+        <is>
+          <t>Elisabetta Cocciaretto</t>
+        </is>
+      </c>
+      <c r="E107" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F107" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G107" s="18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H107" s="17" t="inlineStr"/>
+      <c r="I107" s="17" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="J107" s="9" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="K107" s="17" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L107" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M107" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="N107" s="17" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O107" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="P107" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="22" customHeight="1">
+      <c r="A108" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>✅ Alexei Popyrin  +3.5</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>Jakub Mensik</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F108" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G108" s="13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H108" s="12" t="inlineStr"/>
+      <c r="I108" s="12" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="J108" s="14" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="K108" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L108" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M108" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="N108" s="12" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="O108" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="P108" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="22" customHeight="1">
+      <c r="A109" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B109" s="17" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>✅ Jasmine Paolini  +1.5</t>
+        </is>
+      </c>
+      <c r="D109" s="17" t="inlineStr">
+        <is>
+          <t>Elise Mertens</t>
+        </is>
+      </c>
+      <c r="E109" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F109" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G109" s="18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H109" s="17" t="inlineStr"/>
+      <c r="I109" s="17" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="J109" s="14" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="K109" s="17" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L109" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M109" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="N109" s="17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O109" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="P109" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="22" customHeight="1">
+      <c r="A110" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B110" s="12" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>✅ Zachary Svajda  +5.5</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>Casper Ruud</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F110" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G110" s="13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H110" s="12" t="inlineStr"/>
+      <c r="I110" s="12" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="J110" s="14" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="K110" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L110" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M110" s="12" t="n">
+        <v>432</v>
+      </c>
+      <c r="N110" s="12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O110" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="P110" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="22" customHeight="1">
+      <c r="A111" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B111" s="17" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>✅ Jelena Ostapenko  +4.5</t>
+        </is>
+      </c>
+      <c r="D111" s="17" t="inlineStr">
+        <is>
+          <t>Qinwen Zheng</t>
+        </is>
+      </c>
+      <c r="E111" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F111" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G111" s="18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H111" s="17" t="inlineStr"/>
+      <c r="I111" s="17" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="J111" s="14" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="K111" s="17" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L111" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M111" s="17" t="n">
+        <v>99</v>
+      </c>
+      <c r="N111" s="17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="O111" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/-0.6)</t>
+        </is>
+      </c>
+      <c r="P111" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="22" customHeight="1">
+      <c r="A112" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>✅ Alexander Shevchenko  +3.5</t>
+        </is>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>Karen Khachanov</t>
+        </is>
+      </c>
+      <c r="E112" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F112" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G112" s="13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H112" s="12" t="inlineStr"/>
+      <c r="I112" s="12" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="J112" s="14" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="K112" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L112" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M112" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="N112" s="12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="O112" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="P112" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="22" customHeight="1">
+      <c r="A113" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B113" s="17" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>✅ Rio Noguchi  -2.5</t>
+        </is>
+      </c>
+      <c r="D113" s="17" t="inlineStr">
+        <is>
+          <t>Jie Cui</t>
+        </is>
+      </c>
+      <c r="E113" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F113" s="17" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="G113" s="18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H113" s="17" t="inlineStr"/>
+      <c r="I113" s="17" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="J113" s="14" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="K113" s="17" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Wuxi, China Men Singles</t>
+        </is>
+      </c>
+      <c r="L113" s="17" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="M113" s="17" t="n">
+        <v>258</v>
+      </c>
+      <c r="N113" s="17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O113" s="17" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="P113" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="22" customHeight="1">
+      <c r="A114" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B114" s="12" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>✅ Dane Sweeny  +2.5</t>
+        </is>
+      </c>
+      <c r="D114" s="12" t="inlineStr">
+        <is>
+          <t>Mark Lajal</t>
+        </is>
+      </c>
+      <c r="E114" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F114" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G114" s="13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H114" s="12" t="inlineStr"/>
+      <c r="I114" s="12" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="J114" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="K114" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Wuxi, China Men Singles</t>
+        </is>
+      </c>
+      <c r="L114" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="M114" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="N114" s="12" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="O114" s="12" t="inlineStr">
+        <is>
+          <t>TA-hard+forma+fat(-0.3/-0.3)</t>
+        </is>
+      </c>
+      <c r="P114" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="22" customHeight="1">
+      <c r="A115" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B115" s="17" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>✅ Jan-Lennard Struff  +3.5</t>
+        </is>
+      </c>
+      <c r="D115" s="17" t="inlineStr">
+        <is>
+          <t>Jiri Lehecka</t>
+        </is>
+      </c>
+      <c r="E115" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F115" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G115" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H115" s="17" t="inlineStr"/>
+      <c r="I115" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="J115" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="K115" s="17" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L115" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M115" s="17" t="n">
+        <v>168</v>
+      </c>
+      <c r="N115" s="17" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="O115" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P115" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="22" customHeight="1">
+      <c r="A116" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B116" s="12" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>✅ Cristian Garin  +1.5</t>
+        </is>
+      </c>
+      <c r="D116" s="12" t="inlineStr">
+        <is>
+          <t>Alejandro Davidovich Fokina</t>
+        </is>
+      </c>
+      <c r="E116" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F116" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G116" s="13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H116" s="12" t="inlineStr"/>
+      <c r="I116" s="12" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="J116" s="14" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="K116" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L116" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M116" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="N116" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O116" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="P116" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="22" customHeight="1">
+      <c r="A117" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B117" s="17" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>✅ Tomas Machac  +2.5</t>
+        </is>
+      </c>
+      <c r="D117" s="17" t="inlineStr">
+        <is>
+          <t>Daniil Medvedev</t>
+        </is>
+      </c>
+      <c r="E117" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F117" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G117" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H117" s="17" t="inlineStr"/>
+      <c r="I117" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="J117" s="15" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="K117" s="17" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L117" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M117" s="17" t="n">
+        <v>102</v>
+      </c>
+      <c r="N117" s="17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="O117" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="P117" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="22" customHeight="1">
+      <c r="A118" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B118" s="12" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>✅ Peyton Stearns  +2.5</t>
+        </is>
+      </c>
+      <c r="D118" s="12" t="inlineStr">
+        <is>
+          <t>Madison Keys</t>
+        </is>
+      </c>
+      <c r="E118" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F118" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G118" s="13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H118" s="12" t="inlineStr"/>
+      <c r="I118" s="12" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="J118" s="15" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="K118" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L118" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M118" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="N118" s="12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O118" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="P118" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="22" customHeight="1">
+      <c r="A119" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B119" s="17" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>✅ Jan-Lennard Struff  +4.5</t>
+        </is>
+      </c>
+      <c r="D119" s="17" t="inlineStr">
+        <is>
+          <t>Jiri Lehecka</t>
+        </is>
+      </c>
+      <c r="E119" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F119" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G119" s="18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H119" s="17" t="inlineStr"/>
+      <c r="I119" s="17" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="J119" s="15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="K119" s="17" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L119" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M119" s="17" t="n">
+        <v>168</v>
+      </c>
+      <c r="N119" s="17" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="O119" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P119" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="22" customHeight="1">
+      <c r="A120" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B120" s="12" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>✅ Miomir Kecmanovic  +3.5</t>
+        </is>
+      </c>
+      <c r="D120" s="12" t="inlineStr">
+        <is>
+          <t>Andrey Rublev</t>
+        </is>
+      </c>
+      <c r="E120" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F120" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G120" s="13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H120" s="12" t="inlineStr"/>
+      <c r="I120" s="12" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="J120" s="15" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="K120" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L120" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M120" s="12" t="n">
+        <v>133</v>
+      </c>
+      <c r="N120" s="12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O120" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="P120" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="22" customHeight="1">
+      <c r="A121" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B121" s="17" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>✅ Daniel Altmaier  +5.5</t>
+        </is>
+      </c>
+      <c r="D121" s="17" t="inlineStr">
+        <is>
+          <t>Alexander Zverev</t>
+        </is>
+      </c>
+      <c r="E121" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F121" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G121" s="18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H121" s="17" t="inlineStr"/>
+      <c r="I121" s="17" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="J121" s="15" t="n">
+        <v>11</v>
+      </c>
+      <c r="K121" s="17" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L121" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M121" s="17" t="n">
+        <v>372</v>
+      </c>
+      <c r="N121" s="17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O121" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="P121" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="22" customHeight="1">
+      <c r="A122" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B122" s="12" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>✅ Vit Kopriva  -1.5</t>
+        </is>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>Ugo Humbert</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F122" s="12" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="G122" s="13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H122" s="12" t="inlineStr"/>
+      <c r="I122" s="12" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="J122" s="15" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="K122" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L122" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M122" s="12" t="n">
+        <v>206</v>
+      </c>
+      <c r="N122" s="12" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="O122" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="P122" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="22" customHeight="1">
+      <c r="A123" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B123" s="17" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>✅ Terence Atmane  +3.5</t>
+        </is>
+      </c>
+      <c r="D123" s="17" t="inlineStr">
+        <is>
+          <t>Flavio Cobolli</t>
+        </is>
+      </c>
+      <c r="E123" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F123" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G123" s="18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H123" s="17" t="inlineStr"/>
+      <c r="I123" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="J123" s="15" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="K123" s="17" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L123" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M123" s="17" t="n">
+        <v>168</v>
+      </c>
+      <c r="N123" s="17" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="O123" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="P123" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="22" customHeight="1">
+      <c r="A124" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>✅ Alexander Blockx  -3.5</t>
+        </is>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>Tallon Griekspoor</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F124" s="12" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="G124" s="13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H124" s="12" t="inlineStr"/>
+      <c r="I124" s="12" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="J124" s="15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="K124" s="12" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L124" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M124" s="12" t="n">
+        <v>231</v>
+      </c>
+      <c r="N124" s="12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O124" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="P124" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="22" customHeight="1">
+      <c r="A125" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B125" s="17" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>✅ Dino Prizmic  +2.5</t>
+        </is>
+      </c>
+      <c r="D125" s="17" t="inlineStr">
+        <is>
+          <t>Novak Djokovic</t>
+        </is>
+      </c>
+      <c r="E125" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F125" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G125" s="18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H125" s="17" t="inlineStr"/>
+      <c r="I125" s="17" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="J125" s="15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="K125" s="17" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L125" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M125" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="N125" s="17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O125" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="P125" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="22" customHeight="1">
+      <c r="A126" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B126" s="12" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>✅ Laura Siegemund  +1.5</t>
+        </is>
+      </c>
+      <c r="D126" s="12" t="inlineStr">
+        <is>
+          <t>Ekaterina Alexandrova</t>
+        </is>
+      </c>
+      <c r="E126" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F126" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G126" s="13" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H126" s="12" t="inlineStr"/>
+      <c r="I126" s="12" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="J126" s="15" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="K126" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L126" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M126" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="N126" s="12" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="O126" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="P126" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="22" customHeight="1">
+      <c r="A127" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B127" s="17" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>✅ Sebastian Baez  +1.5</t>
+        </is>
+      </c>
+      <c r="D127" s="17" t="inlineStr">
+        <is>
+          <t>Alexander Bublik</t>
+        </is>
+      </c>
+      <c r="E127" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F127" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G127" s="18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H127" s="17" t="inlineStr"/>
+      <c r="I127" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="J127" s="15" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="K127" s="17" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L127" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M127" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="N127" s="17" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="O127" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="P127" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="22" customHeight="1">
+      <c r="A128" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B128" s="12" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>✅ Karolina Pliskova  -1.5</t>
+        </is>
+      </c>
+      <c r="D128" s="12" t="inlineStr">
+        <is>
+          <t>Jaqueline Cristian</t>
+        </is>
+      </c>
+      <c r="E128" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F128" s="12" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="G128" s="13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H128" s="12" t="inlineStr"/>
+      <c r="I128" s="12" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="J128" s="15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="K128" s="12" t="inlineStr">
+        <is>
+          <t>WTA - WTA Rome, Italy Women Singles</t>
+        </is>
+      </c>
+      <c r="L128" s="12" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M128" s="12" t="n">
+        <v>159</v>
+      </c>
+      <c r="N128" s="12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O128" s="12" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(-0.3/0.0)</t>
+        </is>
+      </c>
+      <c r="P128" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="22" customHeight="1">
+      <c r="A129" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B129" s="17" t="inlineStr">
+        <is>
+          <t>02:11</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>✅ Aleksandar Vukic  +5.5</t>
+        </is>
+      </c>
+      <c r="D129" s="17" t="inlineStr">
+        <is>
+          <t>Tommy Paul</t>
+        </is>
+      </c>
+      <c r="E129" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F129" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G129" s="18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="H129" s="17" t="inlineStr"/>
+      <c r="I129" s="17" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="J129" s="15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K129" s="17" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L129" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M129" s="17" t="n">
+        <v>246</v>
+      </c>
+      <c r="N129" s="17" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="O129" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma+fat(0.0/-0.3)</t>
+        </is>
+      </c>
+      <c r="P129" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
     <row r="130" ht="22" customHeight="1"/>
     <row r="131" ht="22" customHeight="1"/>
     <row r="132" ht="22" customHeight="1"/>

--- a/data/value_bets_log.xlsx
+++ b/data/value_bets_log.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Value Bets Log" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Handicap Bets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Value Bets Log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Handicap Bets" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -151,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -207,6 +207,7 @@
     <xf numFmtId="0" fontId="3" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -572,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q131"/>
+  <dimension ref="A1:Q140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2206,10 +2207,20 @@
       <c r="M25" s="13" t="n">
         <v>1.66</v>
       </c>
-      <c r="N25" s="10" t="inlineStr"/>
-      <c r="O25" s="11" t="inlineStr"/>
-      <c r="P25" s="12" t="inlineStr"/>
-      <c r="Q25" s="12" t="inlineStr"/>
+      <c r="N25" s="10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="O25" s="11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P25" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q25" s="12" t="n">
+        <v>0.66</v>
+      </c>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
@@ -2267,10 +2278,20 @@
       <c r="M26" s="7" t="n">
         <v>1.42</v>
       </c>
-      <c r="N26" s="10" t="inlineStr"/>
-      <c r="O26" s="11" t="inlineStr"/>
-      <c r="P26" s="5" t="inlineStr"/>
-      <c r="Q26" s="5" t="inlineStr"/>
+      <c r="N26" s="10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="O26" s="11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P26" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q26" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
@@ -2462,10 +2483,20 @@
       <c r="M29" s="13" t="n">
         <v>1.31</v>
       </c>
-      <c r="N29" s="10" t="inlineStr"/>
-      <c r="O29" s="11" t="inlineStr"/>
-      <c r="P29" s="12" t="inlineStr"/>
-      <c r="Q29" s="12" t="inlineStr"/>
+      <c r="N29" s="10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="O29" s="11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P29" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q29" s="12" t="n">
+        <v>0.31</v>
+      </c>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
@@ -3553,10 +3584,20 @@
       <c r="M46" s="7" t="n">
         <v>2.37</v>
       </c>
-      <c r="N46" s="10" t="inlineStr"/>
-      <c r="O46" s="11" t="inlineStr"/>
-      <c r="P46" s="5" t="inlineStr"/>
-      <c r="Q46" s="5" t="inlineStr"/>
+      <c r="N46" s="10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O46" s="11" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="P46" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q46" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="12" t="inlineStr">
@@ -3803,10 +3844,20 @@
       <c r="M50" s="7" t="n">
         <v>3.55</v>
       </c>
-      <c r="N50" s="10" t="inlineStr"/>
-      <c r="O50" s="11" t="inlineStr"/>
-      <c r="P50" s="5" t="inlineStr"/>
-      <c r="Q50" s="5" t="inlineStr"/>
+      <c r="N50" s="10" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="O50" s="11" t="n">
+        <v>-6.33</v>
+      </c>
+      <c r="P50" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q50" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="12" t="inlineStr">
@@ -3925,10 +3976,20 @@
       <c r="M52" s="7" t="n">
         <v>2.57</v>
       </c>
-      <c r="N52" s="10" t="inlineStr"/>
-      <c r="O52" s="11" t="inlineStr"/>
-      <c r="P52" s="5" t="inlineStr"/>
-      <c r="Q52" s="5" t="inlineStr"/>
+      <c r="N52" s="10" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O52" s="11" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="P52" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q52" s="5" t="n">
+        <v>1.57</v>
+      </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="12" t="inlineStr">
@@ -3986,10 +4047,20 @@
       <c r="M53" s="13" t="n">
         <v>3.6</v>
       </c>
-      <c r="N53" s="10" t="inlineStr"/>
-      <c r="O53" s="11" t="inlineStr"/>
-      <c r="P53" s="12" t="inlineStr"/>
-      <c r="Q53" s="12" t="inlineStr"/>
+      <c r="N53" s="10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O53" s="11" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="P53" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q53" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
@@ -4047,10 +4118,20 @@
       <c r="M54" s="7" t="n">
         <v>2.8</v>
       </c>
-      <c r="N54" s="10" t="inlineStr"/>
-      <c r="O54" s="11" t="inlineStr"/>
-      <c r="P54" s="5" t="inlineStr"/>
-      <c r="Q54" s="5" t="inlineStr"/>
+      <c r="N54" s="10" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O54" s="11" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="P54" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q54" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="12" t="inlineStr">
@@ -4108,10 +4189,20 @@
       <c r="M55" s="13" t="n">
         <v>2.15</v>
       </c>
-      <c r="N55" s="10" t="inlineStr"/>
-      <c r="O55" s="11" t="inlineStr"/>
-      <c r="P55" s="12" t="inlineStr"/>
-      <c r="Q55" s="12" t="inlineStr"/>
+      <c r="N55" s="10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O55" s="11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="P55" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q55" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
@@ -4236,10 +4327,20 @@
       <c r="M57" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="N57" s="10" t="inlineStr"/>
-      <c r="O57" s="11" t="inlineStr"/>
-      <c r="P57" s="12" t="inlineStr"/>
-      <c r="Q57" s="12" t="inlineStr"/>
+      <c r="N57" s="10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O57" s="11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P57" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q57" s="12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="5" t="inlineStr">
@@ -4297,10 +4398,20 @@
       <c r="M58" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="N58" s="10" t="inlineStr"/>
-      <c r="O58" s="11" t="inlineStr"/>
-      <c r="P58" s="5" t="inlineStr"/>
-      <c r="Q58" s="5" t="inlineStr"/>
+      <c r="N58" s="10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O58" s="11" t="n">
+        <v>-3.85</v>
+      </c>
+      <c r="P58" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q58" s="5" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="12" t="inlineStr">
@@ -4358,10 +4469,20 @@
       <c r="M59" s="13" t="n">
         <v>2.18</v>
       </c>
-      <c r="N59" s="10" t="inlineStr"/>
-      <c r="O59" s="11" t="inlineStr"/>
-      <c r="P59" s="12" t="inlineStr"/>
-      <c r="Q59" s="12" t="inlineStr"/>
+      <c r="N59" s="10" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="O59" s="11" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="P59" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q59" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="5" t="inlineStr">
@@ -4419,10 +4540,20 @@
       <c r="M60" s="7" t="n">
         <v>2.35</v>
       </c>
-      <c r="N60" s="10" t="inlineStr"/>
-      <c r="O60" s="11" t="inlineStr"/>
-      <c r="P60" s="5" t="inlineStr"/>
-      <c r="Q60" s="5" t="inlineStr"/>
+      <c r="N60" s="10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O60" s="11" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="P60" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q60" s="5" t="n">
+        <v>1.35</v>
+      </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="12" t="inlineStr">
@@ -4547,10 +4678,20 @@
       <c r="M62" s="7" t="n">
         <v>1.75</v>
       </c>
-      <c r="N62" s="10" t="inlineStr"/>
-      <c r="O62" s="11" t="inlineStr"/>
-      <c r="P62" s="5" t="inlineStr"/>
-      <c r="Q62" s="5" t="inlineStr"/>
+      <c r="N62" s="10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O62" s="11" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="P62" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q62" s="5" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="12" t="inlineStr">
@@ -4809,10 +4950,20 @@
       <c r="M66" s="7" t="n">
         <v>1.61</v>
       </c>
-      <c r="N66" s="10" t="inlineStr"/>
-      <c r="O66" s="11" t="inlineStr"/>
-      <c r="P66" s="5" t="inlineStr"/>
-      <c r="Q66" s="5" t="inlineStr"/>
+      <c r="N66" s="10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O66" s="11" t="n">
+        <v>-3.59</v>
+      </c>
+      <c r="P66" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q66" s="5" t="n">
+        <v>0.61</v>
+      </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="12" t="inlineStr">
@@ -4870,10 +5021,20 @@
       <c r="M67" s="13" t="n">
         <v>1.61</v>
       </c>
-      <c r="N67" s="10" t="inlineStr"/>
-      <c r="O67" s="11" t="inlineStr"/>
-      <c r="P67" s="12" t="inlineStr"/>
-      <c r="Q67" s="12" t="inlineStr"/>
+      <c r="N67" s="10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="O67" s="11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P67" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q67" s="12" t="n">
+        <v>0.61</v>
+      </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
@@ -4931,10 +5092,20 @@
       <c r="M68" s="7" t="n">
         <v>2.55</v>
       </c>
-      <c r="N68" s="10" t="inlineStr"/>
-      <c r="O68" s="11" t="inlineStr"/>
-      <c r="P68" s="5" t="inlineStr"/>
-      <c r="Q68" s="5" t="inlineStr"/>
+      <c r="N68" s="10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="O68" s="11" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="P68" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q68" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="12" t="inlineStr">
@@ -4992,10 +5163,20 @@
       <c r="M69" s="13" t="n">
         <v>2.62</v>
       </c>
-      <c r="N69" s="10" t="inlineStr"/>
-      <c r="O69" s="11" t="inlineStr"/>
-      <c r="P69" s="12" t="inlineStr"/>
-      <c r="Q69" s="12" t="inlineStr"/>
+      <c r="N69" s="10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="O69" s="11" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="P69" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q69" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
@@ -5254,10 +5435,20 @@
       <c r="M73" s="13" t="n">
         <v>4.55</v>
       </c>
-      <c r="N73" s="10" t="inlineStr"/>
-      <c r="O73" s="11" t="inlineStr"/>
-      <c r="P73" s="12" t="inlineStr"/>
-      <c r="Q73" s="12" t="inlineStr"/>
+      <c r="N73" s="10" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="O73" s="11" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="P73" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q73" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
@@ -5315,10 +5506,20 @@
       <c r="M74" s="7" t="n">
         <v>1.45</v>
       </c>
-      <c r="N74" s="10" t="inlineStr"/>
-      <c r="O74" s="11" t="inlineStr"/>
-      <c r="P74" s="5" t="inlineStr"/>
-      <c r="Q74" s="5" t="inlineStr"/>
+      <c r="N74" s="10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O74" s="11" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="P74" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q74" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="12" t="inlineStr">
@@ -5443,10 +5644,20 @@
       <c r="M76" s="7" t="n">
         <v>1.44</v>
       </c>
-      <c r="N76" s="10" t="inlineStr"/>
-      <c r="O76" s="11" t="inlineStr"/>
-      <c r="P76" s="5" t="inlineStr"/>
-      <c r="Q76" s="5" t="inlineStr"/>
+      <c r="N76" s="10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O76" s="11" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="P76" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q76" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="12" t="inlineStr">
@@ -5571,10 +5782,20 @@
       <c r="M78" s="7" t="n">
         <v>1.31</v>
       </c>
-      <c r="N78" s="10" t="inlineStr"/>
-      <c r="O78" s="11" t="inlineStr"/>
-      <c r="P78" s="5" t="inlineStr"/>
-      <c r="Q78" s="5" t="inlineStr"/>
+      <c r="N78" s="10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="O78" s="11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P78" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q78" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="12" t="inlineStr">
@@ -5632,10 +5853,20 @@
       <c r="M79" s="13" t="n">
         <v>1.5</v>
       </c>
-      <c r="N79" s="10" t="inlineStr"/>
-      <c r="O79" s="11" t="inlineStr"/>
-      <c r="P79" s="12" t="inlineStr"/>
-      <c r="Q79" s="12" t="inlineStr"/>
+      <c r="N79" s="10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O79" s="11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P79" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q79" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
@@ -5760,10 +5991,20 @@
       <c r="M81" s="13" t="n">
         <v>2.05</v>
       </c>
-      <c r="N81" s="10" t="inlineStr"/>
-      <c r="O81" s="11" t="inlineStr"/>
-      <c r="P81" s="12" t="inlineStr"/>
-      <c r="Q81" s="12" t="inlineStr"/>
+      <c r="N81" s="10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O81" s="11" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="P81" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q81" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="5" t="inlineStr">
@@ -5882,10 +6123,20 @@
       <c r="M83" s="13" t="n">
         <v>1.55</v>
       </c>
-      <c r="N83" s="10" t="inlineStr"/>
-      <c r="O83" s="11" t="inlineStr"/>
-      <c r="P83" s="12" t="inlineStr"/>
-      <c r="Q83" s="12" t="inlineStr"/>
+      <c r="N83" s="10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="O83" s="11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P83" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q83" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="5" t="inlineStr">
@@ -6077,10 +6328,20 @@
       <c r="M86" s="7" t="n">
         <v>1.47</v>
       </c>
-      <c r="N86" s="10" t="inlineStr"/>
-      <c r="O86" s="11" t="inlineStr"/>
-      <c r="P86" s="5" t="inlineStr"/>
-      <c r="Q86" s="5" t="inlineStr"/>
+      <c r="N86" s="10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="O86" s="11" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="P86" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q86" s="5" t="n">
+        <v>0.47</v>
+      </c>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="12" t="inlineStr">
@@ -6138,10 +6399,20 @@
       <c r="M87" s="13" t="n">
         <v>1.7</v>
       </c>
-      <c r="N87" s="10" t="inlineStr"/>
-      <c r="O87" s="11" t="inlineStr"/>
-      <c r="P87" s="12" t="inlineStr"/>
-      <c r="Q87" s="12" t="inlineStr"/>
+      <c r="N87" s="10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="O87" s="11" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="P87" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q87" s="12" t="n">
+        <v>0.7</v>
+      </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="5" t="inlineStr">
@@ -6266,10 +6537,20 @@
       <c r="M89" s="13" t="n">
         <v>1.62</v>
       </c>
-      <c r="N89" s="10" t="inlineStr"/>
-      <c r="O89" s="11" t="inlineStr"/>
-      <c r="P89" s="12" t="inlineStr"/>
-      <c r="Q89" s="12" t="inlineStr"/>
+      <c r="N89" s="10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="O89" s="11" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="P89" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q89" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="5" t="inlineStr">
@@ -6327,10 +6608,20 @@
       <c r="M90" s="7" t="n">
         <v>2.3</v>
       </c>
-      <c r="N90" s="10" t="inlineStr"/>
-      <c r="O90" s="11" t="inlineStr"/>
-      <c r="P90" s="5" t="inlineStr"/>
-      <c r="Q90" s="5" t="inlineStr"/>
+      <c r="N90" s="10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O90" s="11" t="n">
+        <v>-4.17</v>
+      </c>
+      <c r="P90" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q90" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="12" t="inlineStr">
@@ -6516,10 +6807,20 @@
       <c r="M93" s="13" t="n">
         <v>2.4</v>
       </c>
-      <c r="N93" s="10" t="inlineStr"/>
-      <c r="O93" s="11" t="inlineStr"/>
-      <c r="P93" s="12" t="inlineStr"/>
-      <c r="Q93" s="12" t="inlineStr"/>
+      <c r="N93" s="10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O93" s="11" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="P93" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q93" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="5" t="inlineStr">
@@ -6577,10 +6878,20 @@
       <c r="M94" s="7" t="n">
         <v>2.37</v>
       </c>
-      <c r="N94" s="10" t="inlineStr"/>
-      <c r="O94" s="11" t="inlineStr"/>
-      <c r="P94" s="5" t="inlineStr"/>
-      <c r="Q94" s="5" t="inlineStr"/>
+      <c r="N94" s="10" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="O94" s="11" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="P94" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q94" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="5" t="inlineStr">
@@ -6638,10 +6949,20 @@
       <c r="M95" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="N95" s="10" t="inlineStr"/>
-      <c r="O95" s="11" t="inlineStr"/>
-      <c r="P95" s="5" t="inlineStr"/>
-      <c r="Q95" s="5" t="inlineStr"/>
+      <c r="N95" s="10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="O95" s="11" t="n">
+        <v>-10.71</v>
+      </c>
+      <c r="P95" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q95" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="12" t="inlineStr">
@@ -6766,10 +7087,20 @@
       <c r="M97" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="N97" s="10" t="inlineStr"/>
-      <c r="O97" s="11" t="inlineStr"/>
-      <c r="P97" s="5" t="inlineStr"/>
-      <c r="Q97" s="5" t="inlineStr"/>
+      <c r="N97" s="10" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="O97" s="11" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="P97" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q97" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="12" t="inlineStr">
@@ -6827,10 +7158,20 @@
       <c r="M98" s="13" t="n">
         <v>3.2</v>
       </c>
-      <c r="N98" s="10" t="inlineStr"/>
-      <c r="O98" s="11" t="inlineStr"/>
-      <c r="P98" s="12" t="inlineStr"/>
-      <c r="Q98" s="12" t="inlineStr"/>
+      <c r="N98" s="10" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="O98" s="11" t="n">
+        <v>7.02</v>
+      </c>
+      <c r="P98" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q98" s="12" t="n">
+        <v>2.2</v>
+      </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="5" t="inlineStr">
@@ -6888,10 +7229,20 @@
       <c r="M99" s="7" t="n">
         <v>2.37</v>
       </c>
-      <c r="N99" s="10" t="inlineStr"/>
-      <c r="O99" s="11" t="inlineStr"/>
-      <c r="P99" s="5" t="inlineStr"/>
-      <c r="Q99" s="5" t="inlineStr"/>
+      <c r="N99" s="10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="O99" s="11" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="P99" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q99" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="12" t="inlineStr">
@@ -6949,10 +7300,20 @@
       <c r="M100" s="13" t="n">
         <v>2.75</v>
       </c>
-      <c r="N100" s="10" t="inlineStr"/>
-      <c r="O100" s="11" t="inlineStr"/>
-      <c r="P100" s="12" t="inlineStr"/>
-      <c r="Q100" s="12" t="inlineStr"/>
+      <c r="N100" s="10" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O100" s="11" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="P100" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q100" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
@@ -7012,8 +7373,14 @@
       </c>
       <c r="N101" s="10" t="inlineStr"/>
       <c r="O101" s="11" t="inlineStr"/>
-      <c r="P101" s="5" t="inlineStr"/>
-      <c r="Q101" s="5" t="inlineStr"/>
+      <c r="P101" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q101" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="12" t="inlineStr">
@@ -7071,10 +7438,20 @@
       <c r="M102" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="N102" s="10" t="inlineStr"/>
-      <c r="O102" s="11" t="inlineStr"/>
-      <c r="P102" s="12" t="inlineStr"/>
-      <c r="Q102" s="12" t="inlineStr"/>
+      <c r="N102" s="10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O102" s="11" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="P102" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q102" s="12" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="5" t="inlineStr">
@@ -7134,8 +7511,14 @@
       </c>
       <c r="N103" s="10" t="inlineStr"/>
       <c r="O103" s="11" t="inlineStr"/>
-      <c r="P103" s="5" t="inlineStr"/>
-      <c r="Q103" s="5" t="inlineStr"/>
+      <c r="P103" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q103" s="5" t="n">
+        <v>1.12</v>
+      </c>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="12" t="inlineStr">
@@ -7193,10 +7576,20 @@
       <c r="M104" s="13" t="n">
         <v>2.15</v>
       </c>
-      <c r="N104" s="10" t="inlineStr"/>
-      <c r="O104" s="11" t="inlineStr"/>
-      <c r="P104" s="12" t="inlineStr"/>
-      <c r="Q104" s="12" t="inlineStr"/>
+      <c r="N104" s="10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="O104" s="11" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="P104" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q104" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="5" t="inlineStr">
@@ -7254,10 +7647,20 @@
       <c r="M105" s="7" t="n">
         <v>5.5</v>
       </c>
-      <c r="N105" s="10" t="inlineStr"/>
-      <c r="O105" s="11" t="inlineStr"/>
-      <c r="P105" s="5" t="inlineStr"/>
-      <c r="Q105" s="5" t="inlineStr"/>
+      <c r="N105" s="10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O105" s="11" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="P105" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q105" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="12" t="inlineStr">
@@ -7376,10 +7779,20 @@
       <c r="M107" s="7" t="n">
         <v>2.62</v>
       </c>
-      <c r="N107" s="10" t="inlineStr"/>
-      <c r="O107" s="11" t="inlineStr"/>
-      <c r="P107" s="5" t="inlineStr"/>
-      <c r="Q107" s="5" t="inlineStr"/>
+      <c r="N107" s="10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O107" s="11" t="n">
+        <v>-4.38</v>
+      </c>
+      <c r="P107" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q107" s="5" t="n">
+        <v>1.62</v>
+      </c>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="12" t="inlineStr">
@@ -7437,10 +7850,20 @@
       <c r="M108" s="13" t="n">
         <v>2.85</v>
       </c>
-      <c r="N108" s="10" t="inlineStr"/>
-      <c r="O108" s="11" t="inlineStr"/>
-      <c r="P108" s="12" t="inlineStr"/>
-      <c r="Q108" s="12" t="inlineStr"/>
+      <c r="N108" s="10" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="O108" s="11" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="P108" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q108" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
@@ -7498,10 +7921,20 @@
       <c r="M109" s="7" t="n">
         <v>3.5</v>
       </c>
-      <c r="N109" s="10" t="inlineStr"/>
-      <c r="O109" s="11" t="inlineStr"/>
-      <c r="P109" s="5" t="inlineStr"/>
-      <c r="Q109" s="5" t="inlineStr"/>
+      <c r="N109" s="10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O109" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P109" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q109" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="12" t="inlineStr">
@@ -7559,10 +7992,20 @@
       <c r="M110" s="13" t="n">
         <v>6.8</v>
       </c>
-      <c r="N110" s="10" t="inlineStr"/>
-      <c r="O110" s="11" t="inlineStr"/>
-      <c r="P110" s="12" t="inlineStr"/>
-      <c r="Q110" s="12" t="inlineStr"/>
+      <c r="N110" s="10" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="O110" s="11" t="n">
+        <v>-18.76</v>
+      </c>
+      <c r="P110" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q110" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="5" t="inlineStr">
@@ -7620,10 +8063,20 @@
       <c r="M111" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="N111" s="10" t="inlineStr"/>
-      <c r="O111" s="11" t="inlineStr"/>
-      <c r="P111" s="5" t="inlineStr"/>
-      <c r="Q111" s="5" t="inlineStr"/>
+      <c r="N111" s="10" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="O111" s="11" t="n">
+        <v>-14.04</v>
+      </c>
+      <c r="P111" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q111" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="12" t="inlineStr">
@@ -7681,10 +8134,20 @@
       <c r="M112" s="13" t="n">
         <v>5.5</v>
       </c>
-      <c r="N112" s="10" t="inlineStr"/>
-      <c r="O112" s="11" t="inlineStr"/>
-      <c r="P112" s="12" t="inlineStr"/>
-      <c r="Q112" s="12" t="inlineStr"/>
+      <c r="N112" s="10" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="O112" s="11" t="n">
+        <v>-17.04</v>
+      </c>
+      <c r="P112" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q112" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="5" t="inlineStr">
@@ -7742,10 +8205,20 @@
       <c r="M113" s="7" t="n">
         <v>2.37</v>
       </c>
-      <c r="N113" s="10" t="inlineStr"/>
-      <c r="O113" s="11" t="inlineStr"/>
-      <c r="P113" s="5" t="inlineStr"/>
-      <c r="Q113" s="5" t="inlineStr"/>
+      <c r="N113" s="10" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O113" s="11" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="P113" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q113" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="12" t="inlineStr">
@@ -7805,8 +8278,14 @@
       </c>
       <c r="N114" s="10" t="inlineStr"/>
       <c r="O114" s="11" t="inlineStr"/>
-      <c r="P114" s="12" t="inlineStr"/>
-      <c r="Q114" s="12" t="inlineStr"/>
+      <c r="P114" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q114" s="12" t="n">
+        <v>0.53</v>
+      </c>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="5" t="inlineStr">
@@ -7866,8 +8345,14 @@
       </c>
       <c r="N115" s="10" t="inlineStr"/>
       <c r="O115" s="11" t="inlineStr"/>
-      <c r="P115" s="5" t="inlineStr"/>
-      <c r="Q115" s="5" t="inlineStr"/>
+      <c r="P115" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q115" s="5" t="n">
+        <v>1.9</v>
+      </c>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="12" t="inlineStr">
@@ -7925,10 +8410,20 @@
       <c r="M116" s="13" t="n">
         <v>2.3</v>
       </c>
-      <c r="N116" s="10" t="inlineStr"/>
-      <c r="O116" s="11" t="inlineStr"/>
-      <c r="P116" s="12" t="inlineStr"/>
-      <c r="Q116" s="12" t="inlineStr"/>
+      <c r="N116" s="10" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="O116" s="11" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="P116" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q116" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="5" t="inlineStr">
@@ -7988,8 +8483,14 @@
       </c>
       <c r="N117" s="10" t="inlineStr"/>
       <c r="O117" s="11" t="inlineStr"/>
-      <c r="P117" s="5" t="inlineStr"/>
-      <c r="Q117" s="5" t="inlineStr"/>
+      <c r="P117" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q117" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="12" t="inlineStr">
@@ -8047,10 +8548,20 @@
       <c r="M118" s="13" t="n">
         <v>4.33</v>
       </c>
-      <c r="N118" s="10" t="inlineStr"/>
-      <c r="O118" s="11" t="inlineStr"/>
-      <c r="P118" s="12" t="inlineStr"/>
-      <c r="Q118" s="12" t="inlineStr"/>
+      <c r="N118" s="10" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="O118" s="11" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="P118" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q118" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="5" t="inlineStr">
@@ -8108,10 +8619,20 @@
       <c r="M119" s="7" t="n">
         <v>1.52</v>
       </c>
-      <c r="N119" s="10" t="inlineStr"/>
-      <c r="O119" s="11" t="inlineStr"/>
-      <c r="P119" s="5" t="inlineStr"/>
-      <c r="Q119" s="5" t="inlineStr"/>
+      <c r="N119" s="10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O119" s="11" t="n">
+        <v>-2.56</v>
+      </c>
+      <c r="P119" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q119" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="12" t="inlineStr">
@@ -8169,10 +8690,20 @@
       <c r="M120" s="13" t="n">
         <v>1.72</v>
       </c>
-      <c r="N120" s="10" t="inlineStr"/>
-      <c r="O120" s="11" t="inlineStr"/>
-      <c r="P120" s="12" t="inlineStr"/>
-      <c r="Q120" s="12" t="inlineStr"/>
+      <c r="N120" s="10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O120" s="11" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="P120" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q120" s="12" t="n">
+        <v>0.72</v>
+      </c>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
@@ -8230,10 +8761,20 @@
       <c r="M121" s="7" t="n">
         <v>13.5</v>
       </c>
-      <c r="N121" s="10" t="inlineStr"/>
-      <c r="O121" s="11" t="inlineStr"/>
-      <c r="P121" s="5" t="inlineStr"/>
-      <c r="Q121" s="5" t="inlineStr"/>
+      <c r="N121" s="10" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="O121" s="11" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="P121" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q121" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="12" t="inlineStr">
@@ -8291,10 +8832,20 @@
       <c r="M122" s="13" t="n">
         <v>1.6</v>
       </c>
-      <c r="N122" s="10" t="inlineStr"/>
-      <c r="O122" s="11" t="inlineStr"/>
-      <c r="P122" s="12" t="inlineStr"/>
-      <c r="Q122" s="12" t="inlineStr"/>
+      <c r="N122" s="10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="O122" s="11" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="P122" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q122" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="5" t="inlineStr">
@@ -8352,10 +8903,20 @@
       <c r="M123" s="7" t="n">
         <v>1.47</v>
       </c>
-      <c r="N123" s="10" t="inlineStr"/>
-      <c r="O123" s="11" t="inlineStr"/>
-      <c r="P123" s="5" t="inlineStr"/>
-      <c r="Q123" s="5" t="inlineStr"/>
+      <c r="N123" s="10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="O123" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q123" s="5" t="n">
+        <v>0.47</v>
+      </c>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="12" t="inlineStr">
@@ -8413,10 +8974,20 @@
       <c r="M124" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="N124" s="10" t="inlineStr"/>
-      <c r="O124" s="11" t="inlineStr"/>
-      <c r="P124" s="12" t="inlineStr"/>
-      <c r="Q124" s="12" t="inlineStr"/>
+      <c r="N124" s="10" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O124" s="11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="P124" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q124" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="5" t="inlineStr">
@@ -8537,8 +9108,14 @@
       </c>
       <c r="N126" s="10" t="inlineStr"/>
       <c r="O126" s="11" t="inlineStr"/>
-      <c r="P126" s="12" t="inlineStr"/>
-      <c r="Q126" s="12" t="inlineStr"/>
+      <c r="P126" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q126" s="12" t="n">
+        <v>2.05</v>
+      </c>
     </row>
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="5" t="inlineStr">
@@ -8596,10 +9173,20 @@
       <c r="M127" s="7" t="n">
         <v>4.15</v>
       </c>
-      <c r="N127" s="10" t="inlineStr"/>
-      <c r="O127" s="11" t="inlineStr"/>
-      <c r="P127" s="5" t="inlineStr"/>
-      <c r="Q127" s="5" t="inlineStr"/>
+      <c r="N127" s="10" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="O127" s="11" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="P127" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q127" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="12" t="inlineStr">
@@ -8657,10 +9244,20 @@
       <c r="M128" s="13" t="n">
         <v>1.29</v>
       </c>
-      <c r="N128" s="10" t="inlineStr"/>
-      <c r="O128" s="11" t="inlineStr"/>
-      <c r="P128" s="12" t="inlineStr"/>
-      <c r="Q128" s="12" t="inlineStr"/>
+      <c r="N128" s="10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O128" s="11" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="P128" s="12" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="Q128" s="12" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="5" t="inlineStr">
@@ -8718,10 +9315,20 @@
       <c r="M129" s="7" t="n">
         <v>2.37</v>
       </c>
-      <c r="N129" s="10" t="inlineStr"/>
-      <c r="O129" s="11" t="inlineStr"/>
-      <c r="P129" s="5" t="inlineStr"/>
-      <c r="Q129" s="5" t="inlineStr"/>
+      <c r="N129" s="10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O129" s="11" t="n">
+        <v>-15.36</v>
+      </c>
+      <c r="P129" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q129" s="5" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="12" t="inlineStr">
@@ -8781,8 +9388,14 @@
       </c>
       <c r="N130" s="10" t="inlineStr"/>
       <c r="O130" s="11" t="inlineStr"/>
-      <c r="P130" s="12" t="inlineStr"/>
-      <c r="Q130" s="12" t="inlineStr"/>
+      <c r="P130" s="12" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q130" s="12" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="5" t="inlineStr">
@@ -8842,18 +9455,564 @@
       </c>
       <c r="N131" s="10" t="inlineStr"/>
       <c r="O131" s="11" t="inlineStr"/>
-      <c r="P131" s="5" t="inlineStr"/>
-      <c r="Q131" s="5" t="inlineStr"/>
-    </row>
-    <row r="132" ht="22" customHeight="1"/>
-    <row r="133" ht="22" customHeight="1"/>
-    <row r="134" ht="22" customHeight="1"/>
-    <row r="135" ht="22" customHeight="1"/>
-    <row r="136" ht="22" customHeight="1"/>
-    <row r="137" ht="22" customHeight="1"/>
-    <row r="138" ht="22" customHeight="1"/>
-    <row r="139" ht="22" customHeight="1"/>
-    <row r="140" ht="22" customHeight="1"/>
+      <c r="P131" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q131" s="5" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="132" ht="22" customHeight="1">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>21:53</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>✅ Chris Rodesch</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>Luka Mikrut</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Zagreb, Croatia Men Singles</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H132" s="8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="I132" s="5" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="J132" s="9" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="K132" s="5" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="L132" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M132" s="7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N132" s="10" t="inlineStr"/>
+      <c r="O132" s="11" t="inlineStr"/>
+      <c r="P132" s="5" t="inlineStr"/>
+      <c r="Q132" s="5" t="inlineStr"/>
+    </row>
+    <row r="133" ht="22" customHeight="1">
+      <c r="A133" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="inlineStr">
+        <is>
+          <t>21:53</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>✅ Quentin Halys</t>
+        </is>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>Botic Van de Zandschulp</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Bordeaux, France Men Singles</t>
+        </is>
+      </c>
+      <c r="F133" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G133" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H133" s="8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I133" s="12" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="J133" s="14" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="K133" s="12" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="L133" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M133" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N133" s="10" t="inlineStr"/>
+      <c r="O133" s="11" t="inlineStr"/>
+      <c r="P133" s="12" t="inlineStr"/>
+      <c r="Q133" s="12" t="inlineStr"/>
+    </row>
+    <row r="134" ht="22" customHeight="1">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>21:53</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>✅ Aleksandar Vukic</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>Giovanni Mpetshi Perricard</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Bordeaux, France Men Singles</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H134" s="8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I134" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="J134" s="14" t="n">
+        <v>39</v>
+      </c>
+      <c r="K134" s="5" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="L134" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M134" s="7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N134" s="10" t="inlineStr"/>
+      <c r="O134" s="11" t="inlineStr"/>
+      <c r="P134" s="5" t="inlineStr"/>
+      <c r="Q134" s="5" t="inlineStr"/>
+    </row>
+    <row r="135" ht="22" customHeight="1">
+      <c r="A135" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B135" s="12" t="inlineStr">
+        <is>
+          <t>21:53</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>✅ Leandro Riedi</t>
+        </is>
+      </c>
+      <c r="D135" s="12" t="inlineStr">
+        <is>
+          <t>Miomir Kecmanovic</t>
+        </is>
+      </c>
+      <c r="E135" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Valencia, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="F135" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G135" s="13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="H135" s="8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I135" s="12" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="J135" s="14" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="K135" s="12" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="L135" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M135" s="13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N135" s="10" t="inlineStr"/>
+      <c r="O135" s="11" t="inlineStr"/>
+      <c r="P135" s="12" t="inlineStr"/>
+      <c r="Q135" s="12" t="inlineStr"/>
+    </row>
+    <row r="136" ht="22" customHeight="1">
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>21:53</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>✅ Maximus Jones</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>Philip Sekulic</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Bengaluru 2, India Men Singles</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H136" s="8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I136" s="5" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="J136" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="K136" s="5" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="L136" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M136" s="7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N136" s="10" t="inlineStr"/>
+      <c r="O136" s="11" t="inlineStr"/>
+      <c r="P136" s="5" t="inlineStr"/>
+      <c r="Q136" s="5" t="inlineStr"/>
+    </row>
+    <row r="137" ht="22" customHeight="1">
+      <c r="A137" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B137" s="12" t="inlineStr">
+        <is>
+          <t>21:53</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>✅ Petr Brunclik</t>
+        </is>
+      </c>
+      <c r="D137" s="12" t="inlineStr">
+        <is>
+          <t>Jaime Faria</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Oeiras 4, Portugal Men Singles</t>
+        </is>
+      </c>
+      <c r="F137" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G137" s="13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H137" s="8" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="I137" s="12" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="J137" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="K137" s="12" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="L137" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M137" s="13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N137" s="10" t="inlineStr"/>
+      <c r="O137" s="11" t="inlineStr"/>
+      <c r="P137" s="12" t="inlineStr"/>
+      <c r="Q137" s="12" t="inlineStr"/>
+    </row>
+    <row r="138" ht="22" customHeight="1">
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>21:53</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>✅ Joao Lucas Reis Da Silva</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>Elmer Moller</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Zagreb, Croatia Men Singles</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G138" s="7" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="H138" s="8" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I138" s="5" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="J138" s="15" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="K138" s="5" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="L138" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M138" s="7" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="N138" s="10" t="inlineStr"/>
+      <c r="O138" s="11" t="inlineStr"/>
+      <c r="P138" s="5" t="inlineStr"/>
+      <c r="Q138" s="5" t="inlineStr"/>
+    </row>
+    <row r="139" ht="22" customHeight="1">
+      <c r="A139" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="inlineStr">
+        <is>
+          <t>21:53</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>✅ Benjamin Bonzi</t>
+        </is>
+      </c>
+      <c r="D139" s="12" t="inlineStr">
+        <is>
+          <t>Tallon Griekspoor</t>
+        </is>
+      </c>
+      <c r="E139" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Bordeaux, France Men Singles</t>
+        </is>
+      </c>
+      <c r="F139" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G139" s="13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H139" s="8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I139" s="12" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="J139" s="15" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="K139" s="12" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="L139" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M139" s="13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N139" s="10" t="inlineStr"/>
+      <c r="O139" s="11" t="inlineStr"/>
+      <c r="P139" s="12" t="inlineStr"/>
+      <c r="Q139" s="12" t="inlineStr"/>
+    </row>
+    <row r="140" ht="22" customHeight="1">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>21:53</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>✅ Alexander Shevchenko</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>Raphael Collignon</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Bordeaux, France Men Singles</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="G140" s="7" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H140" s="8" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I140" s="5" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="J140" s="15" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="K140" s="5" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="L140" s="5" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+      <c r="M140" s="7" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N140" s="10" t="inlineStr"/>
+      <c r="O140" s="11" t="inlineStr"/>
+      <c r="P140" s="5" t="inlineStr"/>
+      <c r="Q140" s="5" t="inlineStr"/>
+    </row>
     <row r="141" ht="22" customHeight="1"/>
     <row r="142" ht="22" customHeight="1"/>
     <row r="143" ht="22" customHeight="1"/>
@@ -9033,7 +10192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P129"/>
+  <dimension ref="A1:R144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9135,6 +10294,16 @@
           <t>Fonte</t>
         </is>
       </c>
+      <c r="Q1" s="19" t="inlineStr">
+        <is>
+          <t>Esito</t>
+        </is>
+      </c>
+      <c r="R1" s="19" t="inlineStr">
+        <is>
+          <t>Profitto</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
@@ -10323,6 +11492,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="17" t="inlineStr">
@@ -11181,6 +12358,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R32" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="12" t="inlineStr">
@@ -11709,6 +12894,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R40" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="12" t="inlineStr">
@@ -11907,6 +13100,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R43" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="17" t="inlineStr">
@@ -11973,6 +13174,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R44" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="12" t="inlineStr">
@@ -12105,6 +13314,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="12" t="inlineStr">
@@ -12237,6 +13454,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R48" t="n">
+        <v>0.83</v>
+      </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="12" t="inlineStr">
@@ -12303,6 +13528,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R49" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="17" t="inlineStr">
@@ -12369,6 +13602,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R50" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="12" t="inlineStr">
@@ -12435,6 +13676,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R51" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="17" t="inlineStr">
@@ -12501,6 +13750,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R52" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="12" t="inlineStr">
@@ -12567,6 +13824,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R53" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="17" t="inlineStr">
@@ -12633,6 +13898,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R54" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="12" t="inlineStr">
@@ -12699,6 +13972,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R55" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="17" t="inlineStr">
@@ -12765,6 +14046,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R56" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="12" t="inlineStr">
@@ -12831,6 +14120,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R57" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="17" t="inlineStr">
@@ -12897,6 +14194,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R58" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="12" t="inlineStr">
@@ -12963,6 +14268,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R59" t="n">
+        <v>0.83</v>
+      </c>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="17" t="inlineStr">
@@ -13029,6 +14342,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R60" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="12" t="inlineStr">
@@ -13095,6 +14416,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R61" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="17" t="inlineStr">
@@ -13161,6 +14490,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R62" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="12" t="inlineStr">
@@ -13227,6 +14564,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R63" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="17" t="inlineStr">
@@ -13293,6 +14638,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R64" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="12" t="inlineStr">
@@ -13359,6 +14712,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R65" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="17" t="inlineStr">
@@ -13425,6 +14786,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R66" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="12" t="inlineStr">
@@ -13491,6 +14860,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R67" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="17" t="inlineStr">
@@ -13623,6 +15000,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R69" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="17" t="inlineStr">
@@ -13689,6 +15074,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R70" t="n">
+        <v>1.1</v>
+      </c>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="12" t="inlineStr">
@@ -13755,6 +15148,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R71" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="17" t="inlineStr">
@@ -13821,6 +15222,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R72" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="12" t="inlineStr">
@@ -13887,6 +15296,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R73" t="n">
+        <v>0.83</v>
+      </c>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="17" t="inlineStr">
@@ -13953,6 +15370,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R74" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="12" t="inlineStr">
@@ -14019,6 +15444,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R75" t="n">
+        <v>0.72</v>
+      </c>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="17" t="inlineStr">
@@ -14085,6 +15518,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R76" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="12" t="inlineStr">
@@ -14151,6 +15592,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R77" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="17" t="inlineStr">
@@ -14217,6 +15666,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R78" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="12" t="inlineStr">
@@ -14283,6 +15740,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R79" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="17" t="inlineStr">
@@ -14349,6 +15814,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R80" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="12" t="inlineStr">
@@ -14415,6 +15888,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R81" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="12" t="inlineStr">
@@ -14481,6 +15962,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R82" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="12" t="inlineStr">
@@ -14547,6 +16036,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R83" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="17" t="inlineStr">
@@ -14613,6 +16110,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R84" t="n">
+        <v>0.83</v>
+      </c>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="17" t="inlineStr">
@@ -14679,6 +16184,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R85" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="12" t="inlineStr">
@@ -14745,6 +16258,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R86" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="17" t="inlineStr">
@@ -14811,6 +16332,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R87" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="12" t="inlineStr">
@@ -14877,6 +16406,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R88" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="17" t="inlineStr">
@@ -14943,6 +16480,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R89" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="12" t="inlineStr">
@@ -15009,6 +16554,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R90" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="17" t="inlineStr">
@@ -15075,6 +16628,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R91" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="12" t="inlineStr">
@@ -15141,6 +16702,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R92" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="17" t="inlineStr">
@@ -15207,6 +16776,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R93" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="12" t="inlineStr">
@@ -15273,6 +16850,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R94" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="17" t="inlineStr">
@@ -15339,6 +16924,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R95" t="n">
+        <v>0.83</v>
+      </c>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="12" t="inlineStr">
@@ -15405,6 +16998,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R96" t="n">
+        <v>0.83</v>
+      </c>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="17" t="inlineStr">
@@ -15471,6 +17072,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R97" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="12" t="inlineStr">
@@ -15537,6 +17146,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R98" t="n">
+        <v>0.9</v>
+      </c>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="17" t="inlineStr">
@@ -15603,6 +17220,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R99" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="12" t="inlineStr">
@@ -15669,6 +17294,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R100" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="17" t="inlineStr">
@@ -15735,6 +17368,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R101" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="12" t="inlineStr">
@@ -15801,6 +17442,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R102" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="17" t="inlineStr">
@@ -15867,6 +17516,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R103" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="12" t="inlineStr">
@@ -15933,6 +17590,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R104" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="17" t="inlineStr">
@@ -15999,6 +17664,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R105" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="12" t="inlineStr">
@@ -16131,6 +17804,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R107" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="12" t="inlineStr">
@@ -16197,6 +17878,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R108" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="17" t="inlineStr">
@@ -16263,6 +17952,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R109" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="12" t="inlineStr">
@@ -16329,6 +18026,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R110" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="17" t="inlineStr">
@@ -16395,6 +18100,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R111" t="n">
+        <v>0.72</v>
+      </c>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="12" t="inlineStr">
@@ -16461,6 +18174,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R112" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="17" t="inlineStr">
@@ -16527,6 +18248,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R113" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="12" t="inlineStr">
@@ -16593,6 +18322,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R114" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="17" t="inlineStr">
@@ -16659,6 +18396,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R115" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="12" t="inlineStr">
@@ -16725,6 +18470,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R116" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="17" t="inlineStr">
@@ -16857,6 +18610,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R118" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="17" t="inlineStr">
@@ -16923,6 +18684,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R119" t="n">
+        <v>0.72</v>
+      </c>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="12" t="inlineStr">
@@ -16989,6 +18758,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R120" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="17" t="inlineStr">
@@ -17055,6 +18832,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R121" t="n">
+        <v>0.83</v>
+      </c>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="12" t="inlineStr">
@@ -17121,6 +18906,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R122" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="17" t="inlineStr">
@@ -17187,6 +18980,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R123" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="12" t="inlineStr">
@@ -17253,6 +19054,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R124" t="n">
+        <v>1.05</v>
+      </c>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="17" t="inlineStr">
@@ -17319,6 +19128,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R125" t="n">
+        <v>0.87</v>
+      </c>
     </row>
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="12" t="inlineStr">
@@ -17385,6 +19202,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R126" t="n">
+        <v>0.87</v>
+      </c>
     </row>
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="17" t="inlineStr">
@@ -17451,6 +19276,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R127" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="12" t="inlineStr">
@@ -17517,6 +19350,14 @@
           <t>odds-api.io</t>
         </is>
       </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="R128" t="n">
+        <v>0.83</v>
+      </c>
     </row>
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="17" t="inlineStr">
@@ -17583,22 +19424,1005 @@
           <t>odds-api.io</t>
         </is>
       </c>
-    </row>
-    <row r="130" ht="22" customHeight="1"/>
-    <row r="131" ht="22" customHeight="1"/>
-    <row r="132" ht="22" customHeight="1"/>
-    <row r="133" ht="22" customHeight="1"/>
-    <row r="134" ht="22" customHeight="1"/>
-    <row r="135" ht="22" customHeight="1"/>
-    <row r="136" ht="22" customHeight="1"/>
-    <row r="137" ht="22" customHeight="1"/>
-    <row r="138" ht="22" customHeight="1"/>
-    <row r="139" ht="22" customHeight="1"/>
-    <row r="140" ht="22" customHeight="1"/>
-    <row r="141" ht="22" customHeight="1"/>
-    <row r="142" ht="22" customHeight="1"/>
-    <row r="143" ht="22" customHeight="1"/>
-    <row r="144" ht="22" customHeight="1"/>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="R129" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="130" ht="22" customHeight="1">
+      <c r="A130" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B130" s="17" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>✅ Leandro Riedi  +1.5</t>
+        </is>
+      </c>
+      <c r="D130" s="17" t="inlineStr">
+        <is>
+          <t>Miomir Kecmanovic</t>
+        </is>
+      </c>
+      <c r="E130" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F130" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G130" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H130" s="17" t="inlineStr"/>
+      <c r="I130" s="17" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="J130" s="9" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="K130" s="17" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Valencia, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="L130" s="17" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="M130" s="17" t="n">
+        <v>77</v>
+      </c>
+      <c r="N130" s="17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="O130" s="17" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="P130" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="22" customHeight="1">
+      <c r="A131" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>✅ Joao Lucas Reis Da Silva  +3.5</t>
+        </is>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t>Elmer Moller</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F131" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G131" s="13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H131" s="12" t="inlineStr"/>
+      <c r="I131" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="J131" s="9" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="K131" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Zagreb, Croatia Men Singles</t>
+        </is>
+      </c>
+      <c r="L131" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="M131" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="N131" s="12" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="O131" s="12" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="P131" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="22" customHeight="1">
+      <c r="A132" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B132" s="17" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>✅ Maximus Jones  +2.5</t>
+        </is>
+      </c>
+      <c r="D132" s="17" t="inlineStr">
+        <is>
+          <t>Philip Sekulic</t>
+        </is>
+      </c>
+      <c r="E132" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F132" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G132" s="18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H132" s="17" t="inlineStr"/>
+      <c r="I132" s="17" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="J132" s="9" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="K132" s="17" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Bengaluru 2, India Men Singles</t>
+        </is>
+      </c>
+      <c r="L132" s="17" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="M132" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="N132" s="17" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O132" s="17" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="P132" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="22" customHeight="1">
+      <c r="A133" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>✅ Aleksandar Vukic  +2.5</t>
+        </is>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>Giovanni Mpetshi Perricard</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F133" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G133" s="13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H133" s="12" t="inlineStr"/>
+      <c r="I133" s="12" t="n">
+        <v>72.3</v>
+      </c>
+      <c r="J133" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="K133" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Bordeaux, France Men Singles</t>
+        </is>
+      </c>
+      <c r="L133" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="M133" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="N133" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="O133" s="12" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="P133" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="22" customHeight="1">
+      <c r="A134" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B134" s="17" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>✅ Nicolas Alvarez Varona  +5.5</t>
+        </is>
+      </c>
+      <c r="D134" s="17" t="inlineStr">
+        <is>
+          <t>Adolfo Daniel Vallejo</t>
+        </is>
+      </c>
+      <c r="E134" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F134" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G134" s="18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H134" s="17" t="inlineStr"/>
+      <c r="I134" s="17" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="J134" s="9" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="K134" s="17" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Valencia, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="L134" s="17" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="M134" s="17" t="n">
+        <v>130</v>
+      </c>
+      <c r="N134" s="17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O134" s="17" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="P134" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="22" customHeight="1">
+      <c r="A135" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B135" s="12" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>✅ Arthur Fery  +0.5</t>
+        </is>
+      </c>
+      <c r="D135" s="12" t="inlineStr">
+        <is>
+          <t>Dominic Stricker</t>
+        </is>
+      </c>
+      <c r="E135" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F135" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G135" s="13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H135" s="12" t="inlineStr"/>
+      <c r="I135" s="12" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="J135" s="9" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="K135" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Zagreb, Croatia Men Singles</t>
+        </is>
+      </c>
+      <c r="L135" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="M135" s="12" t="n">
+        <v>168</v>
+      </c>
+      <c r="N135" s="12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="O135" s="12" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="P135" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="22" customHeight="1">
+      <c r="A136" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B136" s="17" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>✅ Alexander Shevchenko  +3.5</t>
+        </is>
+      </c>
+      <c r="D136" s="17" t="inlineStr">
+        <is>
+          <t>Raphael Collignon</t>
+        </is>
+      </c>
+      <c r="E136" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F136" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G136" s="18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H136" s="17" t="inlineStr"/>
+      <c r="I136" s="17" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="J136" s="9" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="K136" s="17" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Bordeaux, France Men Singles</t>
+        </is>
+      </c>
+      <c r="L136" s="17" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="M136" s="17" t="n">
+        <v>86</v>
+      </c>
+      <c r="N136" s="17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="O136" s="17" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="P136" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="22" customHeight="1">
+      <c r="A137" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B137" s="12" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>✅ Petr Brunclik  +4.5</t>
+        </is>
+      </c>
+      <c r="D137" s="12" t="inlineStr">
+        <is>
+          <t>Jaime Faria</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F137" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G137" s="13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="H137" s="12" t="inlineStr"/>
+      <c r="I137" s="12" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="J137" s="9" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="K137" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Oeiras 4, Portugal Men Singles</t>
+        </is>
+      </c>
+      <c r="L137" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="M137" s="12" t="n">
+        <v>115</v>
+      </c>
+      <c r="N137" s="12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="O137" s="12" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="P137" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="22" customHeight="1">
+      <c r="A138" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B138" s="17" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>✅ Daniel Elahi Galan  +2.5</t>
+        </is>
+      </c>
+      <c r="D138" s="17" t="inlineStr">
+        <is>
+          <t>Jan Choinski</t>
+        </is>
+      </c>
+      <c r="E138" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F138" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G138" s="18" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H138" s="17" t="inlineStr"/>
+      <c r="I138" s="17" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="J138" s="14" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="K138" s="17" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Zagreb, Croatia Men Singles</t>
+        </is>
+      </c>
+      <c r="L138" s="17" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="M138" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="N138" s="17" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="O138" s="17" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="P138" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="22" customHeight="1">
+      <c r="A139" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>✅ Benjamin Bonzi  +1.5</t>
+        </is>
+      </c>
+      <c r="D139" s="12" t="inlineStr">
+        <is>
+          <t>Tallon Griekspoor</t>
+        </is>
+      </c>
+      <c r="E139" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F139" s="12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G139" s="13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H139" s="12" t="inlineStr"/>
+      <c r="I139" s="12" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="J139" s="14" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="K139" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Bordeaux, France Men Singles</t>
+        </is>
+      </c>
+      <c r="L139" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="M139" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="N139" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="O139" s="12" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="P139" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="22" customHeight="1">
+      <c r="A140" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B140" s="17" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>✅ Aleksandar Kovacevic  +3.5</t>
+        </is>
+      </c>
+      <c r="D140" s="17" t="inlineStr">
+        <is>
+          <t>Alejandro Tabilo</t>
+        </is>
+      </c>
+      <c r="E140" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F140" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G140" s="18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="H140" s="17" t="inlineStr"/>
+      <c r="I140" s="17" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="J140" s="14" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="K140" s="17" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Valencia, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="L140" s="17" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="M140" s="17" t="n">
+        <v>162</v>
+      </c>
+      <c r="N140" s="17" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="O140" s="17" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="P140" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="22" customHeight="1">
+      <c r="A141" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B141" s="12" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>✅ Roberto Bautista Agut  +2.5</t>
+        </is>
+      </c>
+      <c r="D141" s="12" t="inlineStr">
+        <is>
+          <t>Zizou Bergs</t>
+        </is>
+      </c>
+      <c r="E141" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F141" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G141" s="13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H141" s="12" t="inlineStr"/>
+      <c r="I141" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="J141" s="14" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="K141" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Valencia, Spain Men Singles</t>
+        </is>
+      </c>
+      <c r="L141" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="M141" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="N141" s="12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="O141" s="12" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="P141" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="22" customHeight="1">
+      <c r="A142" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B142" s="17" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>✅ Andres Andrade  +2.5</t>
+        </is>
+      </c>
+      <c r="D142" s="17" t="inlineStr">
+        <is>
+          <t>Marco Cecchinato</t>
+        </is>
+      </c>
+      <c r="E142" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F142" s="17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G142" s="18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H142" s="17" t="inlineStr"/>
+      <c r="I142" s="17" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="J142" s="14" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="K142" s="17" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Zagreb, Croatia Men Singles</t>
+        </is>
+      </c>
+      <c r="L142" s="17" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="M142" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="N142" s="17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O142" s="17" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="P142" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="22" customHeight="1">
+      <c r="A143" s="12" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B143" s="12" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>✅ Titouan Droguet  +0.5</t>
+        </is>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
+          <t>Terence Atmane</t>
+        </is>
+      </c>
+      <c r="E143" s="12" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F143" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G143" s="13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H143" s="12" t="inlineStr"/>
+      <c r="I143" s="12" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="J143" s="15" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="K143" s="12" t="inlineStr">
+        <is>
+          <t>Challenger - ATP Challenger Bordeaux, France Men Singles</t>
+        </is>
+      </c>
+      <c r="L143" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+      <c r="M143" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="N143" s="12" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="O143" s="12" t="inlineStr">
+        <is>
+          <t>TA-hard+forma</t>
+        </is>
+      </c>
+      <c r="P143" s="12" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="22" customHeight="1">
+      <c r="A144" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B144" s="17" t="inlineStr">
+        <is>
+          <t>21:54</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>✅ Luciano Darderi  +3.5</t>
+        </is>
+      </c>
+      <c r="D144" s="17" t="inlineStr">
+        <is>
+          <t>Rafael Jodar</t>
+        </is>
+      </c>
+      <c r="E144" s="17" t="inlineStr">
+        <is>
+          <t>Games</t>
+        </is>
+      </c>
+      <c r="F144" s="17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G144" s="18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H144" s="17" t="inlineStr"/>
+      <c r="I144" s="17" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="J144" s="15" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="K144" s="17" t="inlineStr">
+        <is>
+          <t>ATP - ATP Rome, Italy Men Singles</t>
+        </is>
+      </c>
+      <c r="L144" s="17" t="inlineStr">
+        <is>
+          <t>CLAY</t>
+        </is>
+      </c>
+      <c r="M144" s="17" t="n">
+        <v>148</v>
+      </c>
+      <c r="N144" s="17" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="O144" s="17" t="inlineStr">
+        <is>
+          <t>TA-clay+forma</t>
+        </is>
+      </c>
+      <c r="P144" s="17" t="inlineStr">
+        <is>
+          <t>odds-api.io</t>
+        </is>
+      </c>
+    </row>
     <row r="145" ht="22" customHeight="1"/>
     <row r="146" ht="22" customHeight="1"/>
     <row r="147" ht="22" customHeight="1"/>
